--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -11,13 +11,14 @@
     <sheet name="Par" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Grp" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Acc" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Op" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Bsk" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Prd" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Bnk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="List" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sync" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Help" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cls" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Op" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bsk" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Prd" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Bnk" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="List" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sync" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Help" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="AcctCodes">Acc!$A$10:$A$259</definedName>
@@ -54,7 +55,7 @@
     <definedName name="OpTbl">Op!$A$10:$S$33</definedName>
     <definedName name="ParamTbl">Par!$A$10:$E$21</definedName>
     <definedName name="ProductTbl">Prd!$B$10:$D$29</definedName>
-    <definedName name="ListBankOps">List!$S$10:$S$29</definedName>
+    <definedName name="ListBankOps">List!$S$10:$S$36</definedName>
     <definedName name="ListOtherScalesLabel">List!$T$10:$T$29</definedName>
     <definedName name="ListBankNames">List!$U$10:$U$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$48</definedName>
@@ -68,22 +69,24 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Acc'!$A$8:$M$259</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Acc'!$8:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Acc'!$A$1:$M$260</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Op'!$A$8:$S$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Op'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Op'!$A$1:$S$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Bsk'!$A$8:$J$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Bsk'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Bsk'!$A$1:$J$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Prd'!$A$8:$G$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Prd'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Prd'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Bnk'!$A$8:$G$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Bnk'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Bnk'!$A$1:$G$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'List'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'List'!$A$1:$R$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Sync'!$A$1:$K$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'Help'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cls'!$8:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cls'!$A$1:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Op'!$A$8:$S$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Op'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Op'!$A$1:$S$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bsk'!$A$8:$J$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Bsk'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Bsk'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Prd'!$A$8:$G$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prd'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Prd'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Bnk'!$A$8:$G$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Bnk'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Bnk'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'List'!$8:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'List'!$A$1:$R$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Sync'!$A$1:$K$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Help'!$A$1:$J$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,7 +100,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00;[Red]-#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0;[Red](#,##0)"/>
   </numFmts>
-  <fonts count="84">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -613,6 +616,42 @@
     </font>
     <font>
       <name val="B Nazanin"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Titr"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <color rgb="006B7A76"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="008B7E68"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <color rgb="002B2A26"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <color rgb="009A6B15"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
       <b val="1"/>
       <color rgb="FF14453D"/>
       <sz val="9"/>
@@ -636,7 +675,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="30">
     <fill>
       <patternFill/>
     </fill>
@@ -778,11 +817,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FBF8F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EADB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E4F0E8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -1412,6 +1471,20 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00DDD5C4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDD5C4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDD5C4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDD5C4"/>
+      </bottom>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1453,7 +1526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -1852,6 +1925,8 @@
     <xf numFmtId="0" fontId="75" fillId="21" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="76" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -1876,20 +1951,45 @@
     <xf numFmtId="0" fontId="79" fillId="23" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="24" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="26" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="27" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="27" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="28" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="28" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="89" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="25" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="90" fillId="29" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3825,51 +3925,51 @@
     </row>
     <row r="45"/>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="168" t="inlineStr">
+      <c r="A46" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">     فایل‌های همراه — با یک کلیک باز می‌شوند (مسیر نسبی، همه در همین پوشه)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="169" t="inlineStr">
+      <c r="A47" s="178" t="inlineStr">
         <is>
           <t>دفتر ثبت  01_Entry</t>
         </is>
       </c>
-      <c r="C47" s="169" t="inlineStr">
+      <c r="C47" s="178" t="inlineStr">
         <is>
           <t>بانک  02_Bank</t>
         </is>
       </c>
-      <c r="E47" s="169" t="inlineStr">
+      <c r="E47" s="178" t="inlineStr">
         <is>
           <t>گزارش‌ها  03_Report</t>
         </is>
       </c>
-      <c r="G47" s="169" t="inlineStr">
+      <c r="G47" s="178" t="inlineStr">
         <is>
           <t>فاکتورها  04_Inv</t>
         </is>
       </c>
-      <c r="I47" s="169" t="inlineStr">
+      <c r="I47" s="178" t="inlineStr">
         <is>
           <t>تراز  05_Bal</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="169" t="inlineStr">
+      <c r="A48" s="178" t="inlineStr">
         <is>
           <t>خریداران  06_Buyers</t>
         </is>
       </c>
-      <c r="C48" s="169" t="inlineStr">
+      <c r="C48" s="178" t="inlineStr">
         <is>
           <t>نمونه  07_Demo</t>
         </is>
       </c>
-      <c r="E48" s="169" t="inlineStr">
+      <c r="E48" s="178" t="inlineStr">
         <is>
           <t>داشبورد  08_Dash</t>
         </is>
@@ -3980,11 +4080,517 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E6B4F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.7109375" customWidth="1" min="1" max="1"/>
+    <col width="34.7109375" customWidth="1" min="2" max="2"/>
+    <col width="16.7109375" customWidth="1" min="3" max="3"/>
+    <col width="22.7109375" customWidth="1" min="4" max="4"/>
+    <col width="26.7109375" customWidth="1" min="5" max="5"/>
+    <col width="8.7109375" customWidth="1" min="6" max="6"/>
+    <col width="38.7109375" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" s="138" t="inlineStr">
+        <is>
+          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
+        </is>
+      </c>
+      <c r="C1" s="132" t="inlineStr">
+        <is>
+          <t>MAZANDASHT  ·  CITRUS SORTING &amp; PACKING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38.25" customHeight="1">
+      <c r="A2" s="133" t="inlineStr">
+        <is>
+          <t>بانک‌ها و حساب‌های شرکت</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45.75" customHeight="1">
+      <c r="A3" s="134" t="inlineStr">
+        <is>
+          <t>کد بانک ثابت است؛ عنوان را آزادانه عوض کنید  ·  پوز باسکول به صادرات ۲۰۰۶ وصل است</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>راهنما</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>ورود دستی</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>خودکار</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>ورود</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>خروج</t>
+        </is>
+      </c>
+      <c r="F4" s="50" t="inlineStr">
+        <is>
+          <t>هشدار</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>بانک‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="140" t="n"/>
+      <c r="C5" s="108" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>بانک فعال</t>
+        </is>
+      </c>
+      <c r="E5" s="140" t="n"/>
+      <c r="F5" s="108" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>مانده اولیه</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1">
+      <c r="A6" s="52">
+        <f>COUNTIF($A$10:$A$19,"?*")</f>
+        <v/>
+      </c>
+      <c r="B6" s="141" t="n"/>
+      <c r="C6" s="109" t="n"/>
+      <c r="D6" s="53">
+        <f>COUNTIF($F$10:$F$19,"بله")</f>
+        <v/>
+      </c>
+      <c r="E6" s="141" t="n"/>
+      <c r="F6" s="109" t="n"/>
+      <c r="G6" s="53">
+        <f>SUM($C$10:$C$19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="6.75" customHeight="1"/>
+    <row r="8" ht="33.75" customHeight="1">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>کد بانک</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>عنوان نمایشی</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>مانده اولیه</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>کد حساب معین</t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>شبا</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>توضیح</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Ledger</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>IBAN</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>BN01</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>صادرات ۹۰۰۹ — جاری اصلی</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D10" s="58" t="inlineStr">
+        <is>
+          <t>BN01</t>
+        </is>
+      </c>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G10" s="60" t="inlineStr">
+        <is>
+          <t>حساب جاری اصلی شرکت</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>BN02</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>صادرات ۲۰۰۶ — پوز باسکول</t>
+        </is>
+      </c>
+      <c r="C11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>BN02</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G11" s="60" t="inlineStr">
+        <is>
+          <t>پوز باسکول به این حساب وصل است</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>BN03</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>ملت</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="58" t="inlineStr">
+        <is>
+          <t>BN03</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G12" s="60" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>BN04</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>کشاورزی</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>BN04</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G13" s="60" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>BN05</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>سپه</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="58" t="inlineStr">
+        <is>
+          <t>BN05</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G14" s="60" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>BN06</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>مهر ایران</t>
+        </is>
+      </c>
+      <c r="C15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="58" t="inlineStr">
+        <is>
+          <t>BN06</t>
+        </is>
+      </c>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G15" s="60" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>BN07</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>تجارت</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58" t="inlineStr">
+        <is>
+          <t>BN07</t>
+        </is>
+      </c>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G16" s="60" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>BN08</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>پاسارگاد</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="58" t="inlineStr">
+        <is>
+          <t>BN08</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G17" s="60" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>BN09</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>رفاه</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="58" t="inlineStr">
+        <is>
+          <t>BN09</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G18" s="60" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>BN10</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>قرض‌الحسنه</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="58" t="inlineStr">
+        <is>
+          <t>BN10</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="47" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G19" s="60" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:G20"/>
+  <mergeCells count="8">
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B10:B20">
+    <cfRule type="expression" priority="1" dxfId="30">
+      <formula>LEFT($A10,6)="BANK02"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F10:F20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>ListYesNo</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.28" right="0.28" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;Lمازندشت&amp;RMAZANDASHT · CITRUS</oddHeader>
+    <oddFooter>&amp;Lمازندشت — سورتینگ و بسته‌بندی مرکبات&amp;Cصفحه &amp;P از &amp;N&amp;RMAZANDASHT · 1405</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FF6B7A76"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.7109375" customWidth="1" min="1" max="18"/>
@@ -4370,7 +4976,7 @@
       </c>
       <c r="S10" s="152" t="inlineStr">
         <is>
-          <t>دریافت از مشتری</t>
+          <t>واریز نقدی به حساب</t>
         </is>
       </c>
       <c r="T10" s="152" t="inlineStr">
@@ -4477,7 +5083,7 @@
       </c>
       <c r="S11" s="152" t="inlineStr">
         <is>
-          <t>پرداخت به مشتری</t>
+          <t>دریافت از مشتری</t>
         </is>
       </c>
       <c r="T11" s="152" t="inlineStr">
@@ -4564,7 +5170,7 @@
       <c r="R12" s="47" t="n"/>
       <c r="S12" s="152" t="inlineStr">
         <is>
-          <t>دریافت نقدی و واریز به بانک</t>
+          <t>واریز بارفروشان</t>
         </is>
       </c>
       <c r="T12" s="152" t="inlineStr">
@@ -4643,7 +5249,7 @@
       <c r="R13" s="47" t="n"/>
       <c r="S13" s="152" t="inlineStr">
         <is>
-          <t>پرداخت هزینه</t>
+          <t>پاس چک مشتریان (واریز به حساب ما)</t>
         </is>
       </c>
       <c r="T13" s="152" t="inlineStr">
@@ -4702,7 +5308,7 @@
       <c r="R14" s="47" t="n"/>
       <c r="S14" s="152" t="inlineStr">
         <is>
-          <t>انتقال داخلی بین بانک‌ها</t>
+          <t>انتقال دریافتی از حساب دیگر</t>
         </is>
       </c>
       <c r="T14" s="152" t="inlineStr">
@@ -4757,7 +5363,7 @@
       <c r="R15" s="47" t="n"/>
       <c r="S15" s="152" t="inlineStr">
         <is>
-          <t>پرداخت انعام مصطفی</t>
+          <t>واریز پز باسکول (۲۰۰۶)</t>
         </is>
       </c>
       <c r="T15" s="152" t="inlineStr">
@@ -4851,7 +5457,7 @@
       <c r="R17" s="47" t="n"/>
       <c r="S17" s="152" t="inlineStr">
         <is>
-          <t>پرداخت به باسکول دیگران</t>
+          <t>دریافت تسهیلات</t>
         </is>
       </c>
       <c r="T17" s="152" t="inlineStr">
@@ -4894,7 +5500,7 @@
       <c r="R18" s="47" t="n"/>
       <c r="S18" s="152" t="inlineStr">
         <is>
-          <t>واریز پز باسکول (۲۰۰۶)</t>
+          <t>سود سپرده</t>
         </is>
       </c>
       <c r="T18" s="152" t="inlineStr">
@@ -4937,7 +5543,7 @@
       <c r="R19" s="47" t="n"/>
       <c r="S19" s="152" t="inlineStr">
         <is>
-          <t>پاس چک (پرداخت چک)</t>
+          <t>سایر دریافت</t>
         </is>
       </c>
       <c r="T19" s="152" t="inlineStr">
@@ -4972,7 +5578,7 @@
       <c r="R20" s="47" t="n"/>
       <c r="S20" s="152" t="inlineStr">
         <is>
-          <t>برگشت چک دریافتی</t>
+          <t>پرداخت به باغدار</t>
         </is>
       </c>
       <c r="T20" s="152" t="inlineStr">
@@ -5002,7 +5608,7 @@
       <c r="R21" s="47" t="n"/>
       <c r="S21" s="152" t="inlineStr">
         <is>
-          <t>واریز چک به حساب</t>
+          <t>پرداخت به مشتری</t>
         </is>
       </c>
       <c r="T21" s="152" t="inlineStr">
@@ -5032,7 +5638,7 @@
       <c r="R22" s="47" t="n"/>
       <c r="S22" s="152" t="inlineStr">
         <is>
-          <t>دریافت تسهیلات</t>
+          <t>پاس چک ما (چک پرداختی شرکت)</t>
         </is>
       </c>
       <c r="T22" s="152" t="inlineStr">
@@ -5062,7 +5668,7 @@
       <c r="R23" s="47" t="n"/>
       <c r="S23" s="152" t="inlineStr">
         <is>
-          <t>بازپرداخت تسهیلات</t>
+          <t>برداشت نقدی از حساب</t>
         </is>
       </c>
       <c r="T23" s="152" t="inlineStr">
@@ -5092,7 +5698,7 @@
       <c r="R24" s="47" t="n"/>
       <c r="S24" s="152" t="inlineStr">
         <is>
-          <t>سایر دریافت</t>
+          <t>انتقال پرداختی به حساب دیگر</t>
         </is>
       </c>
       <c r="T24" s="152" t="inlineStr">
@@ -5122,7 +5728,7 @@
       <c r="R25" s="47" t="n"/>
       <c r="S25" s="152" t="inlineStr">
         <is>
-          <t>سایر پرداخت</t>
+          <t>کارمزد و هزینه بانکی</t>
         </is>
       </c>
       <c r="T25" s="152" t="inlineStr">
@@ -5152,7 +5758,7 @@
       <c r="R26" s="47" t="n"/>
       <c r="S26" s="152" t="inlineStr">
         <is>
-          <t>تسویه دریافت (واسط)</t>
+          <t>پرداخت هزینه</t>
         </is>
       </c>
       <c r="T26" s="152" t="inlineStr">
@@ -5182,7 +5788,7 @@
       <c r="R27" s="47" t="n"/>
       <c r="S27" s="152" t="inlineStr">
         <is>
-          <t>تسویه پرداخت (واسط)</t>
+          <t>پرداخت انعام مصطفی</t>
         </is>
       </c>
       <c r="T27" s="152" t="inlineStr">
@@ -5210,6 +5816,11 @@
       <c r="P28" s="47" t="n"/>
       <c r="Q28" s="47" t="n"/>
       <c r="R28" s="47" t="n"/>
+      <c r="S28" s="152" t="inlineStr">
+        <is>
+          <t>پرداخت به باسکول دیگران</t>
+        </is>
+      </c>
       <c r="T28" s="152" t="inlineStr">
         <is>
           <t>BD019 – (بدون نام)</t>
@@ -5235,22 +5846,67 @@
       <c r="P29" s="47" t="n"/>
       <c r="Q29" s="47" t="n"/>
       <c r="R29" s="47" t="n"/>
+      <c r="S29" s="152" t="inlineStr">
+        <is>
+          <t>بازپرداخت تسهیلات</t>
+        </is>
+      </c>
       <c r="T29" s="152" t="inlineStr">
         <is>
           <t>BD020 – (بدون نام)</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
+    <row r="30">
+      <c r="S30" s="152" t="inlineStr">
+        <is>
+          <t>پاس چک مشتری برگشتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="S31" s="152" t="inlineStr">
+        <is>
+          <t>سایر پرداخت</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="S32" s="153" t="inlineStr">
         <is>
           <t>این سه فهرست، کشوهای فایل 02_Bank را می‌سازند. برای اضافه کردن نوع عملیات بانکی جدید، یک ردیف به ستون S اضافه کنید و در شیت Sync فایل بانک همان ردیف را ادامه دهید.</t>
         </is>
       </c>
-      <c r="T32" s="166" t="n"/>
-      <c r="U32" s="167" t="n"/>
+      <c r="T32" s="154" t="n"/>
+      <c r="U32" s="155" t="n"/>
+    </row>
+    <row r="33">
+      <c r="S33" s="152" t="inlineStr">
+        <is>
+          <t>دریافت از حساب شخصی رئیس</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="S34" s="152" t="inlineStr">
+        <is>
+          <t>انتقال داخلی بین بانک‌ها</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="S35" s="152" t="inlineStr">
+        <is>
+          <t>تسویه دریافت (واسط)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="S36" s="152" t="inlineStr">
+        <is>
+          <t>تسویه پرداخت (واسط)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5277,7 +5933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFB9B2A1"/>
@@ -5360,22 +6016,26 @@
       <c r="D7" s="110" t="n"/>
       <c r="E7" s="110" t="n"/>
       <c r="F7" s="110" t="n"/>
-      <c r="H7" s="154" t="inlineStr">
-        <is>
-          <t>دریافت از مشتری</t>
-        </is>
-      </c>
-      <c r="I7" s="155" t="inlineStr">
+      <c r="H7" s="156" t="inlineStr">
+        <is>
+          <t>واریز نقدی به حساب</t>
+        </is>
+      </c>
+      <c r="I7" s="157" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="J7" s="155" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="K7" s="155" t="inlineStr"/>
+      <c r="J7" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K7" s="157" t="inlineStr">
+        <is>
+          <t>X003</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="92" t="inlineStr">
@@ -5408,22 +6068,22 @@
           <t>شیت منبع</t>
         </is>
       </c>
-      <c r="H8" s="154" t="inlineStr">
-        <is>
-          <t>پرداخت به مشتری</t>
-        </is>
-      </c>
-      <c r="I8" s="155" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="J8" s="155" t="inlineStr">
+      <c r="H8" s="156" t="inlineStr">
+        <is>
+          <t>دریافت از مشتری</t>
+        </is>
+      </c>
+      <c r="I8" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J8" s="157" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="K8" s="155" t="inlineStr"/>
+      <c r="K8" s="157" t="inlineStr"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="93" t="inlineStr">
@@ -5435,7 +6095,7 @@
         <f>IFERROR(VLOOKUP($A9,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C9" s="156">
+      <c r="C9" s="158">
         <f>IFERROR(VLOOKUP($A9,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5452,26 +6112,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H9" s="154" t="inlineStr">
-        <is>
-          <t>دریافت نقدی و واریز به بانک</t>
-        </is>
-      </c>
-      <c r="I9" s="155" t="inlineStr">
+      <c r="H9" s="156" t="inlineStr">
+        <is>
+          <t>واریز بارفروشان</t>
+        </is>
+      </c>
+      <c r="I9" s="157" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="J9" s="155" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K9" s="155" t="inlineStr">
-        <is>
-          <t>X003</t>
-        </is>
-      </c>
+      <c r="J9" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K9" s="157" t="inlineStr"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="93" t="inlineStr">
@@ -5483,7 +6139,7 @@
         <f>IFERROR(VLOOKUP($A10,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C10" s="156">
+      <c r="C10" s="158">
         <f>IFERROR(VLOOKUP($A10,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5500,22 +6156,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H10" s="154" t="inlineStr">
-        <is>
-          <t>پرداخت هزینه</t>
-        </is>
-      </c>
-      <c r="I10" s="155" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="J10" s="155" t="inlineStr">
+      <c r="H10" s="156" t="inlineStr">
+        <is>
+          <t>پاس چک مشتریان (واریز به حساب ما)</t>
+        </is>
+      </c>
+      <c r="I10" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J10" s="157" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="K10" s="155" t="inlineStr"/>
+      <c r="K10" s="157" t="inlineStr"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="93" t="inlineStr">
@@ -5527,7 +6183,7 @@
         <f>IFERROR(VLOOKUP($A11,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C11" s="156">
+      <c r="C11" s="158">
         <f>IFERROR(VLOOKUP($A11,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5544,22 +6200,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H11" s="154" t="inlineStr">
-        <is>
-          <t>انتقال داخلی بین بانک‌ها</t>
-        </is>
-      </c>
-      <c r="I11" s="155" t="inlineStr">
-        <is>
-          <t>TRF</t>
-        </is>
-      </c>
-      <c r="J11" s="155" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="K11" s="155" t="inlineStr"/>
+      <c r="H11" s="156" t="inlineStr">
+        <is>
+          <t>انتقال دریافتی از حساب دیگر</t>
+        </is>
+      </c>
+      <c r="I11" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J11" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K11" s="157" t="inlineStr"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="93" t="inlineStr">
@@ -5571,7 +6227,7 @@
         <f>IFERROR(VLOOKUP($A12,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C12" s="156">
+      <c r="C12" s="158">
         <f>IFERROR(VLOOKUP($A12,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5588,24 +6244,24 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H12" s="154" t="inlineStr">
-        <is>
-          <t>پرداخت انعام مصطفی</t>
-        </is>
-      </c>
-      <c r="I12" s="155" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="J12" s="155" t="inlineStr">
+      <c r="H12" s="156" t="inlineStr">
+        <is>
+          <t>واریز پز باسکول (۲۰۰۶)</t>
+        </is>
+      </c>
+      <c r="I12" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J12" s="157" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="K12" s="155" t="inlineStr">
-        <is>
-          <t>X001</t>
+      <c r="K12" s="157" t="inlineStr">
+        <is>
+          <t>X011</t>
         </is>
       </c>
     </row>
@@ -5619,7 +6275,7 @@
         <f>IFERROR(VLOOKUP($A13,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C13" s="156">
+      <c r="C13" s="158">
         <f>IFERROR(VLOOKUP($A13,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5636,22 +6292,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H13" s="154" t="inlineStr">
+      <c r="H13" s="156" t="inlineStr">
         <is>
           <t>دریافت هزینه باسکول دیگران</t>
         </is>
       </c>
-      <c r="I13" s="155" t="inlineStr">
+      <c r="I13" s="157" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="J13" s="155" t="inlineStr">
+      <c r="J13" s="157" t="inlineStr">
         <is>
           <t>PICK</t>
         </is>
       </c>
-      <c r="K13" s="155" t="inlineStr"/>
+      <c r="K13" s="157" t="inlineStr"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="93" t="inlineStr">
@@ -5663,7 +6319,7 @@
         <f>IFERROR(VLOOKUP($A14,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C14" s="156">
+      <c r="C14" s="158">
         <f>IFERROR(VLOOKUP($A14,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5680,22 +6336,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H14" s="154" t="inlineStr">
-        <is>
-          <t>پرداخت به باسکول دیگران</t>
-        </is>
-      </c>
-      <c r="I14" s="155" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="J14" s="155" t="inlineStr">
-        <is>
-          <t>PICK</t>
-        </is>
-      </c>
-      <c r="K14" s="155" t="inlineStr"/>
+      <c r="H14" s="156" t="inlineStr">
+        <is>
+          <t>دریافت تسهیلات</t>
+        </is>
+      </c>
+      <c r="I14" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J14" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K14" s="157" t="inlineStr"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="93" t="inlineStr">
@@ -5707,7 +6363,7 @@
         <f>IFERROR(VLOOKUP($A15,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C15" s="156">
+      <c r="C15" s="158">
         <f>IFERROR(VLOOKUP($A15,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5724,24 +6380,24 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H15" s="154" t="inlineStr">
-        <is>
-          <t>واریز پز باسکول (۲۰۰۶)</t>
-        </is>
-      </c>
-      <c r="I15" s="155" t="inlineStr">
+      <c r="H15" s="156" t="inlineStr">
+        <is>
+          <t>سود سپرده</t>
+        </is>
+      </c>
+      <c r="I15" s="157" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="J15" s="155" t="inlineStr">
+      <c r="J15" s="157" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="K15" s="155" t="inlineStr">
-        <is>
-          <t>X011</t>
+      <c r="K15" s="157" t="inlineStr">
+        <is>
+          <t>X015</t>
         </is>
       </c>
     </row>
@@ -5755,7 +6411,7 @@
         <f>IFERROR(VLOOKUP($A16,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C16" s="156">
+      <c r="C16" s="158">
         <f>IFERROR(VLOOKUP($A16,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5772,26 +6428,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H16" s="154" t="inlineStr">
-        <is>
-          <t>پاس چک (پرداخت چک)</t>
-        </is>
-      </c>
-      <c r="I16" s="155" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="J16" s="155" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K16" s="155" t="inlineStr">
-        <is>
-          <t>X010</t>
-        </is>
-      </c>
+      <c r="H16" s="156" t="inlineStr">
+        <is>
+          <t>سایر دریافت</t>
+        </is>
+      </c>
+      <c r="I16" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J16" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K16" s="157" t="inlineStr"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="93" t="inlineStr">
@@ -5803,7 +6455,7 @@
         <f>IFERROR(VLOOKUP($A17,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C17" s="156">
+      <c r="C17" s="158">
         <f>IFERROR(VLOOKUP($A17,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5820,26 +6472,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H17" s="154" t="inlineStr">
-        <is>
-          <t>برگشت چک دریافتی</t>
-        </is>
-      </c>
-      <c r="I17" s="155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="J17" s="155" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K17" s="155" t="inlineStr">
-        <is>
-          <t>X010</t>
-        </is>
-      </c>
+      <c r="H17" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت به باغدار</t>
+        </is>
+      </c>
+      <c r="I17" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J17" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K17" s="157" t="inlineStr"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="93" t="inlineStr">
@@ -5851,7 +6499,7 @@
         <f>IFERROR(VLOOKUP($A18,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C18" s="156">
+      <c r="C18" s="158">
         <f>IFERROR(VLOOKUP($A18,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5868,26 +6516,22 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H18" s="154" t="inlineStr">
-        <is>
-          <t>واریز چک به حساب</t>
-        </is>
-      </c>
-      <c r="I18" s="155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="J18" s="155" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K18" s="155" t="inlineStr">
-        <is>
-          <t>X010</t>
-        </is>
-      </c>
+      <c r="H18" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت به مشتری</t>
+        </is>
+      </c>
+      <c r="I18" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J18" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K18" s="157" t="inlineStr"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="93" t="inlineStr">
@@ -5899,7 +6543,7 @@
         <f>IFERROR(VLOOKUP($A19,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C19" s="156">
+      <c r="C19" s="158">
         <f>IFERROR(VLOOKUP($A19,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5916,22 +6560,26 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H19" s="154" t="inlineStr">
-        <is>
-          <t>دریافت تسهیلات</t>
-        </is>
-      </c>
-      <c r="I19" s="155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="J19" s="155" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="K19" s="155" t="inlineStr"/>
+      <c r="H19" s="156" t="inlineStr">
+        <is>
+          <t>پاس چک ما (چک پرداختی شرکت)</t>
+        </is>
+      </c>
+      <c r="I19" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J19" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K19" s="157" t="inlineStr">
+        <is>
+          <t>X010</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="93" t="inlineStr">
@@ -5943,7 +6591,7 @@
         <f>IFERROR(VLOOKUP($A20,Par!$A$10:$E$21,2,0),"")</f>
         <v/>
       </c>
-      <c r="C20" s="156">
+      <c r="C20" s="158">
         <f>IFERROR(VLOOKUP($A20,Par!$A$10:$E$21,3,0),"")</f>
         <v/>
       </c>
@@ -5960,58 +6608,66 @@
           <t>Params</t>
         </is>
       </c>
-      <c r="H20" s="154" t="inlineStr">
-        <is>
-          <t>بازپرداخت تسهیلات</t>
-        </is>
-      </c>
-      <c r="I20" s="155" t="inlineStr">
+      <c r="H20" s="156" t="inlineStr">
+        <is>
+          <t>برداشت نقدی از حساب</t>
+        </is>
+      </c>
+      <c r="I20" s="157" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="J20" s="155" t="inlineStr">
+      <c r="J20" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K20" s="157" t="inlineStr">
+        <is>
+          <t>X003</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="156" t="inlineStr">
+        <is>
+          <t>انتقال پرداختی به حساب دیگر</t>
+        </is>
+      </c>
+      <c r="I21" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J21" s="157" t="inlineStr">
         <is>
           <t>CODE</t>
         </is>
       </c>
-      <c r="K20" s="155" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="H21" s="154" t="inlineStr">
-        <is>
-          <t>سایر دریافت</t>
-        </is>
-      </c>
-      <c r="I21" s="155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="J21" s="155" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="K21" s="155" t="inlineStr"/>
+      <c r="K21" s="157" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="H22" s="154" t="inlineStr">
-        <is>
-          <t>سایر پرداخت</t>
-        </is>
-      </c>
-      <c r="I22" s="155" t="inlineStr">
+      <c r="H22" s="156" t="inlineStr">
+        <is>
+          <t>کارمزد و هزینه بانکی</t>
+        </is>
+      </c>
+      <c r="I22" s="157" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="J22" s="155" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
-      <c r="K22" s="155" t="inlineStr"/>
+      <c r="J22" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K22" s="157" t="inlineStr">
+        <is>
+          <t>X012</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -6028,26 +6684,22 @@
       <c r="D23" s="110" t="n"/>
       <c r="E23" s="110" t="n"/>
       <c r="F23" s="110" t="n"/>
-      <c r="H23" s="154" t="inlineStr">
-        <is>
-          <t>تسویه دریافت (واسط)</t>
-        </is>
-      </c>
-      <c r="I23" s="155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="J23" s="155" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K23" s="155" t="inlineStr">
-        <is>
-          <t>X011</t>
-        </is>
-      </c>
+      <c r="H23" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت هزینه</t>
+        </is>
+      </c>
+      <c r="I23" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J23" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K23" s="157" t="inlineStr"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="92" t="inlineStr">
@@ -6072,24 +6724,24 @@
           <t>شیت منبع</t>
         </is>
       </c>
-      <c r="H24" s="154" t="inlineStr">
-        <is>
-          <t>تسویه پرداخت (واسط)</t>
-        </is>
-      </c>
-      <c r="I24" s="155" t="inlineStr">
+      <c r="H24" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت انعام مصطفی</t>
+        </is>
+      </c>
+      <c r="I24" s="157" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="J24" s="155" t="inlineStr">
+      <c r="J24" s="157" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="K24" s="155" t="inlineStr">
-        <is>
-          <t>X011</t>
+      <c r="K24" s="157" t="inlineStr">
+        <is>
+          <t>X001</t>
         </is>
       </c>
     </row>
@@ -6099,11 +6751,11 @@
           <t>باغدار</t>
         </is>
       </c>
-      <c r="B25" s="156">
+      <c r="B25" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A25)</f>
         <v/>
       </c>
-      <c r="C25" s="156">
+      <c r="C25" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A25)</f>
         <v/>
       </c>
@@ -6112,6 +6764,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H25" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت به باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="I25" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J25" s="157" t="inlineStr">
+        <is>
+          <t>PICK</t>
+        </is>
+      </c>
+      <c r="K25" s="157" t="inlineStr"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="93" t="inlineStr">
@@ -6119,11 +6787,11 @@
           <t>بارفروش</t>
         </is>
       </c>
-      <c r="B26" s="156">
+      <c r="B26" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A26)</f>
         <v/>
       </c>
-      <c r="C26" s="156">
+      <c r="C26" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A26)</f>
         <v/>
       </c>
@@ -6132,6 +6800,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H26" s="156" t="inlineStr">
+        <is>
+          <t>بازپرداخت تسهیلات</t>
+        </is>
+      </c>
+      <c r="I26" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J26" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K26" s="157" t="inlineStr"/>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="93" t="inlineStr">
@@ -6139,11 +6823,11 @@
           <t>فروشنده سبد</t>
         </is>
       </c>
-      <c r="B27" s="156">
+      <c r="B27" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A27)</f>
         <v/>
       </c>
-      <c r="C27" s="156">
+      <c r="C27" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A27)</f>
         <v/>
       </c>
@@ -6152,6 +6836,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H27" s="156" t="inlineStr">
+        <is>
+          <t>پاس چک مشتری برگشتی</t>
+        </is>
+      </c>
+      <c r="I27" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J27" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K27" s="157" t="inlineStr"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="93" t="inlineStr">
@@ -6159,11 +6859,11 @@
           <t>تأمین‌کننده</t>
         </is>
       </c>
-      <c r="B28" s="156">
+      <c r="B28" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A28)</f>
         <v/>
       </c>
-      <c r="C28" s="156">
+      <c r="C28" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A28)</f>
         <v/>
       </c>
@@ -6172,6 +6872,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H28" s="156" t="inlineStr">
+        <is>
+          <t>سایر پرداخت</t>
+        </is>
+      </c>
+      <c r="I28" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J28" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K28" s="157" t="inlineStr"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="93" t="inlineStr">
@@ -6179,17 +6895,37 @@
           <t>کارمند</t>
         </is>
       </c>
-      <c r="B29" s="156">
+      <c r="B29" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A29)</f>
         <v/>
       </c>
-      <c r="C29" s="156">
+      <c r="C29" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A29)</f>
         <v/>
       </c>
       <c r="F29" s="96" t="inlineStr">
         <is>
           <t>Accounts / Groups</t>
+        </is>
+      </c>
+      <c r="H29" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت به حساب شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="I29" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J29" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K29" s="157" t="inlineStr">
+        <is>
+          <t>X021</t>
         </is>
       </c>
     </row>
@@ -6199,17 +6935,37 @@
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="B30" s="156">
+      <c r="B30" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A30)</f>
         <v/>
       </c>
-      <c r="C30" s="156">
+      <c r="C30" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A30)</f>
         <v/>
       </c>
       <c r="F30" s="96" t="inlineStr">
         <is>
           <t>Accounts / Groups</t>
+        </is>
+      </c>
+      <c r="H30" s="156" t="inlineStr">
+        <is>
+          <t>دریافت از حساب شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="I30" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J30" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K30" s="157" t="inlineStr">
+        <is>
+          <t>X021</t>
         </is>
       </c>
     </row>
@@ -6219,11 +6975,11 @@
           <t>باسکول دیگران</t>
         </is>
       </c>
-      <c r="B31" s="156">
+      <c r="B31" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A31)</f>
         <v/>
       </c>
-      <c r="C31" s="156">
+      <c r="C31" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A31)</f>
         <v/>
       </c>
@@ -6232,6 +6988,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H31" s="156" t="inlineStr">
+        <is>
+          <t>انتقال داخلی بین بانک‌ها</t>
+        </is>
+      </c>
+      <c r="I31" s="157" t="inlineStr">
+        <is>
+          <t>TRF</t>
+        </is>
+      </c>
+      <c r="J31" s="157" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K31" s="157" t="inlineStr"/>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="93" t="inlineStr">
@@ -6239,17 +7011,37 @@
           <t>دارایی ثابت</t>
         </is>
       </c>
-      <c r="B32" s="156">
+      <c r="B32" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A32)</f>
         <v/>
       </c>
-      <c r="C32" s="156">
+      <c r="C32" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A32)</f>
         <v/>
       </c>
       <c r="F32" s="96" t="inlineStr">
         <is>
           <t>Accounts / Groups</t>
+        </is>
+      </c>
+      <c r="H32" s="156" t="inlineStr">
+        <is>
+          <t>تسویه دریافت (واسط)</t>
+        </is>
+      </c>
+      <c r="I32" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J32" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K32" s="157" t="inlineStr">
+        <is>
+          <t>X011</t>
         </is>
       </c>
     </row>
@@ -6259,17 +7051,37 @@
           <t>وام و تسهیلات</t>
         </is>
       </c>
-      <c r="B33" s="156">
+      <c r="B33" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A33)</f>
         <v/>
       </c>
-      <c r="C33" s="156">
+      <c r="C33" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A33)</f>
         <v/>
       </c>
       <c r="F33" s="96" t="inlineStr">
         <is>
           <t>Accounts / Groups</t>
+        </is>
+      </c>
+      <c r="H33" s="156" t="inlineStr">
+        <is>
+          <t>تسویه پرداخت (واسط)</t>
+        </is>
+      </c>
+      <c r="I33" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J33" s="157" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K33" s="157" t="inlineStr">
+        <is>
+          <t>X011</t>
         </is>
       </c>
     </row>
@@ -6279,11 +7091,11 @@
           <t>سرمایه و آورده صاحبان</t>
         </is>
       </c>
-      <c r="B34" s="156">
+      <c r="B34" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A34)</f>
         <v/>
       </c>
-      <c r="C34" s="156">
+      <c r="C34" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A34)</f>
         <v/>
       </c>
@@ -6299,11 +7111,11 @@
           <t>بانک و صندوق</t>
         </is>
       </c>
-      <c r="B35" s="156">
+      <c r="B35" s="158">
         <f>COUNTIF(Acc!$B$10:$B$259,$A35)</f>
         <v/>
       </c>
-      <c r="C35" s="156">
+      <c r="C35" s="158">
         <f>COUNTIF(Grp!$A$10:$A$52,$A35)</f>
         <v/>
       </c>
@@ -6670,7 +7482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF14453D"/>
@@ -6755,7 +7567,7 @@
           <t>۱</t>
         </is>
       </c>
-      <c r="B8" s="157" t="inlineStr">
+      <c r="B8" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  این فایل چیست و چرا «مادر» است؟</t>
         </is>
@@ -6767,7 +7579,7 @@
           <t>۲</t>
         </is>
       </c>
-      <c r="B9" s="157" t="inlineStr">
+      <c r="B9" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  نقشه فایل‌ها و جریان داده</t>
         </is>
@@ -6779,7 +7591,7 @@
           <t>۳</t>
         </is>
       </c>
-      <c r="B10" s="157" t="inlineStr">
+      <c r="B10" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  قواعد کدگذاری</t>
         </is>
@@ -6791,7 +7603,7 @@
           <t>۴</t>
         </is>
       </c>
-      <c r="B11" s="157" t="inlineStr">
+      <c r="B11" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  دفتر حساب‌ها (Accounts)</t>
         </is>
@@ -6803,7 +7615,7 @@
           <t>۵</t>
         </is>
       </c>
-      <c r="B12" s="157" t="inlineStr">
+      <c r="B12" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  گروه‌ها و زیرگروه‌ها</t>
         </is>
@@ -6815,7 +7627,7 @@
           <t>۶</t>
         </is>
       </c>
-      <c r="B13" s="157" t="inlineStr">
+      <c r="B13" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  عملیات و قواعد بدهکار/بستانکار</t>
         </is>
@@ -6827,7 +7639,7 @@
           <t>۷</t>
         </is>
       </c>
-      <c r="B14" s="157" t="inlineStr">
+      <c r="B14" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  پارامترهای محاسباتی</t>
         </is>
@@ -6839,7 +7651,7 @@
           <t>۸</t>
         </is>
       </c>
-      <c r="B15" s="157" t="inlineStr">
+      <c r="B15" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  سبدها و وزن تار</t>
         </is>
@@ -6851,7 +7663,7 @@
           <t>۹</t>
         </is>
       </c>
-      <c r="B16" s="157" t="inlineStr">
+      <c r="B16" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  محصولات، بانک‌ها و پوز</t>
         </is>
@@ -6863,7 +7675,7 @@
           <t>۱۰</t>
         </is>
       </c>
-      <c r="B17" s="157" t="inlineStr">
+      <c r="B17" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  افزودن حساب / عملیات جدید — گام‌به‌گام</t>
         </is>
@@ -6875,7 +7687,7 @@
           <t>۱۱</t>
         </is>
       </c>
-      <c r="B18" s="157" t="inlineStr">
+      <c r="B18" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  همگام‌سازی و Update Links</t>
         </is>
@@ -6887,7 +7699,7 @@
           <t>۱۲</t>
         </is>
       </c>
-      <c r="B19" s="157" t="inlineStr">
+      <c r="B19" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  ترازنامه، فاکتور و گزارش‌ها</t>
         </is>
@@ -6899,7 +7711,7 @@
           <t>۱۳</t>
         </is>
       </c>
-      <c r="B20" s="157" t="inlineStr">
+      <c r="B20" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  عیب‌یابی فرمول‌ها</t>
         </is>
@@ -6911,7 +7723,7 @@
           <t>۱۴</t>
         </is>
       </c>
-      <c r="B21" s="157" t="inlineStr">
+      <c r="B21" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  پشتیبان‌گیری و نگهداری</t>
         </is>
@@ -6923,7 +7735,7 @@
           <t>۱۵</t>
         </is>
       </c>
-      <c r="B22" s="157" t="inlineStr">
+      <c r="B22" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  واژه‌نامه</t>
         </is>
@@ -6935,7 +7747,7 @@
           <t>۱۶</t>
         </is>
       </c>
-      <c r="B23" s="157" t="inlineStr">
+      <c r="B23" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve">  قواعد طلایی</t>
         </is>
@@ -7770,56 +8582,56 @@
       <c r="J109" s="110" t="n"/>
     </row>
     <row r="110" ht="20.25" customHeight="1">
-      <c r="B110" s="158" t="inlineStr">
+      <c r="B110" s="160" t="inlineStr">
         <is>
           <t>•  کدها را تغییر ندهید؛ عنوان‌ها را آزادانه عوض کنید.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="20.25" customHeight="1">
-      <c r="B111" s="158" t="inlineStr">
+      <c r="B111" s="160" t="inlineStr">
         <is>
           <t>•  ردیف تازه = ردیف خالی بعدی؛ بین ردیف‌ها ردیف خالی نگذارید.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20.25" customHeight="1">
-      <c r="B112" s="158" t="inlineStr">
+      <c r="B112" s="160" t="inlineStr">
         <is>
           <t>•  برای حذف، محتوای سلول را پاک کنید؛ ردیف را حذف نکنید.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20.25" customHeight="1">
-      <c r="B113" s="158" t="inlineStr">
+      <c r="B113" s="160" t="inlineStr">
         <is>
           <t>•  همه فایل‌ها در یک پوشه؛ مسیر لینک نسبی است.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="20.25" customHeight="1">
-      <c r="B114" s="158" t="inlineStr">
+      <c r="B114" s="160" t="inlineStr">
         <is>
           <t>•  بعد از هر تغییر INFO: Data → Edit Links → Update Values.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="20.25" customHeight="1">
-      <c r="B115" s="158" t="inlineStr">
+      <c r="B115" s="160" t="inlineStr">
         <is>
           <t>•  تاریخ شمسی 1405/07/10؛ ساعت 09:30؛ اعداد با ارقام لاتین.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="20.25" customHeight="1">
-      <c r="B116" s="158" t="inlineStr">
+      <c r="B116" s="160" t="inlineStr">
         <is>
           <t>•  قبل از تغییرات بزرگ، نسخه پشتیبان بگیرید.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="20.25" customHeight="1">
-      <c r="B117" s="158" t="inlineStr">
+      <c r="B117" s="160" t="inlineStr">
         <is>
           <t>•  ترازنامه‌ای که تراز نیست، گزارش نیست؛ اول اختلاف را پیدا کنید.</t>
         </is>
@@ -7827,84 +8639,84 @@
     </row>
     <row r="118"/>
     <row r="119">
-      <c r="A119" s="159" t="inlineStr">
+      <c r="A119" s="161" t="inlineStr">
         <is>
           <t>۰۹   سری جدید (v03) — چه چیزهایی اضافه شد؟</t>
         </is>
       </c>
-      <c r="B119" s="166" t="n"/>
-      <c r="C119" s="166" t="n"/>
-      <c r="D119" s="166" t="n"/>
-      <c r="E119" s="166" t="n"/>
-      <c r="F119" s="166" t="n"/>
-      <c r="G119" s="166" t="n"/>
-      <c r="H119" s="166" t="n"/>
-      <c r="I119" s="166" t="n"/>
-      <c r="J119" s="167" t="n"/>
+      <c r="B119" s="154" t="n"/>
+      <c r="C119" s="154" t="n"/>
+      <c r="D119" s="154" t="n"/>
+      <c r="E119" s="154" t="n"/>
+      <c r="F119" s="154" t="n"/>
+      <c r="G119" s="154" t="n"/>
+      <c r="H119" s="154" t="n"/>
+      <c r="I119" s="154" t="n"/>
+      <c r="J119" s="155" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="160" t="inlineStr">
+      <c r="A120" s="162" t="inlineStr">
         <is>
           <t>• فایل تراکنش‌ها (02_Bank) بازنویسی شد: کشوی بانک عامل، کد طرف حساب تایپی، انتقال داخلی با بانک مبدأ و مقصد، دفتر چک و پنج شیت تحلیل با نمودار.</t>
         </is>
       </c>
-      <c r="B120" s="166" t="n"/>
-      <c r="C120" s="166" t="n"/>
-      <c r="D120" s="166" t="n"/>
-      <c r="E120" s="166" t="n"/>
-      <c r="F120" s="166" t="n"/>
-      <c r="G120" s="166" t="n"/>
-      <c r="H120" s="166" t="n"/>
-      <c r="I120" s="166" t="n"/>
-      <c r="J120" s="167" t="n"/>
+      <c r="B120" s="154" t="n"/>
+      <c r="C120" s="154" t="n"/>
+      <c r="D120" s="154" t="n"/>
+      <c r="E120" s="154" t="n"/>
+      <c r="F120" s="154" t="n"/>
+      <c r="G120" s="154" t="n"/>
+      <c r="H120" s="154" t="n"/>
+      <c r="I120" s="154" t="n"/>
+      <c r="J120" s="155" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="161" t="inlineStr">
+      <c r="A121" s="163" t="inlineStr">
         <is>
           <t>• داشبورد (08_Dash) اضافه شد: وزن، مبلغ، بانک‌ها، پز و طرف حساب‌ها در یک صفحه.</t>
         </is>
       </c>
-      <c r="B121" s="166" t="n"/>
-      <c r="C121" s="166" t="n"/>
-      <c r="D121" s="166" t="n"/>
-      <c r="E121" s="166" t="n"/>
-      <c r="F121" s="166" t="n"/>
-      <c r="G121" s="166" t="n"/>
-      <c r="H121" s="166" t="n"/>
-      <c r="I121" s="166" t="n"/>
-      <c r="J121" s="167" t="n"/>
+      <c r="B121" s="154" t="n"/>
+      <c r="C121" s="154" t="n"/>
+      <c r="D121" s="154" t="n"/>
+      <c r="E121" s="154" t="n"/>
+      <c r="F121" s="154" t="n"/>
+      <c r="G121" s="154" t="n"/>
+      <c r="H121" s="154" t="n"/>
+      <c r="I121" s="154" t="n"/>
+      <c r="J121" s="155" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="160" t="inlineStr">
+      <c r="A122" s="162" t="inlineStr">
         <is>
           <t>• همه فهرست‌های کشویی در همین فایل تعریف شده‌اند؛ شیت List ستون‌های S، T و U سه فهرست جدید است.</t>
         </is>
       </c>
-      <c r="B122" s="166" t="n"/>
-      <c r="C122" s="166" t="n"/>
-      <c r="D122" s="166" t="n"/>
-      <c r="E122" s="166" t="n"/>
-      <c r="F122" s="166" t="n"/>
-      <c r="G122" s="166" t="n"/>
-      <c r="H122" s="166" t="n"/>
-      <c r="I122" s="166" t="n"/>
-      <c r="J122" s="167" t="n"/>
+      <c r="B122" s="154" t="n"/>
+      <c r="C122" s="154" t="n"/>
+      <c r="D122" s="154" t="n"/>
+      <c r="E122" s="154" t="n"/>
+      <c r="F122" s="154" t="n"/>
+      <c r="G122" s="154" t="n"/>
+      <c r="H122" s="154" t="n"/>
+      <c r="I122" s="154" t="n"/>
+      <c r="J122" s="155" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="161" t="inlineStr">
+      <c r="A123" s="163" t="inlineStr">
         <is>
           <t>• همه شیت‌ها راست‌به‌چپ و آماده چاپ A4 هستند.</t>
         </is>
       </c>
-      <c r="B123" s="166" t="n"/>
-      <c r="C123" s="166" t="n"/>
-      <c r="D123" s="166" t="n"/>
-      <c r="E123" s="166" t="n"/>
-      <c r="F123" s="166" t="n"/>
-      <c r="G123" s="166" t="n"/>
-      <c r="H123" s="166" t="n"/>
-      <c r="I123" s="166" t="n"/>
-      <c r="J123" s="167" t="n"/>
+      <c r="B123" s="154" t="n"/>
+      <c r="C123" s="154" t="n"/>
+      <c r="D123" s="154" t="n"/>
+      <c r="E123" s="154" t="n"/>
+      <c r="F123" s="154" t="n"/>
+      <c r="G123" s="154" t="n"/>
+      <c r="H123" s="154" t="n"/>
+      <c r="I123" s="154" t="n"/>
+      <c r="J123" s="155" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="1" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -10537,7 +11349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P259"/>
+  <dimension ref="A1:P260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -10801,16 +11613,16 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="K9" s="162" t="inlineStr">
+      <c r="K9" s="173" t="inlineStr">
         <is>
           <t>راهنمای باسکول دیگران</t>
         </is>
       </c>
-      <c r="L9" s="163" t="n"/>
-      <c r="M9" s="163" t="n"/>
-      <c r="N9" s="163" t="n"/>
-      <c r="O9" s="163" t="n"/>
-      <c r="P9" s="164" t="n"/>
+      <c r="L9" s="174" t="n"/>
+      <c r="M9" s="174" t="n"/>
+      <c r="N9" s="174" t="n"/>
+      <c r="O9" s="174" t="n"/>
+      <c r="P9" s="175" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="63" t="inlineStr">
@@ -10861,7 +11673,7 @@
           <t>بله</t>
         </is>
       </c>
-      <c r="K10" s="165" t="inlineStr">
+      <c r="K10" s="176" t="inlineStr">
         <is>
           <t>این اشخاص، طرف حساب «باسکول دیگران» هستند: در فایل 02_Bank با نوع «دریافت/پرداخت باسکول دیگران» انتخاب می‌شوند و مانده بدهی هر کدام در شیت Payable همان فایل و در گزارش گروه‌ها (01_Entry ← GRep) دیده می‌شود. برای شخص جدید، نخستین کد خالی BD را پر کنید.</t>
         </is>
@@ -20028,6 +20840,43 @@
       <c r="M259">
         <f>IF(OR($B259="",$A259=""),"",IF(OR($B259=$K259,AND(LEFT($A259,1)="S",OR($B259="فروشنده سبد",$B259="تأمین‌کننده")),AND(LEFT($A259,2)="BD",$B259="باسکول دیگران")),"✓","⚠"))</f>
         <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="164" t="inlineStr">
+        <is>
+          <t>X021</t>
+        </is>
+      </c>
+      <c r="B260" s="164" t="inlineStr">
+        <is>
+          <t>سرمایه و آورده صاحبان</t>
+        </is>
+      </c>
+      <c r="C260" s="164" t="inlineStr">
+        <is>
+          <t>جاری شرکا</t>
+        </is>
+      </c>
+      <c r="D260" s="164" t="inlineStr">
+        <is>
+          <t>حساب جاری رئیس شرکت</t>
+        </is>
+      </c>
+      <c r="E260" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F260" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20121,6 +20970,1469 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   طبقه‌بندی تراکنش‌های بانکی — این پول برای چه کاری بود؟</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   هر ردیف یک زیرمجموعه است: خرید مرکبات، فروش مرکبات، قبض، حقوق، تعمیر و نگهداری دستگاه‌ها، و هزینه‌های شخصی رئیس. ستون «دامنه» مشخص می‌کند این پول شرکت است یا پول شخصی رئیس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="167" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="B8" s="167" t="inlineStr">
+        <is>
+          <t>عنوان طبقه‌بندی</t>
+        </is>
+      </c>
+      <c r="C8" s="167" t="inlineStr">
+        <is>
+          <t>دامنه</t>
+        </is>
+      </c>
+      <c r="D8" s="167" t="inlineStr">
+        <is>
+          <t>گروه حساب</t>
+        </is>
+      </c>
+      <c r="E8" s="167" t="inlineStr">
+        <is>
+          <t>توضیح</t>
+        </is>
+      </c>
+      <c r="F8" s="167" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="168" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B9" s="168" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C9" s="168" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D9" s="168" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="E9" s="168" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="F9" s="168" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="169" t="inlineStr">
+        <is>
+          <t>TC01</t>
+        </is>
+      </c>
+      <c r="B10" s="170" t="inlineStr">
+        <is>
+          <t>خرید مرکبات</t>
+        </is>
+      </c>
+      <c r="C10" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D10" s="169" t="inlineStr">
+        <is>
+          <t>باغدار</t>
+        </is>
+      </c>
+      <c r="E10" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F10" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="169" t="inlineStr">
+        <is>
+          <t>TC02</t>
+        </is>
+      </c>
+      <c r="B11" s="170" t="inlineStr">
+        <is>
+          <t>فروش مرکبات</t>
+        </is>
+      </c>
+      <c r="C11" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D11" s="169" t="inlineStr">
+        <is>
+          <t>بارفروش</t>
+        </is>
+      </c>
+      <c r="E11" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F11" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="169" t="inlineStr">
+        <is>
+          <t>TC03</t>
+        </is>
+      </c>
+      <c r="B12" s="170" t="inlineStr">
+        <is>
+          <t>واریز بارفروشان</t>
+        </is>
+      </c>
+      <c r="C12" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D12" s="169" t="inlineStr">
+        <is>
+          <t>بارفروش</t>
+        </is>
+      </c>
+      <c r="E12" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F12" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="169" t="inlineStr">
+        <is>
+          <t>TC04</t>
+        </is>
+      </c>
+      <c r="B13" s="170" t="inlineStr">
+        <is>
+          <t>دریافتی از مشتری</t>
+        </is>
+      </c>
+      <c r="C13" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D13" s="169" t="inlineStr">
+        <is>
+          <t>بارفروش</t>
+        </is>
+      </c>
+      <c r="E13" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F13" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="169" t="inlineStr">
+        <is>
+          <t>TC05</t>
+        </is>
+      </c>
+      <c r="B14" s="170" t="inlineStr">
+        <is>
+          <t>پرداخت به باغدار</t>
+        </is>
+      </c>
+      <c r="C14" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D14" s="169" t="inlineStr">
+        <is>
+          <t>باغدار</t>
+        </is>
+      </c>
+      <c r="E14" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F14" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="169" t="inlineStr">
+        <is>
+          <t>TC06</t>
+        </is>
+      </c>
+      <c r="B15" s="170" t="inlineStr">
+        <is>
+          <t>خرید سبد</t>
+        </is>
+      </c>
+      <c r="C15" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D15" s="169" t="inlineStr">
+        <is>
+          <t>فروشنده سبد</t>
+        </is>
+      </c>
+      <c r="E15" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F15" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="169" t="inlineStr">
+        <is>
+          <t>TC07</t>
+        </is>
+      </c>
+      <c r="B16" s="170" t="inlineStr">
+        <is>
+          <t>فروش سبد</t>
+        </is>
+      </c>
+      <c r="C16" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D16" s="169" t="inlineStr">
+        <is>
+          <t>فروشنده سبد</t>
+        </is>
+      </c>
+      <c r="E16" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F16" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="169" t="inlineStr">
+        <is>
+          <t>TC08</t>
+        </is>
+      </c>
+      <c r="B17" s="170" t="inlineStr">
+        <is>
+          <t>حمل و تخلیه</t>
+        </is>
+      </c>
+      <c r="C17" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D17" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E17" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F17" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="169" t="inlineStr">
+        <is>
+          <t>TC09</t>
+        </is>
+      </c>
+      <c r="B18" s="170" t="inlineStr">
+        <is>
+          <t>کارمزد بانکی</t>
+        </is>
+      </c>
+      <c r="C18" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D18" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E18" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F18" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="169" t="inlineStr">
+        <is>
+          <t>TC10</t>
+        </is>
+      </c>
+      <c r="B19" s="170" t="inlineStr">
+        <is>
+          <t>قبض آب، برق و گاز</t>
+        </is>
+      </c>
+      <c r="C19" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D19" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E19" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F19" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="169" t="inlineStr">
+        <is>
+          <t>TC11</t>
+        </is>
+      </c>
+      <c r="B20" s="170" t="inlineStr">
+        <is>
+          <t>حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="C20" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D20" s="169" t="inlineStr">
+        <is>
+          <t>کارمند</t>
+        </is>
+      </c>
+      <c r="E20" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F20" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="169" t="inlineStr">
+        <is>
+          <t>TC12</t>
+        </is>
+      </c>
+      <c r="B21" s="170" t="inlineStr">
+        <is>
+          <t>بیمه تأمین اجتماعی</t>
+        </is>
+      </c>
+      <c r="C21" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D21" s="169" t="inlineStr">
+        <is>
+          <t>کارمند</t>
+        </is>
+      </c>
+      <c r="E21" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F21" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="169" t="inlineStr">
+        <is>
+          <t>TC13</t>
+        </is>
+      </c>
+      <c r="B22" s="170" t="inlineStr">
+        <is>
+          <t>تعمیر و نگهداری دستگاه سورتینگ</t>
+        </is>
+      </c>
+      <c r="C22" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D22" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E22" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F22" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="169" t="inlineStr">
+        <is>
+          <t>TC14</t>
+        </is>
+      </c>
+      <c r="B23" s="170" t="inlineStr">
+        <is>
+          <t>تعمیر و نگهداری خط بسته‌بندی</t>
+        </is>
+      </c>
+      <c r="C23" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D23" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E23" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F23" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="169" t="inlineStr">
+        <is>
+          <t>TC15</t>
+        </is>
+      </c>
+      <c r="B24" s="170" t="inlineStr">
+        <is>
+          <t>تعمیر و نگهداری سردخانه</t>
+        </is>
+      </c>
+      <c r="C24" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D24" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E24" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F24" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="169" t="inlineStr">
+        <is>
+          <t>TC16</t>
+        </is>
+      </c>
+      <c r="B25" s="170" t="inlineStr">
+        <is>
+          <t>قطعات و لوازم یدکی</t>
+        </is>
+      </c>
+      <c r="C25" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D25" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E25" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F25" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="169" t="inlineStr">
+        <is>
+          <t>TC17</t>
+        </is>
+      </c>
+      <c r="B26" s="170" t="inlineStr">
+        <is>
+          <t>سوخت و انرژی</t>
+        </is>
+      </c>
+      <c r="C26" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D26" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E26" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F26" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="169" t="inlineStr">
+        <is>
+          <t>TC18</t>
+        </is>
+      </c>
+      <c r="B27" s="170" t="inlineStr">
+        <is>
+          <t>اجاره انبار و زمین</t>
+        </is>
+      </c>
+      <c r="C27" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D27" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E27" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F27" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="169" t="inlineStr">
+        <is>
+          <t>TC19</t>
+        </is>
+      </c>
+      <c r="B28" s="170" t="inlineStr">
+        <is>
+          <t>انعام مصطفی</t>
+        </is>
+      </c>
+      <c r="C28" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D28" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E28" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F28" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="169" t="inlineStr">
+        <is>
+          <t>TC20</t>
+        </is>
+      </c>
+      <c r="B29" s="170" t="inlineStr">
+        <is>
+          <t>هزینه باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="C29" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D29" s="169" t="inlineStr">
+        <is>
+          <t>باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="E29" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F29" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="169" t="inlineStr">
+        <is>
+          <t>TC21</t>
+        </is>
+      </c>
+      <c r="B30" s="170" t="inlineStr">
+        <is>
+          <t>تسویه باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="C30" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D30" s="169" t="inlineStr">
+        <is>
+          <t>باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="E30" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F30" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="169" t="inlineStr">
+        <is>
+          <t>TC22</t>
+        </is>
+      </c>
+      <c r="B31" s="170" t="inlineStr">
+        <is>
+          <t>اقساط و تسهیلات</t>
+        </is>
+      </c>
+      <c r="C31" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D31" s="169" t="inlineStr">
+        <is>
+          <t>وام و تسهیلات</t>
+        </is>
+      </c>
+      <c r="E31" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F31" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="169" t="inlineStr">
+        <is>
+          <t>TC23</t>
+        </is>
+      </c>
+      <c r="B32" s="170" t="inlineStr">
+        <is>
+          <t>دریافت تسهیلات</t>
+        </is>
+      </c>
+      <c r="C32" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D32" s="169" t="inlineStr">
+        <is>
+          <t>وام و تسهیلات</t>
+        </is>
+      </c>
+      <c r="E32" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F32" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="169" t="inlineStr">
+        <is>
+          <t>TC24</t>
+        </is>
+      </c>
+      <c r="B33" s="170" t="inlineStr">
+        <is>
+          <t>مالیات و عوارض</t>
+        </is>
+      </c>
+      <c r="C33" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D33" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E33" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F33" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="169" t="inlineStr">
+        <is>
+          <t>TC25</t>
+        </is>
+      </c>
+      <c r="B34" s="170" t="inlineStr">
+        <is>
+          <t>سرمایه و آورده صاحبان</t>
+        </is>
+      </c>
+      <c r="C34" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D34" s="169" t="inlineStr">
+        <is>
+          <t>سرمایه و آورده صاحبان</t>
+        </is>
+      </c>
+      <c r="E34" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F34" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="169" t="inlineStr">
+        <is>
+          <t>TC26</t>
+        </is>
+      </c>
+      <c r="B35" s="170" t="inlineStr">
+        <is>
+          <t>انتقال بین حساب‌های شرکت</t>
+        </is>
+      </c>
+      <c r="C35" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D35" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E35" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F35" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="169" t="inlineStr">
+        <is>
+          <t>TC27</t>
+        </is>
+      </c>
+      <c r="B36" s="170" t="inlineStr">
+        <is>
+          <t>سایر درآمد</t>
+        </is>
+      </c>
+      <c r="C36" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D36" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E36" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F36" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="169" t="inlineStr">
+        <is>
+          <t>TC28</t>
+        </is>
+      </c>
+      <c r="B37" s="170" t="inlineStr">
+        <is>
+          <t>سایر هزینه</t>
+        </is>
+      </c>
+      <c r="C37" s="169" t="inlineStr">
+        <is>
+          <t>شرکتی</t>
+        </is>
+      </c>
+      <c r="D37" s="169" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E37" s="169" t="inlineStr">
+        <is>
+          <t>هزینه/درآمد شرکت</t>
+        </is>
+      </c>
+      <c r="F37" s="169" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="171" t="inlineStr">
+        <is>
+          <t>TC29</t>
+        </is>
+      </c>
+      <c r="B38" s="172" t="inlineStr">
+        <is>
+          <t>هزینه شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="C38" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D38" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E38" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F38" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="171" t="inlineStr">
+        <is>
+          <t>TC30</t>
+        </is>
+      </c>
+      <c r="B39" s="172" t="inlineStr">
+        <is>
+          <t>خرید وسایل شخصی</t>
+        </is>
+      </c>
+      <c r="C39" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D39" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E39" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F39" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="171" t="inlineStr">
+        <is>
+          <t>TC31</t>
+        </is>
+      </c>
+      <c r="B40" s="172" t="inlineStr">
+        <is>
+          <t>فروش وسایل شخصی</t>
+        </is>
+      </c>
+      <c r="C40" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D40" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E40" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F40" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="171" t="inlineStr">
+        <is>
+          <t>TC32</t>
+        </is>
+      </c>
+      <c r="B41" s="172" t="inlineStr">
+        <is>
+          <t>خرید خودرو</t>
+        </is>
+      </c>
+      <c r="C41" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D41" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E41" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F41" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="171" t="inlineStr">
+        <is>
+          <t>TC33</t>
+        </is>
+      </c>
+      <c r="B42" s="172" t="inlineStr">
+        <is>
+          <t>فروش خودرو</t>
+        </is>
+      </c>
+      <c r="C42" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D42" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E42" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F42" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="171" t="inlineStr">
+        <is>
+          <t>TC34</t>
+        </is>
+      </c>
+      <c r="B43" s="172" t="inlineStr">
+        <is>
+          <t>سوخت و تعمیر خودرو شخصی</t>
+        </is>
+      </c>
+      <c r="C43" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D43" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E43" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F43" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="171" t="inlineStr">
+        <is>
+          <t>TC35</t>
+        </is>
+      </c>
+      <c r="B44" s="172" t="inlineStr">
+        <is>
+          <t>مسکن و قبض منزل</t>
+        </is>
+      </c>
+      <c r="C44" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D44" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E44" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F44" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="171" t="inlineStr">
+        <is>
+          <t>TC36</t>
+        </is>
+      </c>
+      <c r="B45" s="172" t="inlineStr">
+        <is>
+          <t>درمان و سلامت</t>
+        </is>
+      </c>
+      <c r="C45" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D45" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E45" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F45" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="171" t="inlineStr">
+        <is>
+          <t>TC37</t>
+        </is>
+      </c>
+      <c r="B46" s="172" t="inlineStr">
+        <is>
+          <t>تحصیل و آموزش</t>
+        </is>
+      </c>
+      <c r="C46" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D46" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E46" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F46" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="171" t="inlineStr">
+        <is>
+          <t>TC38</t>
+        </is>
+      </c>
+      <c r="B47" s="172" t="inlineStr">
+        <is>
+          <t>سفر و تفریح</t>
+        </is>
+      </c>
+      <c r="C47" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D47" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E47" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F47" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="171" t="inlineStr">
+        <is>
+          <t>TC39</t>
+        </is>
+      </c>
+      <c r="B48" s="172" t="inlineStr">
+        <is>
+          <t>هدیه و نذورات</t>
+        </is>
+      </c>
+      <c r="C48" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D48" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E48" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F48" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="171" t="inlineStr">
+        <is>
+          <t>TC40</t>
+        </is>
+      </c>
+      <c r="B49" s="172" t="inlineStr">
+        <is>
+          <t>دریافتی شخصی</t>
+        </is>
+      </c>
+      <c r="C49" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D49" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E49" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F49" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="171" t="inlineStr">
+        <is>
+          <t>TC41</t>
+        </is>
+      </c>
+      <c r="B50" s="172" t="inlineStr">
+        <is>
+          <t>واریز از حساب شرکت به شخصی</t>
+        </is>
+      </c>
+      <c r="C50" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D50" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E50" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F50" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="171" t="inlineStr">
+        <is>
+          <t>TC42</t>
+        </is>
+      </c>
+      <c r="B51" s="172" t="inlineStr">
+        <is>
+          <t>برگشت وجه شخصی به شرکت</t>
+        </is>
+      </c>
+      <c r="C51" s="171" t="inlineStr">
+        <is>
+          <t>شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D51" s="171" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="E51" s="171" t="inlineStr">
+        <is>
+          <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
+        </is>
+      </c>
+      <c r="F51" s="171" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 مازندشت — فایل مادر&amp;C&amp;8 MAZANDASHT · CLASSIFICATION&amp;R&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;F&amp;C&amp;8 صفحه &amp;P از &amp;N&amp;R&amp;8 نسخه ۰۴ · ۱۴۰۵</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFC4623F"/>
@@ -22407,7 +24719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF6B4E9E"/>
@@ -23094,7 +25406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFE0A458"/>
@@ -23894,510 +26206,4 @@
   </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF2E6B4F"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11.7109375" customWidth="1" min="1" max="1"/>
-    <col width="34.7109375" customWidth="1" min="2" max="2"/>
-    <col width="16.7109375" customWidth="1" min="3" max="3"/>
-    <col width="22.7109375" customWidth="1" min="4" max="4"/>
-    <col width="26.7109375" customWidth="1" min="5" max="5"/>
-    <col width="8.7109375" customWidth="1" min="6" max="6"/>
-    <col width="38.7109375" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" s="138" t="inlineStr">
-        <is>
-          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
-        </is>
-      </c>
-      <c r="C1" s="132" t="inlineStr">
-        <is>
-          <t>MAZANDASHT  ·  CITRUS SORTING &amp; PACKING</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38.25" customHeight="1">
-      <c r="A2" s="133" t="inlineStr">
-        <is>
-          <t>بانک‌ها و حساب‌های شرکت</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45.75" customHeight="1">
-      <c r="A3" s="134" t="inlineStr">
-        <is>
-          <t>کد بانک ثابت است؛ عنوان را آزادانه عوض کنید  ·  پوز باسکول به صادرات ۲۰۰۶ وصل است</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>راهنما</t>
-        </is>
-      </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>ورود دستی</t>
-        </is>
-      </c>
-      <c r="C4" s="36" t="inlineStr">
-        <is>
-          <t>خودکار</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="inlineStr">
-        <is>
-          <t>ورود</t>
-        </is>
-      </c>
-      <c r="E4" s="38" t="inlineStr">
-        <is>
-          <t>خروج</t>
-        </is>
-      </c>
-      <c r="F4" s="50" t="inlineStr">
-        <is>
-          <t>هشدار</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>بانک‌ها</t>
-        </is>
-      </c>
-      <c r="B5" s="140" t="n"/>
-      <c r="C5" s="108" t="n"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>بانک فعال</t>
-        </is>
-      </c>
-      <c r="E5" s="140" t="n"/>
-      <c r="F5" s="108" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>مانده اولیه</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="52">
-        <f>COUNTIF($A$10:$A$19,"?*")</f>
-        <v/>
-      </c>
-      <c r="B6" s="141" t="n"/>
-      <c r="C6" s="109" t="n"/>
-      <c r="D6" s="53">
-        <f>COUNTIF($F$10:$F$19,"بله")</f>
-        <v/>
-      </c>
-      <c r="E6" s="141" t="n"/>
-      <c r="F6" s="109" t="n"/>
-      <c r="G6" s="53">
-        <f>SUM($C$10:$C$19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="6.75" customHeight="1"/>
-    <row r="8" ht="33.75" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
-        <is>
-          <t>کد بانک</t>
-        </is>
-      </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>عنوان نمایشی</t>
-        </is>
-      </c>
-      <c r="C8" s="42" t="inlineStr">
-        <is>
-          <t>مانده اولیه</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>کد حساب معین</t>
-        </is>
-      </c>
-      <c r="E8" s="42" t="inlineStr">
-        <is>
-          <t>شبا</t>
-        </is>
-      </c>
-      <c r="F8" s="42" t="inlineStr">
-        <is>
-          <t>فعال</t>
-        </is>
-      </c>
-      <c r="G8" s="42" t="inlineStr">
-        <is>
-          <t>توضیح</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
-        <is>
-          <t>Ledger</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>IBAN</t>
-        </is>
-      </c>
-      <c r="F9" s="43" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G9" s="43" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>BN01</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>صادرات ۹۰۰۹ — جاری اصلی</t>
-        </is>
-      </c>
-      <c r="C10" s="46" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="D10" s="58" t="inlineStr">
-        <is>
-          <t>BN01</t>
-        </is>
-      </c>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>حساب جاری اصلی شرکت</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>BN02</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="inlineStr">
-        <is>
-          <t>صادرات ۲۰۰۶ — پوز باسکول</t>
-        </is>
-      </c>
-      <c r="C11" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="58" t="inlineStr">
-        <is>
-          <t>BN02</t>
-        </is>
-      </c>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G11" s="60" t="inlineStr">
-        <is>
-          <t>پوز باسکول به این حساب وصل است</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>BN03</t>
-        </is>
-      </c>
-      <c r="B12" s="45" t="inlineStr">
-        <is>
-          <t>ملت</t>
-        </is>
-      </c>
-      <c r="C12" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="58" t="inlineStr">
-        <is>
-          <t>BN03</t>
-        </is>
-      </c>
-      <c r="E12" s="59" t="n"/>
-      <c r="F12" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G12" s="60" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>BN04</t>
-        </is>
-      </c>
-      <c r="B13" s="45" t="inlineStr">
-        <is>
-          <t>کشاورزی</t>
-        </is>
-      </c>
-      <c r="C13" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="58" t="inlineStr">
-        <is>
-          <t>BN04</t>
-        </is>
-      </c>
-      <c r="E13" s="59" t="n"/>
-      <c r="F13" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G13" s="60" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>BN05</t>
-        </is>
-      </c>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>سپه</t>
-        </is>
-      </c>
-      <c r="C14" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="58" t="inlineStr">
-        <is>
-          <t>BN05</t>
-        </is>
-      </c>
-      <c r="E14" s="59" t="n"/>
-      <c r="F14" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G14" s="60" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>BN06</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="inlineStr">
-        <is>
-          <t>مهر ایران</t>
-        </is>
-      </c>
-      <c r="C15" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="58" t="inlineStr">
-        <is>
-          <t>BN06</t>
-        </is>
-      </c>
-      <c r="E15" s="59" t="n"/>
-      <c r="F15" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G15" s="60" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>BN07</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>تجارت</t>
-        </is>
-      </c>
-      <c r="C16" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="58" t="inlineStr">
-        <is>
-          <t>BN07</t>
-        </is>
-      </c>
-      <c r="E16" s="59" t="n"/>
-      <c r="F16" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G16" s="60" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>BN08</t>
-        </is>
-      </c>
-      <c r="B17" s="45" t="inlineStr">
-        <is>
-          <t>پاسارگاد</t>
-        </is>
-      </c>
-      <c r="C17" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="58" t="inlineStr">
-        <is>
-          <t>BN08</t>
-        </is>
-      </c>
-      <c r="E17" s="59" t="n"/>
-      <c r="F17" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G17" s="60" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>BN09</t>
-        </is>
-      </c>
-      <c r="B18" s="45" t="inlineStr">
-        <is>
-          <t>رفاه</t>
-        </is>
-      </c>
-      <c r="C18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="58" t="inlineStr">
-        <is>
-          <t>BN09</t>
-        </is>
-      </c>
-      <c r="E18" s="59" t="n"/>
-      <c r="F18" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G18" s="60" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>BN10</t>
-        </is>
-      </c>
-      <c r="B19" s="45" t="inlineStr">
-        <is>
-          <t>قرض‌الحسنه</t>
-        </is>
-      </c>
-      <c r="C19" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="58" t="inlineStr">
-        <is>
-          <t>BN10</t>
-        </is>
-      </c>
-      <c r="E19" s="59" t="n"/>
-      <c r="F19" s="47" t="inlineStr">
-        <is>
-          <t>بله</t>
-        </is>
-      </c>
-      <c r="G19" s="60" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A8:G20"/>
-  <mergeCells count="8">
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D6:F6"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B10:B20">
-    <cfRule type="expression" priority="1" dxfId="30">
-      <formula>LEFT($A10,6)="BANK02"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="F10:F20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>ListYesNo</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.28" right="0.28" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;Lمازندشت&amp;RMAZANDASHT · CITRUS</oddHeader>
-    <oddFooter>&amp;Lمازندشت — سورتینگ و بسته‌بندی مرکبات&amp;Cصفحه &amp;P از &amp;N&amp;RMAZANDASHT · 1405</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -70,7 +70,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Acc'!$8:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Acc'!$A$1:$M$260</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cls'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cls'!$A$1:$F$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cls'!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Op'!$A$8:$S$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Op'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Op'!$A$1:$S$35</definedName>
@@ -20979,11 +20979,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -20996,7 +20997,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="166" t="inlineStr">
         <is>
-          <t xml:space="preserve">   هر ردیف یک زیرمجموعه است: خرید مرکبات، فروش مرکبات، قبض، حقوق، تعمیر و نگهداری دستگاه‌ها، و هزینه‌های شخصی رئیس. ستون «دامنه» مشخص می‌کند این پول شرکت است یا پول شخصی رئیس.</t>
+          <t xml:space="preserve">   دو ستون اول، کشوی دوستونی شیت Txn را می‌سازد: «طبقه» (کشوی اول) و «زیرطبقه» (کشوی دوم) — بعد از انتخاب طبقه، فقط زیرطبقه‌های همان طبقه نشان داده می‌شود. ستون «دامنه» می‌گوید این پول شرکت است یا پول شخصی رئیس.</t>
         </is>
       </c>
     </row>
@@ -21013,25 +21014,30 @@
       </c>
       <c r="B8" s="167" t="inlineStr">
         <is>
-          <t>عنوان طبقه‌بندی</t>
+          <t>طبقه (کشوی اول)</t>
         </is>
       </c>
       <c r="C8" s="167" t="inlineStr">
         <is>
+          <t>زیرطبقه (کشوی دوم)</t>
+        </is>
+      </c>
+      <c r="D8" s="167" t="inlineStr">
+        <is>
           <t>دامنه</t>
         </is>
       </c>
-      <c r="D8" s="167" t="inlineStr">
+      <c r="E8" s="167" t="inlineStr">
         <is>
           <t>گروه حساب</t>
         </is>
       </c>
-      <c r="E8" s="167" t="inlineStr">
+      <c r="F8" s="167" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
-      <c r="F8" s="167" t="inlineStr">
+      <c r="G8" s="167" t="inlineStr">
         <is>
           <t>فعال</t>
         </is>
@@ -21045,25 +21051,30 @@
       </c>
       <c r="B9" s="168" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C9" s="168" t="inlineStr">
         <is>
+          <t>Sub-category</t>
+        </is>
+      </c>
+      <c r="D9" s="168" t="inlineStr">
+        <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D9" s="168" t="inlineStr">
+      <c r="E9" s="168" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="E9" s="168" t="inlineStr">
+      <c r="F9" s="168" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="F9" s="168" t="inlineStr">
+      <c r="G9" s="168" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -21077,25 +21088,30 @@
       </c>
       <c r="B10" s="170" t="inlineStr">
         <is>
+          <t>خرید و فروش مرکبات</t>
+        </is>
+      </c>
+      <c r="C10" s="170" t="inlineStr">
+        <is>
           <t>خرید مرکبات</t>
         </is>
       </c>
-      <c r="C10" s="169" t="inlineStr">
+      <c r="D10" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D10" s="169" t="inlineStr">
+      <c r="E10" s="169" t="inlineStr">
         <is>
           <t>باغدار</t>
         </is>
       </c>
-      <c r="E10" s="169" t="inlineStr">
+      <c r="F10" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F10" s="169" t="inlineStr">
+      <c r="G10" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21109,25 +21125,30 @@
       </c>
       <c r="B11" s="170" t="inlineStr">
         <is>
+          <t>خرید و فروش مرکبات</t>
+        </is>
+      </c>
+      <c r="C11" s="170" t="inlineStr">
+        <is>
           <t>فروش مرکبات</t>
         </is>
       </c>
-      <c r="C11" s="169" t="inlineStr">
+      <c r="D11" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D11" s="169" t="inlineStr">
+      <c r="E11" s="169" t="inlineStr">
         <is>
           <t>بارفروش</t>
         </is>
       </c>
-      <c r="E11" s="169" t="inlineStr">
+      <c r="F11" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F11" s="169" t="inlineStr">
+      <c r="G11" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21141,25 +21162,30 @@
       </c>
       <c r="B12" s="170" t="inlineStr">
         <is>
+          <t>خرید و فروش مرکبات</t>
+        </is>
+      </c>
+      <c r="C12" s="170" t="inlineStr">
+        <is>
           <t>واریز بارفروشان</t>
         </is>
       </c>
-      <c r="C12" s="169" t="inlineStr">
+      <c r="D12" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D12" s="169" t="inlineStr">
+      <c r="E12" s="169" t="inlineStr">
         <is>
           <t>بارفروش</t>
         </is>
       </c>
-      <c r="E12" s="169" t="inlineStr">
+      <c r="F12" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F12" s="169" t="inlineStr">
+      <c r="G12" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21173,25 +21199,30 @@
       </c>
       <c r="B13" s="170" t="inlineStr">
         <is>
+          <t>خرید و فروش مرکبات</t>
+        </is>
+      </c>
+      <c r="C13" s="170" t="inlineStr">
+        <is>
           <t>دریافتی از مشتری</t>
         </is>
       </c>
-      <c r="C13" s="169" t="inlineStr">
+      <c r="D13" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D13" s="169" t="inlineStr">
+      <c r="E13" s="169" t="inlineStr">
         <is>
           <t>بارفروش</t>
         </is>
       </c>
-      <c r="E13" s="169" t="inlineStr">
+      <c r="F13" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F13" s="169" t="inlineStr">
+      <c r="G13" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21205,25 +21236,30 @@
       </c>
       <c r="B14" s="170" t="inlineStr">
         <is>
+          <t>خرید و فروش مرکبات</t>
+        </is>
+      </c>
+      <c r="C14" s="170" t="inlineStr">
+        <is>
           <t>پرداخت به باغدار</t>
         </is>
       </c>
-      <c r="C14" s="169" t="inlineStr">
+      <c r="D14" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D14" s="169" t="inlineStr">
+      <c r="E14" s="169" t="inlineStr">
         <is>
           <t>باغدار</t>
         </is>
       </c>
-      <c r="E14" s="169" t="inlineStr">
+      <c r="F14" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F14" s="169" t="inlineStr">
+      <c r="G14" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21237,25 +21273,30 @@
       </c>
       <c r="B15" s="170" t="inlineStr">
         <is>
+          <t>سبد و بسته‌بندی</t>
+        </is>
+      </c>
+      <c r="C15" s="170" t="inlineStr">
+        <is>
           <t>خرید سبد</t>
         </is>
       </c>
-      <c r="C15" s="169" t="inlineStr">
+      <c r="D15" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D15" s="169" t="inlineStr">
+      <c r="E15" s="169" t="inlineStr">
         <is>
           <t>فروشنده سبد</t>
         </is>
       </c>
-      <c r="E15" s="169" t="inlineStr">
+      <c r="F15" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F15" s="169" t="inlineStr">
+      <c r="G15" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21269,25 +21310,30 @@
       </c>
       <c r="B16" s="170" t="inlineStr">
         <is>
+          <t>سبد و بسته‌بندی</t>
+        </is>
+      </c>
+      <c r="C16" s="170" t="inlineStr">
+        <is>
           <t>فروش سبد</t>
         </is>
       </c>
-      <c r="C16" s="169" t="inlineStr">
+      <c r="D16" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D16" s="169" t="inlineStr">
+      <c r="E16" s="169" t="inlineStr">
         <is>
           <t>فروشنده سبد</t>
         </is>
       </c>
-      <c r="E16" s="169" t="inlineStr">
+      <c r="F16" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F16" s="169" t="inlineStr">
+      <c r="G16" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21296,30 +21342,35 @@
     <row r="17">
       <c r="A17" s="169" t="inlineStr">
         <is>
-          <t>TC08</t>
+          <t>TC16</t>
         </is>
       </c>
       <c r="B17" s="170" t="inlineStr">
         <is>
-          <t>حمل و تخلیه</t>
-        </is>
-      </c>
-      <c r="C17" s="169" t="inlineStr">
+          <t>سبد و بسته‌بندی</t>
+        </is>
+      </c>
+      <c r="C17" s="170" t="inlineStr">
+        <is>
+          <t>قطعات و لوازم یدکی</t>
+        </is>
+      </c>
+      <c r="D17" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D17" s="169" t="inlineStr">
+      <c r="E17" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E17" s="169" t="inlineStr">
+      <c r="F17" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F17" s="169" t="inlineStr">
+      <c r="G17" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21328,30 +21379,35 @@
     <row r="18">
       <c r="A18" s="169" t="inlineStr">
         <is>
-          <t>TC09</t>
+          <t>TC08</t>
         </is>
       </c>
       <c r="B18" s="170" t="inlineStr">
         <is>
-          <t>کارمزد بانکی</t>
-        </is>
-      </c>
-      <c r="C18" s="169" t="inlineStr">
+          <t>هزینه جاری</t>
+        </is>
+      </c>
+      <c r="C18" s="170" t="inlineStr">
+        <is>
+          <t>حمل و تخلیه</t>
+        </is>
+      </c>
+      <c r="D18" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D18" s="169" t="inlineStr">
+      <c r="E18" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E18" s="169" t="inlineStr">
+      <c r="F18" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F18" s="169" t="inlineStr">
+      <c r="G18" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21360,30 +21416,35 @@
     <row r="19">
       <c r="A19" s="169" t="inlineStr">
         <is>
-          <t>TC10</t>
+          <t>TC09</t>
         </is>
       </c>
       <c r="B19" s="170" t="inlineStr">
         <is>
-          <t>قبض آب، برق و گاز</t>
-        </is>
-      </c>
-      <c r="C19" s="169" t="inlineStr">
+          <t>هزینه جاری</t>
+        </is>
+      </c>
+      <c r="C19" s="170" t="inlineStr">
+        <is>
+          <t>کارمزد بانکی</t>
+        </is>
+      </c>
+      <c r="D19" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D19" s="169" t="inlineStr">
+      <c r="E19" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E19" s="169" t="inlineStr">
+      <c r="F19" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F19" s="169" t="inlineStr">
+      <c r="G19" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21392,30 +21453,35 @@
     <row r="20">
       <c r="A20" s="169" t="inlineStr">
         <is>
-          <t>TC11</t>
+          <t>TC10</t>
         </is>
       </c>
       <c r="B20" s="170" t="inlineStr">
         <is>
-          <t>حقوق و دستمزد</t>
-        </is>
-      </c>
-      <c r="C20" s="169" t="inlineStr">
+          <t>هزینه جاری</t>
+        </is>
+      </c>
+      <c r="C20" s="170" t="inlineStr">
+        <is>
+          <t>قبض آب، برق و گاز</t>
+        </is>
+      </c>
+      <c r="D20" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D20" s="169" t="inlineStr">
-        <is>
-          <t>کارمند</t>
-        </is>
-      </c>
       <c r="E20" s="169" t="inlineStr">
         <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="F20" s="169" t="inlineStr">
+        <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F20" s="169" t="inlineStr">
+      <c r="G20" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21424,30 +21490,35 @@
     <row r="21">
       <c r="A21" s="169" t="inlineStr">
         <is>
-          <t>TC12</t>
+          <t>TC17</t>
         </is>
       </c>
       <c r="B21" s="170" t="inlineStr">
         <is>
-          <t>بیمه تأمین اجتماعی</t>
-        </is>
-      </c>
-      <c r="C21" s="169" t="inlineStr">
+          <t>هزینه جاری</t>
+        </is>
+      </c>
+      <c r="C21" s="170" t="inlineStr">
+        <is>
+          <t>سوخت و انرژی</t>
+        </is>
+      </c>
+      <c r="D21" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D21" s="169" t="inlineStr">
-        <is>
-          <t>کارمند</t>
-        </is>
-      </c>
       <c r="E21" s="169" t="inlineStr">
         <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="F21" s="169" t="inlineStr">
+        <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F21" s="169" t="inlineStr">
+      <c r="G21" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21456,30 +21527,35 @@
     <row r="22">
       <c r="A22" s="169" t="inlineStr">
         <is>
-          <t>TC13</t>
+          <t>TC18</t>
         </is>
       </c>
       <c r="B22" s="170" t="inlineStr">
         <is>
-          <t>تعمیر و نگهداری دستگاه سورتینگ</t>
-        </is>
-      </c>
-      <c r="C22" s="169" t="inlineStr">
+          <t>هزینه جاری</t>
+        </is>
+      </c>
+      <c r="C22" s="170" t="inlineStr">
+        <is>
+          <t>اجاره انبار و زمین</t>
+        </is>
+      </c>
+      <c r="D22" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D22" s="169" t="inlineStr">
+      <c r="E22" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E22" s="169" t="inlineStr">
+      <c r="F22" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F22" s="169" t="inlineStr">
+      <c r="G22" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21488,30 +21564,35 @@
     <row r="23">
       <c r="A23" s="169" t="inlineStr">
         <is>
-          <t>TC14</t>
+          <t>TC24</t>
         </is>
       </c>
       <c r="B23" s="170" t="inlineStr">
         <is>
-          <t>تعمیر و نگهداری خط بسته‌بندی</t>
-        </is>
-      </c>
-      <c r="C23" s="169" t="inlineStr">
+          <t>هزینه جاری</t>
+        </is>
+      </c>
+      <c r="C23" s="170" t="inlineStr">
+        <is>
+          <t>مالیات و عوارض</t>
+        </is>
+      </c>
+      <c r="D23" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D23" s="169" t="inlineStr">
+      <c r="E23" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E23" s="169" t="inlineStr">
+      <c r="F23" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F23" s="169" t="inlineStr">
+      <c r="G23" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21520,30 +21601,35 @@
     <row r="24">
       <c r="A24" s="169" t="inlineStr">
         <is>
-          <t>TC15</t>
+          <t>TC11</t>
         </is>
       </c>
       <c r="B24" s="170" t="inlineStr">
         <is>
-          <t>تعمیر و نگهداری سردخانه</t>
-        </is>
-      </c>
-      <c r="C24" s="169" t="inlineStr">
+          <t>نیروی انسانی</t>
+        </is>
+      </c>
+      <c r="C24" s="170" t="inlineStr">
+        <is>
+          <t>حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="D24" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D24" s="169" t="inlineStr">
-        <is>
-          <t>سایر حساب</t>
-        </is>
-      </c>
       <c r="E24" s="169" t="inlineStr">
         <is>
+          <t>کارمند</t>
+        </is>
+      </c>
+      <c r="F24" s="169" t="inlineStr">
+        <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F24" s="169" t="inlineStr">
+      <c r="G24" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21552,30 +21638,35 @@
     <row r="25">
       <c r="A25" s="169" t="inlineStr">
         <is>
-          <t>TC16</t>
+          <t>TC12</t>
         </is>
       </c>
       <c r="B25" s="170" t="inlineStr">
         <is>
-          <t>قطعات و لوازم یدکی</t>
-        </is>
-      </c>
-      <c r="C25" s="169" t="inlineStr">
+          <t>نیروی انسانی</t>
+        </is>
+      </c>
+      <c r="C25" s="170" t="inlineStr">
+        <is>
+          <t>بیمه تأمین اجتماعی</t>
+        </is>
+      </c>
+      <c r="D25" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D25" s="169" t="inlineStr">
-        <is>
-          <t>سایر حساب</t>
-        </is>
-      </c>
       <c r="E25" s="169" t="inlineStr">
         <is>
+          <t>کارمند</t>
+        </is>
+      </c>
+      <c r="F25" s="169" t="inlineStr">
+        <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F25" s="169" t="inlineStr">
+      <c r="G25" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21584,30 +21675,35 @@
     <row r="26">
       <c r="A26" s="169" t="inlineStr">
         <is>
-          <t>TC17</t>
+          <t>TC13</t>
         </is>
       </c>
       <c r="B26" s="170" t="inlineStr">
         <is>
-          <t>سوخت و انرژی</t>
-        </is>
-      </c>
-      <c r="C26" s="169" t="inlineStr">
+          <t>تعمیر و نگهداری</t>
+        </is>
+      </c>
+      <c r="C26" s="170" t="inlineStr">
+        <is>
+          <t>تعمیر و نگهداری دستگاه سورتینگ</t>
+        </is>
+      </c>
+      <c r="D26" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D26" s="169" t="inlineStr">
+      <c r="E26" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E26" s="169" t="inlineStr">
+      <c r="F26" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F26" s="169" t="inlineStr">
+      <c r="G26" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21616,30 +21712,35 @@
     <row r="27">
       <c r="A27" s="169" t="inlineStr">
         <is>
-          <t>TC18</t>
+          <t>TC14</t>
         </is>
       </c>
       <c r="B27" s="170" t="inlineStr">
         <is>
-          <t>اجاره انبار و زمین</t>
-        </is>
-      </c>
-      <c r="C27" s="169" t="inlineStr">
+          <t>تعمیر و نگهداری</t>
+        </is>
+      </c>
+      <c r="C27" s="170" t="inlineStr">
+        <is>
+          <t>تعمیر و نگهداری خط بسته‌بندی</t>
+        </is>
+      </c>
+      <c r="D27" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D27" s="169" t="inlineStr">
+      <c r="E27" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E27" s="169" t="inlineStr">
+      <c r="F27" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F27" s="169" t="inlineStr">
+      <c r="G27" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21648,30 +21749,35 @@
     <row r="28">
       <c r="A28" s="169" t="inlineStr">
         <is>
-          <t>TC19</t>
+          <t>TC15</t>
         </is>
       </c>
       <c r="B28" s="170" t="inlineStr">
         <is>
-          <t>انعام مصطفی</t>
-        </is>
-      </c>
-      <c r="C28" s="169" t="inlineStr">
+          <t>تعمیر و نگهداری</t>
+        </is>
+      </c>
+      <c r="C28" s="170" t="inlineStr">
+        <is>
+          <t>تعمیر و نگهداری سردخانه</t>
+        </is>
+      </c>
+      <c r="D28" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D28" s="169" t="inlineStr">
+      <c r="E28" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E28" s="169" t="inlineStr">
+      <c r="F28" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F28" s="169" t="inlineStr">
+      <c r="G28" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21685,25 +21791,30 @@
       </c>
       <c r="B29" s="170" t="inlineStr">
         <is>
+          <t>باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="C29" s="170" t="inlineStr">
+        <is>
           <t>هزینه باسکول دیگران</t>
         </is>
       </c>
-      <c r="C29" s="169" t="inlineStr">
+      <c r="D29" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D29" s="169" t="inlineStr">
+      <c r="E29" s="169" t="inlineStr">
         <is>
           <t>باسکول دیگران</t>
         </is>
       </c>
-      <c r="E29" s="169" t="inlineStr">
+      <c r="F29" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F29" s="169" t="inlineStr">
+      <c r="G29" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21717,25 +21828,30 @@
       </c>
       <c r="B30" s="170" t="inlineStr">
         <is>
+          <t>باسکول دیگران</t>
+        </is>
+      </c>
+      <c r="C30" s="170" t="inlineStr">
+        <is>
           <t>تسویه باسکول دیگران</t>
         </is>
       </c>
-      <c r="C30" s="169" t="inlineStr">
+      <c r="D30" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D30" s="169" t="inlineStr">
+      <c r="E30" s="169" t="inlineStr">
         <is>
           <t>باسکول دیگران</t>
         </is>
       </c>
-      <c r="E30" s="169" t="inlineStr">
+      <c r="F30" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F30" s="169" t="inlineStr">
+      <c r="G30" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21744,30 +21860,35 @@
     <row r="31">
       <c r="A31" s="169" t="inlineStr">
         <is>
-          <t>TC22</t>
+          <t>TC19</t>
         </is>
       </c>
       <c r="B31" s="170" t="inlineStr">
         <is>
-          <t>اقساط و تسهیلات</t>
-        </is>
-      </c>
-      <c r="C31" s="169" t="inlineStr">
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C31" s="170" t="inlineStr">
+        <is>
+          <t>انعام مصطفی</t>
+        </is>
+      </c>
+      <c r="D31" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D31" s="169" t="inlineStr">
-        <is>
-          <t>وام و تسهیلات</t>
-        </is>
-      </c>
       <c r="E31" s="169" t="inlineStr">
         <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="F31" s="169" t="inlineStr">
+        <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F31" s="169" t="inlineStr">
+      <c r="G31" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21776,30 +21897,35 @@
     <row r="32">
       <c r="A32" s="169" t="inlineStr">
         <is>
-          <t>TC23</t>
+          <t>TC22</t>
         </is>
       </c>
       <c r="B32" s="170" t="inlineStr">
         <is>
-          <t>دریافت تسهیلات</t>
-        </is>
-      </c>
-      <c r="C32" s="169" t="inlineStr">
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C32" s="170" t="inlineStr">
+        <is>
+          <t>اقساط و تسهیلات</t>
+        </is>
+      </c>
+      <c r="D32" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D32" s="169" t="inlineStr">
+      <c r="E32" s="169" t="inlineStr">
         <is>
           <t>وام و تسهیلات</t>
         </is>
       </c>
-      <c r="E32" s="169" t="inlineStr">
+      <c r="F32" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F32" s="169" t="inlineStr">
+      <c r="G32" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21808,30 +21934,35 @@
     <row r="33">
       <c r="A33" s="169" t="inlineStr">
         <is>
-          <t>TC24</t>
+          <t>TC23</t>
         </is>
       </c>
       <c r="B33" s="170" t="inlineStr">
         <is>
-          <t>مالیات و عوارض</t>
-        </is>
-      </c>
-      <c r="C33" s="169" t="inlineStr">
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C33" s="170" t="inlineStr">
+        <is>
+          <t>دریافت تسهیلات</t>
+        </is>
+      </c>
+      <c r="D33" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D33" s="169" t="inlineStr">
-        <is>
-          <t>سایر حساب</t>
-        </is>
-      </c>
       <c r="E33" s="169" t="inlineStr">
         <is>
+          <t>وام و تسهیلات</t>
+        </is>
+      </c>
+      <c r="F33" s="169" t="inlineStr">
+        <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F33" s="169" t="inlineStr">
+      <c r="G33" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21845,25 +21976,30 @@
       </c>
       <c r="B34" s="170" t="inlineStr">
         <is>
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C34" s="170" t="inlineStr">
+        <is>
           <t>سرمایه و آورده صاحبان</t>
         </is>
       </c>
-      <c r="C34" s="169" t="inlineStr">
+      <c r="D34" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D34" s="169" t="inlineStr">
+      <c r="E34" s="169" t="inlineStr">
         <is>
           <t>سرمایه و آورده صاحبان</t>
         </is>
       </c>
-      <c r="E34" s="169" t="inlineStr">
+      <c r="F34" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F34" s="169" t="inlineStr">
+      <c r="G34" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21877,25 +22013,30 @@
       </c>
       <c r="B35" s="170" t="inlineStr">
         <is>
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C35" s="170" t="inlineStr">
+        <is>
           <t>انتقال بین حساب‌های شرکت</t>
         </is>
       </c>
-      <c r="C35" s="169" t="inlineStr">
+      <c r="D35" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D35" s="169" t="inlineStr">
+      <c r="E35" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E35" s="169" t="inlineStr">
+      <c r="F35" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F35" s="169" t="inlineStr">
+      <c r="G35" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21909,25 +22050,30 @@
       </c>
       <c r="B36" s="170" t="inlineStr">
         <is>
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C36" s="170" t="inlineStr">
+        <is>
           <t>سایر درآمد</t>
         </is>
       </c>
-      <c r="C36" s="169" t="inlineStr">
+      <c r="D36" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D36" s="169" t="inlineStr">
+      <c r="E36" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E36" s="169" t="inlineStr">
+      <c r="F36" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F36" s="169" t="inlineStr">
+      <c r="G36" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21941,25 +22087,30 @@
       </c>
       <c r="B37" s="170" t="inlineStr">
         <is>
+          <t>مالی و سرمایه</t>
+        </is>
+      </c>
+      <c r="C37" s="170" t="inlineStr">
+        <is>
           <t>سایر هزینه</t>
         </is>
       </c>
-      <c r="C37" s="169" t="inlineStr">
+      <c r="D37" s="169" t="inlineStr">
         <is>
           <t>شرکتی</t>
         </is>
       </c>
-      <c r="D37" s="169" t="inlineStr">
+      <c r="E37" s="169" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E37" s="169" t="inlineStr">
+      <c r="F37" s="169" t="inlineStr">
         <is>
           <t>هزینه/درآمد شرکت</t>
         </is>
       </c>
-      <c r="F37" s="169" t="inlineStr">
+      <c r="G37" s="169" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -21968,30 +22119,35 @@
     <row r="38">
       <c r="A38" s="171" t="inlineStr">
         <is>
-          <t>TC29</t>
+          <t>TC30</t>
         </is>
       </c>
       <c r="B38" s="172" t="inlineStr">
         <is>
-          <t>هزینه شخصی رئیس</t>
-        </is>
-      </c>
-      <c r="C38" s="171" t="inlineStr">
+          <t>شخصی رئیس — دارایی</t>
+        </is>
+      </c>
+      <c r="C38" s="172" t="inlineStr">
+        <is>
+          <t>خرید وسایل شخصی</t>
+        </is>
+      </c>
+      <c r="D38" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D38" s="171" t="inlineStr">
+      <c r="E38" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E38" s="171" t="inlineStr">
+      <c r="F38" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F38" s="171" t="inlineStr">
+      <c r="G38" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22000,30 +22156,35 @@
     <row r="39">
       <c r="A39" s="171" t="inlineStr">
         <is>
-          <t>TC30</t>
+          <t>TC31</t>
         </is>
       </c>
       <c r="B39" s="172" t="inlineStr">
         <is>
-          <t>خرید وسایل شخصی</t>
-        </is>
-      </c>
-      <c r="C39" s="171" t="inlineStr">
+          <t>شخصی رئیس — دارایی</t>
+        </is>
+      </c>
+      <c r="C39" s="172" t="inlineStr">
+        <is>
+          <t>فروش وسایل شخصی</t>
+        </is>
+      </c>
+      <c r="D39" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D39" s="171" t="inlineStr">
+      <c r="E39" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E39" s="171" t="inlineStr">
+      <c r="F39" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F39" s="171" t="inlineStr">
+      <c r="G39" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22032,30 +22193,35 @@
     <row r="40">
       <c r="A40" s="171" t="inlineStr">
         <is>
-          <t>TC31</t>
+          <t>TC32</t>
         </is>
       </c>
       <c r="B40" s="172" t="inlineStr">
         <is>
-          <t>فروش وسایل شخصی</t>
-        </is>
-      </c>
-      <c r="C40" s="171" t="inlineStr">
+          <t>شخصی رئیس — دارایی</t>
+        </is>
+      </c>
+      <c r="C40" s="172" t="inlineStr">
+        <is>
+          <t>خرید خودرو</t>
+        </is>
+      </c>
+      <c r="D40" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D40" s="171" t="inlineStr">
+      <c r="E40" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E40" s="171" t="inlineStr">
+      <c r="F40" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F40" s="171" t="inlineStr">
+      <c r="G40" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22064,30 +22230,35 @@
     <row r="41">
       <c r="A41" s="171" t="inlineStr">
         <is>
-          <t>TC32</t>
+          <t>TC33</t>
         </is>
       </c>
       <c r="B41" s="172" t="inlineStr">
         <is>
-          <t>خرید خودرو</t>
-        </is>
-      </c>
-      <c r="C41" s="171" t="inlineStr">
+          <t>شخصی رئیس — دارایی</t>
+        </is>
+      </c>
+      <c r="C41" s="172" t="inlineStr">
+        <is>
+          <t>فروش خودرو</t>
+        </is>
+      </c>
+      <c r="D41" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D41" s="171" t="inlineStr">
+      <c r="E41" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E41" s="171" t="inlineStr">
+      <c r="F41" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F41" s="171" t="inlineStr">
+      <c r="G41" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22096,30 +22267,35 @@
     <row r="42">
       <c r="A42" s="171" t="inlineStr">
         <is>
-          <t>TC33</t>
+          <t>TC35</t>
         </is>
       </c>
       <c r="B42" s="172" t="inlineStr">
         <is>
-          <t>فروش خودرو</t>
-        </is>
-      </c>
-      <c r="C42" s="171" t="inlineStr">
+          <t>شخصی رئیس — دارایی</t>
+        </is>
+      </c>
+      <c r="C42" s="172" t="inlineStr">
+        <is>
+          <t>مسکن و قبض منزل</t>
+        </is>
+      </c>
+      <c r="D42" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D42" s="171" t="inlineStr">
+      <c r="E42" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E42" s="171" t="inlineStr">
+      <c r="F42" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F42" s="171" t="inlineStr">
+      <c r="G42" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22128,30 +22304,35 @@
     <row r="43">
       <c r="A43" s="171" t="inlineStr">
         <is>
-          <t>TC34</t>
+          <t>TC29</t>
         </is>
       </c>
       <c r="B43" s="172" t="inlineStr">
         <is>
-          <t>سوخت و تعمیر خودرو شخصی</t>
-        </is>
-      </c>
-      <c r="C43" s="171" t="inlineStr">
+          <t>شخصی رئیس — زندگی</t>
+        </is>
+      </c>
+      <c r="C43" s="172" t="inlineStr">
+        <is>
+          <t>هزینه شخصی رئیس</t>
+        </is>
+      </c>
+      <c r="D43" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D43" s="171" t="inlineStr">
+      <c r="E43" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E43" s="171" t="inlineStr">
+      <c r="F43" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F43" s="171" t="inlineStr">
+      <c r="G43" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22160,30 +22341,35 @@
     <row r="44">
       <c r="A44" s="171" t="inlineStr">
         <is>
-          <t>TC35</t>
+          <t>TC34</t>
         </is>
       </c>
       <c r="B44" s="172" t="inlineStr">
         <is>
-          <t>مسکن و قبض منزل</t>
-        </is>
-      </c>
-      <c r="C44" s="171" t="inlineStr">
+          <t>شخصی رئیس — زندگی</t>
+        </is>
+      </c>
+      <c r="C44" s="172" t="inlineStr">
+        <is>
+          <t>سوخت و تعمیر خودرو شخصی</t>
+        </is>
+      </c>
+      <c r="D44" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D44" s="171" t="inlineStr">
+      <c r="E44" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E44" s="171" t="inlineStr">
+      <c r="F44" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F44" s="171" t="inlineStr">
+      <c r="G44" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22197,25 +22383,30 @@
       </c>
       <c r="B45" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — زندگی</t>
+        </is>
+      </c>
+      <c r="C45" s="172" t="inlineStr">
+        <is>
           <t>درمان و سلامت</t>
         </is>
       </c>
-      <c r="C45" s="171" t="inlineStr">
+      <c r="D45" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D45" s="171" t="inlineStr">
+      <c r="E45" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E45" s="171" t="inlineStr">
+      <c r="F45" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F45" s="171" t="inlineStr">
+      <c r="G45" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22229,25 +22420,30 @@
       </c>
       <c r="B46" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — زندگی</t>
+        </is>
+      </c>
+      <c r="C46" s="172" t="inlineStr">
+        <is>
           <t>تحصیل و آموزش</t>
         </is>
       </c>
-      <c r="C46" s="171" t="inlineStr">
+      <c r="D46" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D46" s="171" t="inlineStr">
+      <c r="E46" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E46" s="171" t="inlineStr">
+      <c r="F46" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F46" s="171" t="inlineStr">
+      <c r="G46" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22261,25 +22457,30 @@
       </c>
       <c r="B47" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — زندگی</t>
+        </is>
+      </c>
+      <c r="C47" s="172" t="inlineStr">
+        <is>
           <t>سفر و تفریح</t>
         </is>
       </c>
-      <c r="C47" s="171" t="inlineStr">
+      <c r="D47" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D47" s="171" t="inlineStr">
+      <c r="E47" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E47" s="171" t="inlineStr">
+      <c r="F47" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F47" s="171" t="inlineStr">
+      <c r="G47" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22293,25 +22494,30 @@
       </c>
       <c r="B48" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — زندگی</t>
+        </is>
+      </c>
+      <c r="C48" s="172" t="inlineStr">
+        <is>
           <t>هدیه و نذورات</t>
         </is>
       </c>
-      <c r="C48" s="171" t="inlineStr">
+      <c r="D48" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D48" s="171" t="inlineStr">
+      <c r="E48" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E48" s="171" t="inlineStr">
+      <c r="F48" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F48" s="171" t="inlineStr">
+      <c r="G48" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22325,25 +22531,30 @@
       </c>
       <c r="B49" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — جریان پول</t>
+        </is>
+      </c>
+      <c r="C49" s="172" t="inlineStr">
+        <is>
           <t>دریافتی شخصی</t>
         </is>
       </c>
-      <c r="C49" s="171" t="inlineStr">
+      <c r="D49" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D49" s="171" t="inlineStr">
+      <c r="E49" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E49" s="171" t="inlineStr">
+      <c r="F49" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F49" s="171" t="inlineStr">
+      <c r="G49" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22357,25 +22568,30 @@
       </c>
       <c r="B50" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — جریان پول</t>
+        </is>
+      </c>
+      <c r="C50" s="172" t="inlineStr">
+        <is>
           <t>واریز از حساب شرکت به شخصی</t>
         </is>
       </c>
-      <c r="C50" s="171" t="inlineStr">
+      <c r="D50" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D50" s="171" t="inlineStr">
+      <c r="E50" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E50" s="171" t="inlineStr">
+      <c r="F50" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F50" s="171" t="inlineStr">
+      <c r="G50" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>
@@ -22389,25 +22605,30 @@
       </c>
       <c r="B51" s="172" t="inlineStr">
         <is>
+          <t>شخصی رئیس — جریان پول</t>
+        </is>
+      </c>
+      <c r="C51" s="172" t="inlineStr">
+        <is>
           <t>برگشت وجه شخصی به شرکت</t>
         </is>
       </c>
-      <c r="C51" s="171" t="inlineStr">
+      <c r="D51" s="171" t="inlineStr">
         <is>
           <t>شخصی رئیس</t>
         </is>
       </c>
-      <c r="D51" s="171" t="inlineStr">
+      <c r="E51" s="171" t="inlineStr">
         <is>
           <t>سایر حساب</t>
         </is>
       </c>
-      <c r="E51" s="171" t="inlineStr">
+      <c r="F51" s="171" t="inlineStr">
         <is>
           <t>پول شخصی رئیس — به حساب جاری رئیس می‌رود</t>
         </is>
       </c>
-      <c r="F51" s="171" t="inlineStr">
+      <c r="G51" s="171" t="inlineStr">
         <is>
           <t>بله</t>
         </is>

--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -11,22 +11,23 @@
     <sheet name="Par" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Grp" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Acc" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cls" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Op" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Bsk" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Prd" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Bnk" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="List" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sync" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Help" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Shrk" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cls" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Op" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bsk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Prd" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Bnk" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="List" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Sync" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Help" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="AcctCodes">Acc!$A$10:$A$259</definedName>
-    <definedName name="AcctTbl">Acc!$A$10:$J$259</definedName>
+    <definedName name="AcctCodes">Acc!$A$10:$A$280</definedName>
+    <definedName name="AcctTbl">Acc!$A$10:$J$280</definedName>
     <definedName name="BankTbl">Bnk!$A$10:$G$19</definedName>
     <definedName name="BasketTbl">Bsk!$B$10:$F$21</definedName>
     <definedName name="GroupTbl">Grp!$A$10:$F$52</definedName>
-    <definedName name="ListAllCodes">OFFSET(Acc!$A$10,0,0,MAX(COUNTIF(Acc!$D$10:$D$259,"?*"),1),1)</definedName>
+    <definedName name="ListAllCodes">OFFSET(Acc!$A$10,0,0,MAX(COUNTIF(Acc!$D$10:$D$280,"?*"),1),1)</definedName>
     <definedName name="ListBanks">OFFSET(Bnk!$B$10,0,0,MAX(COUNTIF(Bnk!$B$10:$B$19,"?*"),1),1)</definedName>
     <definedName name="ListBasketOps">OFFSET(Op!$B$24,0,0,MAX(COUNTIF(Op!$B$24:$B$33,"?*"),1),1)</definedName>
     <definedName name="ListBaskets">OFFSET(Bsk!$B$10,0,0,MAX(COUNTIF(Bsk!$B$10:$B$21,"?*"),1),1)</definedName>
@@ -55,38 +56,43 @@
     <definedName name="OpTbl">Op!$A$10:$S$33</definedName>
     <definedName name="ParamTbl">Par!$A$10:$E$21</definedName>
     <definedName name="ProductTbl">Prd!$B$10:$D$29</definedName>
-    <definedName name="ListBankOps">List!$S$10:$S$36</definedName>
+    <definedName name="ListBankOps">List!$S$10:$S$38</definedName>
     <definedName name="ListOtherScalesLabel">List!$T$10:$T$29</definedName>
     <definedName name="ListBankNames">List!$U$10:$U$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$48</definedName>
+    <definedName name="ShrkTbl">Shrk!$A$12:$D$31</definedName>
+    <definedName name="ListShrk">OFFSET(Shrk!$A$12,0,0,MAX(COUNTIF(Shrk!$B$12:$B$31,"?*"),1),1)</definedName>
+    <definedName name="ListShrkNames">OFFSET(Shrk!$B$12,0,0,MAX(COUNTIF(Shrk!$B$12:$B$31,"?*"),1),1)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Co'!$A$1:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Par'!$A$8:$E$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Par'!$7:$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Par'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Grp'!$A$8:$F$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Grp'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Grp'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Grp'!$A$1:$E$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Acc'!$A$8:$M$259</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Acc'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Acc'!$A$1:$M$260</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Cls'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Cls'!$A$1:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Op'!$A$8:$S$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Op'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Op'!$A$1:$S$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Bsk'!$A$8:$J$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Bsk'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Bsk'!$A$1:$J$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Prd'!$A$8:$G$30</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Prd'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Prd'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Bnk'!$A$8:$G$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Bnk'!$7:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Bnk'!$A$1:$G$22</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'List'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'List'!$A$1:$R$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'Sync'!$A$1:$K$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'Help'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Acc'!$A$1:$M$282</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Shrk'!$10:$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Shrk'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Cls'!$8:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Cls'!$A$1:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Op'!$A$8:$S$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Op'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Op'!$A$1:$S$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Bsk'!$A$8:$J$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Bsk'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Bsk'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Prd'!$A$8:$G$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Prd'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Prd'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Bnk'!$A$8:$G$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Bnk'!$7:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Bnk'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'List'!$8:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'List'!$A$1:$R$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Sync'!$A$1:$K$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Help'!$A$1:$J$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -94,13 +100,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;[Red]-#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0;[Red](#,##0)"/>
+    <numFmt numFmtId="168" formatCode="0&quot;٪&quot;"/>
   </numFmts>
-  <fonts count="91">
+  <fonts count="107">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -663,6 +670,98 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FFD8E6DF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="B Titr"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <color rgb="FFD8E6DF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="FF6B7A76"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FF14453D"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FF3F7A57"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FFC89B3C"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FFC4623F"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FF2B5C7A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="FFEFDFB8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="FFD8E6DF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="FF2B2A26"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="FF14453D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="B Nazanin"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -675,7 +774,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -837,11 +936,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC89B3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F0E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3EADB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4623F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E4F0E8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="80">
     <border>
       <left/>
       <right/>
@@ -1509,6 +1633,220 @@
       <diagonal/>
     </border>
     <border>
+      <bottom style="thin">
+        <color rgb="FF14453D"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF14453D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF14453D"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF14453D"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF14453D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF14453D"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFEDE6D8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC4623F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC4623F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC4623F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC4623F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFEDE6D8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFEDE6D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFEDE6D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFEDE6D8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC4623F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC4623F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC4623F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC4623F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC4623F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC4623F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC4623F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC4623F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="FFEDE6D8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFEDE6D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="FF14453D"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFEDE6D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFEDE6D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFEDE6D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFEDE6D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFEDE6D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFEDE6D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFEDE6D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFEDE6D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF14453D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF14453D"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF14453D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF14453D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF14453D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF14453D"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF14453D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF14453D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="00D8D2C2"/>
       </left>
@@ -1526,7 +1864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -1986,12 +2324,125 @@
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="103" fillId="33" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="21" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="93" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="94" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="95" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="96" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="97" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="20" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="20" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="20" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="30" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="101" fillId="30" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="102" fillId="31" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="22" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="30" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="30" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="21" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="21" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="102" fillId="21" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="31" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="32" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="22" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="31" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="29" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="106" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="20" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="31" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="32" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2685,6 +3136,61 @@
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>MAZANDASHT</author>
+  </authors>
+  <commentList>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>کد ثابت شریک (SH01…SH20). همین کد در باسکول، شیت پرداخت و تراکنش بانکی انتخاب می‌شود.</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>نام کامل شخص/شرکت شریک. اگر ردیفی بی‌نام بماند، در کشوها دیده نمی‌شود.</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>درصد سهم شریک از بار و مبلغ شراکتی (۱ تا ۹۹). همین عدد، مبنای محاسبه سهم وزنی و ریالی است.</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>خودکار: ۱۰۰ منهای نسبت شریک. این نسبت، سهمی است که در دفتر روزنامه سند می‌خورد.</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>بار/محصول شراکتی و توضیح کوتاه قرارداد.</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>محصول اصلی این شراکت (کیوی، پرتقال، نارنگی …).</t>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0">
+      <text>
+        <t>بانک شرکت که سهم شریک از آن پرداخت می‌شود (BNxx).</t>
+      </text>
+    </comment>
+    <comment ref="J10" authorId="0" shapeId="0">
+      <text>
+        <t>فعال / غیرفعال.</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>هر یادداشت دیگر: شماره قرارداد، شرایط تسویه …</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
     <author>راهنمای مازندشت</author>
   </authors>
   <commentList>
@@ -2787,7 +3293,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>راهنمای مازندشت</author>
@@ -2842,7 +3348,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>راهنمای مازندشت</author>
@@ -2882,7 +3388,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>راهنمای مازندشت</author>
@@ -3263,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.7109375" customWidth="1" min="1" max="10"/>
@@ -3924,59 +4430,80 @@
       <c r="J44" s="115" t="n"/>
     </row>
     <row r="45"/>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="177" t="inlineStr">
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     شیت تازه:  Shrk — شرکا و نسبت شراکت  (۲۰ شریک، نسبت سهم شریک و سهم شرکت)</t>
+        </is>
+      </c>
+      <c r="B50" s="214" t="n"/>
+      <c r="C50" s="214" t="n"/>
+      <c r="D50" s="214" t="n"/>
+      <c r="E50" s="214" t="n"/>
+      <c r="F50" s="214" t="n"/>
+      <c r="G50" s="214" t="n"/>
+      <c r="H50" s="214" t="n"/>
+      <c r="I50" s="214" t="n"/>
+      <c r="J50" s="215" t="n"/>
+    </row>
+    <row r="51"/>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="216" t="inlineStr">
         <is>
           <t xml:space="preserve">     فایل‌های همراه — با یک کلیک باز می‌شوند (مسیر نسبی، همه در همین پوشه)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="178" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="217" t="inlineStr">
         <is>
           <t>دفتر ثبت  01_Entry</t>
         </is>
       </c>
-      <c r="C47" s="178" t="inlineStr">
+      <c r="C53" s="217" t="inlineStr">
         <is>
           <t>بانک  02_Bank</t>
         </is>
       </c>
-      <c r="E47" s="178" t="inlineStr">
+      <c r="E53" s="217" t="inlineStr">
         <is>
           <t>گزارش‌ها  03_Report</t>
         </is>
       </c>
-      <c r="G47" s="178" t="inlineStr">
+      <c r="G53" s="217" t="inlineStr">
         <is>
           <t>فاکتورها  04_Inv</t>
         </is>
       </c>
-      <c r="I47" s="178" t="inlineStr">
+      <c r="I53" s="217" t="inlineStr">
         <is>
           <t>تراز  05_Bal</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="178" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="217" t="inlineStr">
         <is>
           <t>خریداران  06_Buyers</t>
         </is>
       </c>
-      <c r="C48" s="178" t="inlineStr">
+      <c r="C54" s="217" t="inlineStr">
         <is>
           <t>نمونه  07_Demo</t>
         </is>
       </c>
-      <c r="E48" s="178" t="inlineStr">
+      <c r="E54" s="217" t="inlineStr">
         <is>
           <t>داشبورد  08_Dash</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="66">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="D28:J28"/>
     <mergeCell ref="G12:H12"/>
@@ -3996,6 +4523,7 @@
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="D30:J30"/>
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="D29:J29"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="B38:J38"/>
@@ -4034,11 +4562,11 @@
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="D27:J27"/>
     <mergeCell ref="D32:J32"/>
-    <mergeCell ref="A46:J46"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A50:J50"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="B39:J39"/>
@@ -4053,14 +4581,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId5"/>
     <hyperlink ref="A44" location="Help!A20" display="راهنمای کامل سامانه — روی این نوار کلیک کنید"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
@@ -4073,11 +4602,853 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFE0A458"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9.7109375" customWidth="1" min="1" max="1"/>
+    <col width="30.7109375" customWidth="1" min="2" max="2"/>
+    <col width="16.7109375" customWidth="1" min="3" max="3"/>
+    <col width="11.7109375" customWidth="1" min="4" max="4"/>
+    <col width="16.7109375" customWidth="1" min="5" max="5"/>
+    <col width="30.7109375" customWidth="1" min="6" max="6"/>
+    <col width="26.7109375" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" s="138" t="inlineStr">
+        <is>
+          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
+        </is>
+      </c>
+      <c r="C1" s="132" t="inlineStr">
+        <is>
+          <t>MAZANDASHT  ·  CITRUS SORTING &amp; PACKING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38.25" customHeight="1">
+      <c r="A2" s="133" t="inlineStr">
+        <is>
+          <t>محصولات — خرید و فروش</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45.75" customHeight="1">
+      <c r="A3" s="134" t="inlineStr">
+        <is>
+          <t>برای هر محصول، دسته (نوع مرکبات)، واحد و سبد پیش‌فرض تعریف می‌شود</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>راهنما</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>ورود دستی</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>خودکار</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>ورود</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>خروج</t>
+        </is>
+      </c>
+      <c r="F4" s="50" t="inlineStr">
+        <is>
+          <t>هشدار</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>محصولات</t>
+        </is>
+      </c>
+      <c r="B5" s="108" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D5" s="108" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="F5" s="108" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>لیمو</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="33" customHeight="1">
+      <c r="A6" s="52">
+        <f>COUNTIF($B$10:$B$29,"?*")</f>
+        <v/>
+      </c>
+      <c r="B6" s="109" t="n"/>
+      <c r="C6" s="85">
+        <f>COUNTIF($C$10:$C$29,"پرتقال")</f>
+        <v/>
+      </c>
+      <c r="D6" s="109" t="n"/>
+      <c r="E6" s="53">
+        <f>COUNTIF($C$10:$C$29,"نارنگی")</f>
+        <v/>
+      </c>
+      <c r="F6" s="109" t="n"/>
+      <c r="G6" s="86">
+        <f>COUNTIF($C$10:$C$29,"لیمو")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="6.75" customHeight="1"/>
+    <row r="8" ht="33.75" customHeight="1">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t>نام محصول</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>دسته / نوع مرکبات</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>واحد</t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>سبد پیش‌فرض</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>توضیح</t>
+        </is>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>برچسب کشویی</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>Default Basket</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="23.25" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>PB01</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>پرتقال تامسون</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F10" s="60" t="inlineStr">
+        <is>
+          <t>خرید از باغ / میدان بار</t>
+        </is>
+      </c>
+      <c r="G10" s="84">
+        <f>IF($B10="","",$B10&amp;" – "&amp;$C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="23.25" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>PB02</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>پرتقال خونی</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F11" s="60" t="n"/>
+      <c r="G11" s="84">
+        <f>IF($B11="","",$B11&amp;" – "&amp;$C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="23.25" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>PB03</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>پرتقال کاراکارا</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E12" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F12" s="60" t="n"/>
+      <c r="G12" s="84">
+        <f>IF($B12="","",$B12&amp;" – "&amp;$C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="23.25" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>PB04</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>پرتقال بیروتی</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="n"/>
+      <c r="G13" s="84">
+        <f>IF($B13="","",$B13&amp;" – "&amp;$C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="23.25" customHeight="1">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>PB05</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>پرتقال یافا</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E14" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="n"/>
+      <c r="G14" s="84">
+        <f>IF($B14="","",$B14&amp;" – "&amp;$C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="23.25" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>PB06</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
+        <is>
+          <t>نارنگی پیچ</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="n"/>
+      <c r="G15" s="84">
+        <f>IF($B15="","",$B15&amp;" – "&amp;$C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="23.25" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>PB07</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="inlineStr">
+        <is>
+          <t>نارنگی ژاپنی</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E16" s="58" t="inlineStr">
+        <is>
+          <t>BK07</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="n"/>
+      <c r="G16" s="84">
+        <f>IF($B16="","",$B16&amp;" – "&amp;$C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="23.25" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>PB08</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="inlineStr">
+        <is>
+          <t>نارنگی اونشو</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="n"/>
+      <c r="G17" s="84">
+        <f>IF($B17="","",$B17&amp;" – "&amp;$C17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="23.25" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>PB09</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="inlineStr">
+        <is>
+          <t>نارنگی یافا</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E18" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="n"/>
+      <c r="G18" s="84">
+        <f>IF($B18="","",$B18&amp;" – "&amp;$C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="23.25" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>PB10</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="inlineStr">
+        <is>
+          <t>لیمو شیرین</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>لیمو</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E19" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="n"/>
+      <c r="G19" s="84">
+        <f>IF($B19="","",$B19&amp;" – "&amp;$C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="23.25" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>PB11</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
+          <t>لیمو ترش</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>لیمو</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E20" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="n"/>
+      <c r="G20" s="84">
+        <f>IF($B20="","",$B20&amp;" – "&amp;$C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="23.25" customHeight="1">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>PB12</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>کامکوات</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>سایر</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E21" s="58" t="inlineStr">
+        <is>
+          <t>BK04</t>
+        </is>
+      </c>
+      <c r="F21" s="60" t="n"/>
+      <c r="G21" s="84">
+        <f>IF($B21="","",$B21&amp;" – "&amp;$C21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="23.25" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>PB13</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>گریپ‌فرویت</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>گریپ‌فرویت</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E22" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F22" s="60" t="n"/>
+      <c r="G22" s="84">
+        <f>IF($B22="","",$B22&amp;" – "&amp;$C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="23.25" customHeight="1">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>PB14</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>خرمالو</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>سایر</t>
+        </is>
+      </c>
+      <c r="D23" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E23" s="58" t="inlineStr">
+        <is>
+          <t>BK01</t>
+        </is>
+      </c>
+      <c r="F23" s="60" t="n"/>
+      <c r="G23" s="84">
+        <f>IF($B23="","",$B23&amp;" – "&amp;$C23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="23.25" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>PB15</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>نارنج</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>سایر</t>
+        </is>
+      </c>
+      <c r="D24" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E24" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F24" s="60" t="n"/>
+      <c r="G24" s="84">
+        <f>IF($B24="","",$B24&amp;" – "&amp;$C24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="23.25" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>PB16</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="D25" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E25" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F25" s="60" t="inlineStr">
+        <is>
+          <t>بار شاخص فصل سرد؛ شراکت با سعید بابایی</t>
+        </is>
+      </c>
+      <c r="G25" s="84">
+        <f>IF($B25="","",$B25&amp;" – "&amp;$C25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="23.25" customHeight="1">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>PB17</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>پرتقال والنسیا</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>کیلوگرم</t>
+        </is>
+      </c>
+      <c r="E26" s="58" t="inlineStr">
+        <is>
+          <t>BK03</t>
+        </is>
+      </c>
+      <c r="F26" s="60" t="inlineStr">
+        <is>
+          <t>رقم دیررس؛ شراکت با مجید قاسمی</t>
+        </is>
+      </c>
+      <c r="G26" s="84">
+        <f>IF($B26="","",$B26&amp;" – "&amp;$C26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="23.25" customHeight="1">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>PB18</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="47" t="n"/>
+      <c r="E27" s="58" t="n"/>
+      <c r="F27" s="60" t="n"/>
+      <c r="G27" s="84">
+        <f>IF($B27="","",$B27&amp;" – "&amp;$C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="23.25" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>PB19</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="n"/>
+      <c r="C28" s="47" t="n"/>
+      <c r="D28" s="47" t="n"/>
+      <c r="E28" s="58" t="n"/>
+      <c r="F28" s="60" t="n"/>
+      <c r="G28" s="84">
+        <f>IF($B28="","",$B28&amp;" – "&amp;$C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="23.25" customHeight="1">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>PB20</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="47" t="n"/>
+      <c r="E29" s="58" t="n"/>
+      <c r="F29" s="60" t="n"/>
+      <c r="G29" s="84">
+        <f>IF($B29="","",$B29&amp;" – "&amp;$C29)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:G30"/>
+  <mergeCells count="10">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C10:C30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>ListCategories</formula1>
+    </dataValidation>
+    <dataValidation sqref="D10:D30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>ListUnits</formula1>
+    </dataValidation>
+    <dataValidation sqref="E10:E30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>ListBaskets</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.28" right="0.28" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;Lمازندشت&amp;RMAZANDASHT · CITRUS</oddHeader>
+    <oddFooter>&amp;Lمازندشت — سورتینگ و بسته‌بندی مرکبات&amp;Cصفحه &amp;P از &amp;N&amp;RMAZANDASHT · 1405</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E6B4F"/>
@@ -4583,14 +5954,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF6B7A76"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.7109375" customWidth="1" min="1" max="18"/>
@@ -5905,6 +7276,20 @@
       <c r="S36" s="152" t="inlineStr">
         <is>
           <t>تسویه پرداخت (واسط)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="S37" s="152" t="inlineStr">
+        <is>
+          <t>پرداخت سهم شراکت به شریک</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="S38" s="152" t="inlineStr">
+        <is>
+          <t>دریافت از شریک</t>
         </is>
       </c>
     </row>
@@ -5933,7 +7318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFB9B2A1"/>
@@ -7104,6 +8489,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H34" s="156" t="inlineStr">
+        <is>
+          <t>پرداخت سهم شراکت به شریک</t>
+        </is>
+      </c>
+      <c r="I34" s="157" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="J34" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K34" s="157" t="inlineStr"/>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="93" t="inlineStr">
@@ -7124,6 +8525,22 @@
           <t>Accounts / Groups</t>
         </is>
       </c>
+      <c r="H35" s="156" t="inlineStr">
+        <is>
+          <t>دریافت از شریک</t>
+        </is>
+      </c>
+      <c r="I35" s="157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="J35" s="157" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="K35" s="157" t="inlineStr"/>
     </row>
     <row r="36" ht="21.75" customHeight="1">
       <c r="A36" s="97" t="inlineStr">
@@ -7482,14 +8899,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF14453D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7109375" customWidth="1" min="1" max="1"/>
@@ -8718,9 +10135,122 @@
       <c r="I123" s="154" t="n"/>
       <c r="J123" s="155" t="n"/>
     </row>
+    <row r="124"/>
+    <row r="125" ht="26" customHeight="1">
+      <c r="A125" s="211" t="inlineStr">
+        <is>
+          <t>۰۹   شراکت — خرید و فروش مشترک</t>
+        </is>
+      </c>
+      <c r="B125" s="222" t="n"/>
+      <c r="C125" s="222" t="n"/>
+      <c r="D125" s="222" t="n"/>
+      <c r="E125" s="222" t="n"/>
+      <c r="F125" s="222" t="n"/>
+      <c r="G125" s="222" t="n"/>
+      <c r="H125" s="222" t="n"/>
+      <c r="I125" s="222" t="n"/>
+      <c r="J125" s="223" t="n"/>
+    </row>
+    <row r="126" ht="46" customHeight="1">
+      <c r="A126" s="212" t="inlineStr">
+        <is>
+          <t>شیت Shrk فهرست شرکاست: کد SHxx، نام، «نسبت سهم شریک» و «نسبت سهم شرکت» (خودکار ۱۰۰ منهای آن). همین کدها به شیت Acc هم اضافه شده‌اند (گروه «شرکا»)، پس در باسکول، شیت پرداخت، تراکنش بانکی، دفاتر و ترازنامه مثل هر طرف حساب دیگری انتخاب می‌شوند.</t>
+        </is>
+      </c>
+      <c r="B126" s="224" t="n"/>
+      <c r="C126" s="224" t="n"/>
+      <c r="D126" s="224" t="n"/>
+      <c r="E126" s="224" t="n"/>
+      <c r="F126" s="224" t="n"/>
+      <c r="G126" s="224" t="n"/>
+      <c r="H126" s="224" t="n"/>
+      <c r="I126" s="224" t="n"/>
+      <c r="J126" s="225" t="n"/>
+    </row>
+    <row r="127" ht="46" customHeight="1">
+      <c r="A127" s="213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     •  در باسکول دو عملیات تازه اضافه شده: «خرید شراکتی (ورود)» و «فروش شراکتی (خروج)». کافی است عملیات را انتخاب و کد شریک را در ستون «کد حساب / مقصد وجه» بزنید.</t>
+        </is>
+      </c>
+      <c r="B127" s="224" t="n"/>
+      <c r="C127" s="224" t="n"/>
+      <c r="D127" s="224" t="n"/>
+      <c r="E127" s="224" t="n"/>
+      <c r="F127" s="224" t="n"/>
+      <c r="G127" s="224" t="n"/>
+      <c r="H127" s="224" t="n"/>
+      <c r="I127" s="224" t="n"/>
+      <c r="J127" s="225" t="n"/>
+    </row>
+    <row r="128" ht="46" customHeight="1">
+      <c r="A128" s="213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     •  محاسبه به وزن است: شیت Scale شش ستون تازه دارد — نسبت شرکت، سهم شرکت (ریال)، سهم شریک (ریال)، سهم شرکت (kg)، سهم شریک (kg) و کنترل. مبلغ هر ردیف = وزن خالص × فی.</t>
+        </is>
+      </c>
+      <c r="B128" s="224" t="n"/>
+      <c r="C128" s="224" t="n"/>
+      <c r="D128" s="224" t="n"/>
+      <c r="E128" s="224" t="n"/>
+      <c r="F128" s="224" t="n"/>
+      <c r="G128" s="224" t="n"/>
+      <c r="H128" s="224" t="n"/>
+      <c r="I128" s="224" t="n"/>
+      <c r="J128" s="225" t="n"/>
+    </row>
+    <row r="129" ht="46" customHeight="1">
+      <c r="A129" s="213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     •  در دفتر روزنامه فقط «سهم شرکت» سند می‌خورد (خرید: بدهکار موجودی / بستانکار شریک — فروش: بدهکار خریدار / بستانکار فروش). سهم شریک در گزارش شیت Shrk فایل 01_Entry دیده می‌شود.</t>
+        </is>
+      </c>
+      <c r="B129" s="224" t="n"/>
+      <c r="C129" s="224" t="n"/>
+      <c r="D129" s="224" t="n"/>
+      <c r="E129" s="224" t="n"/>
+      <c r="F129" s="224" t="n"/>
+      <c r="G129" s="224" t="n"/>
+      <c r="H129" s="224" t="n"/>
+      <c r="I129" s="224" t="n"/>
+      <c r="J129" s="225" t="n"/>
+    </row>
+    <row r="130" ht="46" customHeight="1">
+      <c r="A130" s="213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     •  پرداخت به شریک = سهم واریزی ما: در شیت پرداخت نوع «پرداخت»، کد SHxx و روش پرداخت را بزنید. این پرداخت‌ها در جدول شرکا از بدهی ما کم می‌شود و ستون «مانده» بدهی باقی‌مانده را نشان می‌دهد.</t>
+        </is>
+      </c>
+      <c r="B130" s="224" t="n"/>
+      <c r="C130" s="224" t="n"/>
+      <c r="D130" s="224" t="n"/>
+      <c r="E130" s="224" t="n"/>
+      <c r="F130" s="224" t="n"/>
+      <c r="G130" s="224" t="n"/>
+      <c r="H130" s="224" t="n"/>
+      <c r="I130" s="224" t="n"/>
+      <c r="J130" s="225" t="n"/>
+    </row>
+    <row r="131" ht="46" customHeight="1">
+      <c r="A131" s="213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     •  برای تغییر نسبت یک شریک، فقط ستون «نسبت سهم شریک ٪» را در همین شیت عوض کنید؛ فایل‌های دیگر با باز شدن، Sync خود را از نو می‌خوانند (نسخه جدید پوشه، همان کدها).</t>
+        </is>
+      </c>
+      <c r="B131" s="224" t="n"/>
+      <c r="C131" s="224" t="n"/>
+      <c r="D131" s="224" t="n"/>
+      <c r="E131" s="224" t="n"/>
+      <c r="F131" s="224" t="n"/>
+      <c r="G131" s="224" t="n"/>
+      <c r="H131" s="224" t="n"/>
+      <c r="I131" s="224" t="n"/>
+      <c r="J131" s="225" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="1" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="104">
+  <mergeCells count="111">
     <mergeCell ref="B67:J67"/>
     <mergeCell ref="B61:J61"/>
     <mergeCell ref="B101:J101"/>
@@ -8731,6 +10261,7 @@
     <mergeCell ref="B38:J38"/>
     <mergeCell ref="B78:J78"/>
     <mergeCell ref="B112:J112"/>
+    <mergeCell ref="A130:J130"/>
     <mergeCell ref="B49:J49"/>
     <mergeCell ref="B55:J55"/>
     <mergeCell ref="B64:J64"/>
@@ -8780,10 +10311,12 @@
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="B57:J57"/>
     <mergeCell ref="B88:J88"/>
+    <mergeCell ref="A125:J125"/>
     <mergeCell ref="B44:J44"/>
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="B28:J28"/>
+    <mergeCell ref="A127:J127"/>
     <mergeCell ref="B99:J99"/>
     <mergeCell ref="B9:J9"/>
     <mergeCell ref="B83:J83"/>
@@ -8803,8 +10336,11 @@
     <mergeCell ref="B70:J70"/>
     <mergeCell ref="B48:J48"/>
     <mergeCell ref="B111:J111"/>
+    <mergeCell ref="A131:J131"/>
+    <mergeCell ref="A126:J126"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A129:J129"/>
     <mergeCell ref="B73:J73"/>
     <mergeCell ref="B10:J10"/>
     <mergeCell ref="B65:J65"/>
@@ -8816,6 +10352,7 @@
     <mergeCell ref="B110:J110"/>
     <mergeCell ref="B113:J113"/>
     <mergeCell ref="B91:J91"/>
+    <mergeCell ref="A128:J128"/>
     <mergeCell ref="B100:J100"/>
     <mergeCell ref="B22:J22"/>
     <mergeCell ref="B115:J115"/>
@@ -9775,7 +11312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.7109375" customWidth="1" min="1" max="1"/>
@@ -11256,6 +12793,33 @@
         </is>
       </c>
       <c r="F51" s="60" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="178" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="B52" s="178" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="C52" s="178" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D52" s="178" t="inlineStr">
+        <is>
+          <t>Partners</t>
+        </is>
+      </c>
+      <c r="E52" s="178" t="inlineStr">
+        <is>
+          <t>rose</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A8:F52"/>
@@ -11349,7 +12913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P260"/>
+  <dimension ref="A1:P280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -20877,6 +22441,1050 @@
         <is>
           <t>—</t>
         </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="164" t="inlineStr">
+        <is>
+          <t>SH01</t>
+        </is>
+      </c>
+      <c r="B261" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C261" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D261" s="164" t="inlineStr">
+        <is>
+          <t>سعید بابایی</t>
+        </is>
+      </c>
+      <c r="E261" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3301</t>
+        </is>
+      </c>
+      <c r="F261" s="164" t="inlineStr">
+        <is>
+          <t>0911-112-3344</t>
+        </is>
+      </c>
+      <c r="G261" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K261">
+        <f>IF($A261="","",IF(LEFT($A261,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>کیوی — شراکت فصلی · نسبت شریک 50٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="164" t="inlineStr">
+        <is>
+          <t>SH02</t>
+        </is>
+      </c>
+      <c r="B262" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C262" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D262" s="164" t="inlineStr">
+        <is>
+          <t>رحمت‌الله اکبری</t>
+        </is>
+      </c>
+      <c r="E262" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3302</t>
+        </is>
+      </c>
+      <c r="F262" s="164" t="inlineStr">
+        <is>
+          <t>0911-223-4455</t>
+        </is>
+      </c>
+      <c r="G262" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K262">
+        <f>IF($A262="","",IF(LEFT($A262,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>پرتقال تامسون · نسبت شریک 40٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="164" t="inlineStr">
+        <is>
+          <t>SH03</t>
+        </is>
+      </c>
+      <c r="B263" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C263" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D263" s="164" t="inlineStr">
+        <is>
+          <t>مهدی رستمی</t>
+        </is>
+      </c>
+      <c r="E263" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3303</t>
+        </is>
+      </c>
+      <c r="F263" s="164" t="inlineStr">
+        <is>
+          <t>0911-334-5566</t>
+        </is>
+      </c>
+      <c r="G263" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K263">
+        <f>IF($A263="","",IF(LEFT($A263,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>نارنگی پیش‌رس · نسبت شریک 35٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="164" t="inlineStr">
+        <is>
+          <t>SH04</t>
+        </is>
+      </c>
+      <c r="B264" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C264" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D264" s="164" t="inlineStr">
+        <is>
+          <t>حسین نیک‌پور</t>
+        </is>
+      </c>
+      <c r="E264" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3304</t>
+        </is>
+      </c>
+      <c r="F264" s="164" t="inlineStr">
+        <is>
+          <t>0911-445-6677</t>
+        </is>
+      </c>
+      <c r="G264" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K264">
+        <f>IF($A264="","",IF(LEFT($A264,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>کیوی — سردخانه · نسبت شریک 50٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="164" t="inlineStr">
+        <is>
+          <t>SH05</t>
+        </is>
+      </c>
+      <c r="B265" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C265" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D265" s="164" t="inlineStr">
+        <is>
+          <t>کریم صادقی</t>
+        </is>
+      </c>
+      <c r="E265" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3305</t>
+        </is>
+      </c>
+      <c r="F265" s="164" t="inlineStr">
+        <is>
+          <t>0911-556-7788</t>
+        </is>
+      </c>
+      <c r="G265" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K265">
+        <f>IF($A265="","",IF(LEFT($A265,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>پرتقال خونی · نسبت شریک 30٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="164" t="inlineStr">
+        <is>
+          <t>SH06</t>
+        </is>
+      </c>
+      <c r="B266" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C266" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D266" s="164" t="inlineStr">
+        <is>
+          <t>عباس موسوی</t>
+        </is>
+      </c>
+      <c r="E266" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3306</t>
+        </is>
+      </c>
+      <c r="F266" s="164" t="inlineStr">
+        <is>
+          <t>0911-667-8899</t>
+        </is>
+      </c>
+      <c r="G266" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K266">
+        <f>IF($A266="","",IF(LEFT($A266,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>نارنگی — صادراتی · نسبت شریک 45٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="164" t="inlineStr">
+        <is>
+          <t>SH07</t>
+        </is>
+      </c>
+      <c r="B267" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C267" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D267" s="164" t="inlineStr">
+        <is>
+          <t>رضا کاظمی</t>
+        </is>
+      </c>
+      <c r="E267" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3307</t>
+        </is>
+      </c>
+      <c r="F267" s="164" t="inlineStr">
+        <is>
+          <t>0911-778-9900</t>
+        </is>
+      </c>
+      <c r="G267" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K267">
+        <f>IF($A267="","",IF(LEFT($A267,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>کیوی · نسبت شریک 50٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="164" t="inlineStr">
+        <is>
+          <t>SH08</t>
+        </is>
+      </c>
+      <c r="B268" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C268" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D268" s="164" t="inlineStr">
+        <is>
+          <t>مجید قاسمی</t>
+        </is>
+      </c>
+      <c r="E268" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3308</t>
+        </is>
+      </c>
+      <c r="F268" s="164" t="inlineStr">
+        <is>
+          <t>0911-889-0011</t>
+        </is>
+      </c>
+      <c r="G268" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K268">
+        <f>IF($A268="","",IF(LEFT($A268,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>پرتقال والنسیا · نسبت شریک 40٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="164" t="inlineStr">
+        <is>
+          <t>SH09</t>
+        </is>
+      </c>
+      <c r="B269" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C269" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D269" s="164" t="inlineStr">
+        <is>
+          <t>علی شریفی</t>
+        </is>
+      </c>
+      <c r="E269" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3309</t>
+        </is>
+      </c>
+      <c r="F269" s="164" t="inlineStr">
+        <is>
+          <t>0911-990-1122</t>
+        </is>
+      </c>
+      <c r="G269" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K269">
+        <f>IF($A269="","",IF(LEFT($A269,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>نارنج · نسبت شریک 25٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="164" t="inlineStr">
+        <is>
+          <t>SH10</t>
+        </is>
+      </c>
+      <c r="B270" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C270" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D270" s="164" t="inlineStr">
+        <is>
+          <t>ناصر رحیمی</t>
+        </is>
+      </c>
+      <c r="E270" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3310</t>
+        </is>
+      </c>
+      <c r="F270" s="164" t="inlineStr">
+        <is>
+          <t>0911-101-2233</t>
+        </is>
+      </c>
+      <c r="G270" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K270">
+        <f>IF($A270="","",IF(LEFT($A270,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>کیوی — درجه یک · نسبت شریک 50٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="164" t="inlineStr">
+        <is>
+          <t>SH11</t>
+        </is>
+      </c>
+      <c r="B271" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C271" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D271" s="164" t="inlineStr">
+        <is>
+          <t>بابک سلطانی</t>
+        </is>
+      </c>
+      <c r="E271" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3311</t>
+        </is>
+      </c>
+      <c r="F271" s="164" t="inlineStr">
+        <is>
+          <t>0911-212-3344</t>
+        </is>
+      </c>
+      <c r="G271" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K271">
+        <f>IF($A271="","",IF(LEFT($A271,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>پرتقال — میدان بار · نسبت شریک 35٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="164" t="inlineStr">
+        <is>
+          <t>SH12</t>
+        </is>
+      </c>
+      <c r="B272" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C272" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D272" s="164" t="inlineStr">
+        <is>
+          <t>جواد کریمی</t>
+        </is>
+      </c>
+      <c r="E272" s="164" t="inlineStr">
+        <is>
+          <t>011-4221-3312</t>
+        </is>
+      </c>
+      <c r="F272" s="164" t="inlineStr">
+        <is>
+          <t>0911-323-4455</t>
+        </is>
+      </c>
+      <c r="G272" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K272">
+        <f>IF($A272="","",IF(LEFT($A272,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>کیوی — صادراتی · نسبت شریک 60٪</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="164" t="inlineStr">
+        <is>
+          <t>SH13</t>
+        </is>
+      </c>
+      <c r="B273" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C273" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D273" s="164" t="inlineStr"/>
+      <c r="E273" s="164" t="inlineStr"/>
+      <c r="F273" s="164" t="inlineStr"/>
+      <c r="G273" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K273">
+        <f>IF($A273="","",IF(LEFT($A273,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="164" t="inlineStr">
+        <is>
+          <t>SH14</t>
+        </is>
+      </c>
+      <c r="B274" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C274" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D274" s="164" t="inlineStr"/>
+      <c r="E274" s="164" t="inlineStr"/>
+      <c r="F274" s="164" t="inlineStr"/>
+      <c r="G274" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>0</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K274">
+        <f>IF($A274="","",IF(LEFT($A274,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="164" t="inlineStr">
+        <is>
+          <t>SH15</t>
+        </is>
+      </c>
+      <c r="B275" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C275" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D275" s="164" t="inlineStr"/>
+      <c r="E275" s="164" t="inlineStr"/>
+      <c r="F275" s="164" t="inlineStr"/>
+      <c r="G275" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K275">
+        <f>IF($A275="","",IF(LEFT($A275,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="164" t="inlineStr">
+        <is>
+          <t>SH16</t>
+        </is>
+      </c>
+      <c r="B276" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C276" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D276" s="164" t="inlineStr"/>
+      <c r="E276" s="164" t="inlineStr"/>
+      <c r="F276" s="164" t="inlineStr"/>
+      <c r="G276" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K276">
+        <f>IF($A276="","",IF(LEFT($A276,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="164" t="inlineStr">
+        <is>
+          <t>SH17</t>
+        </is>
+      </c>
+      <c r="B277" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C277" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D277" s="164" t="inlineStr"/>
+      <c r="E277" s="164" t="inlineStr"/>
+      <c r="F277" s="164" t="inlineStr"/>
+      <c r="G277" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K277">
+        <f>IF($A277="","",IF(LEFT($A277,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="164" t="inlineStr">
+        <is>
+          <t>SH18</t>
+        </is>
+      </c>
+      <c r="B278" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C278" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D278" s="164" t="inlineStr"/>
+      <c r="E278" s="164" t="inlineStr"/>
+      <c r="F278" s="164" t="inlineStr"/>
+      <c r="G278" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K278">
+        <f>IF($A278="","",IF(LEFT($A278,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="164" t="inlineStr">
+        <is>
+          <t>SH19</t>
+        </is>
+      </c>
+      <c r="B279" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C279" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D279" s="164" t="inlineStr"/>
+      <c r="E279" s="164" t="inlineStr"/>
+      <c r="F279" s="164" t="inlineStr"/>
+      <c r="G279" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K279">
+        <f>IF($A279="","",IF(LEFT($A279,2)="SH","شرکا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="164" t="inlineStr">
+        <is>
+          <t>SH20</t>
+        </is>
+      </c>
+      <c r="B280" s="164" t="inlineStr">
+        <is>
+          <t>شرکا</t>
+        </is>
+      </c>
+      <c r="C280" s="164" t="inlineStr">
+        <is>
+          <t>شراکت</t>
+        </is>
+      </c>
+      <c r="D280" s="164" t="inlineStr"/>
+      <c r="E280" s="164" t="inlineStr"/>
+      <c r="F280" s="164" t="inlineStr"/>
+      <c r="G280" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>طرف حساب</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K280">
+        <f>IF($A280="","",IF(LEFT($A280,2)="SH","شرکا",""))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -20975,6 +23583,1132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
+        <is>
+          <t>مازندشت  ·  سورتینگ و بسته‌بندی مرکبات    ·    MAZANDASHT  ·  CITRUS SORTING &amp; PACKING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ◈  شراکت — شرکا و نسبت سهم</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="181" t="inlineStr">
+        <is>
+          <t>هر شریک یک کد SHxx، یک نام و یک «نسبت سهم شریک» دارد  ·  نسبت شرکت خودکار = ۱۰۰ منهای آن  ·  همین جدول، کشوی باسکول و پرداخت‌ها را می‌سازد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1">
+      <c r="A4" s="182" t="n"/>
+      <c r="B4" s="182" t="n"/>
+      <c r="C4" s="182" t="n"/>
+      <c r="D4" s="182" t="n"/>
+      <c r="E4" s="182" t="n"/>
+      <c r="F4" s="182" t="n"/>
+      <c r="G4" s="182" t="n"/>
+      <c r="H4" s="182" t="n"/>
+      <c r="I4" s="182" t="n"/>
+      <c r="J4" s="182" t="n"/>
+      <c r="K4" s="182" t="n"/>
+    </row>
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="183" t="inlineStr">
+        <is>
+          <t>شرکای تعریف‌شده</t>
+        </is>
+      </c>
+      <c r="B6" s="154" t="n"/>
+      <c r="C6" s="155" t="n"/>
+      <c r="D6" s="183" t="inlineStr">
+        <is>
+          <t>شرکای فعال</t>
+        </is>
+      </c>
+      <c r="E6" s="155" t="n"/>
+      <c r="F6" s="183" t="inlineStr">
+        <is>
+          <t>میانگین نسبت شریک</t>
+        </is>
+      </c>
+      <c r="G6" s="155" t="n"/>
+      <c r="H6" s="183" t="inlineStr">
+        <is>
+          <t>جمع نسبت شرکت</t>
+        </is>
+      </c>
+      <c r="I6" s="155" t="n"/>
+      <c r="J6" s="183" t="inlineStr">
+        <is>
+          <t>موضوع‌های شراکت</t>
+        </is>
+      </c>
+      <c r="K6" s="155" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="185">
+        <f>COUNTIF($B$12:$B$31,"?*")</f>
+        <v/>
+      </c>
+      <c r="B7" s="154" t="n"/>
+      <c r="C7" s="155" t="n"/>
+      <c r="D7" s="187">
+        <f>COUNTIFS($B$12:$B$31,"?*",$J$12:$J$31,"فعال")</f>
+        <v/>
+      </c>
+      <c r="E7" s="155" t="n"/>
+      <c r="F7" s="188">
+        <f>IFERROR(ROUND(AVERAGE($C$12:$C$31),0),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="155" t="n"/>
+      <c r="H7" s="189">
+        <f>SUM($D$12:$D$31)</f>
+        <v/>
+      </c>
+      <c r="I7" s="155" t="n"/>
+      <c r="J7" s="190">
+        <f>COUNTIF($E$12:$E$31,"?*")</f>
+        <v/>
+      </c>
+      <c r="K7" s="155" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="218" t="inlineStr">
+        <is>
+          <t>فهرست شرکا   کدها را تغییر ندهید؛ نام و نسبت را آزادانه به‌روز کنید</t>
+        </is>
+      </c>
+      <c r="B9" s="192" t="n"/>
+      <c r="C9" s="192" t="n"/>
+      <c r="D9" s="192" t="n"/>
+      <c r="E9" s="192" t="n"/>
+      <c r="F9" s="192" t="n"/>
+      <c r="G9" s="192" t="n"/>
+      <c r="H9" s="192" t="n"/>
+      <c r="I9" s="192" t="n"/>
+      <c r="J9" s="192" t="n"/>
+      <c r="K9" s="193" t="inlineStr">
+        <is>
+          <t>۰۱</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="194" t="inlineStr">
+        <is>
+          <t>کد شریک</t>
+        </is>
+      </c>
+      <c r="B10" s="194" t="inlineStr">
+        <is>
+          <t>نام شریک</t>
+        </is>
+      </c>
+      <c r="C10" s="194" t="inlineStr">
+        <is>
+          <t>نسبت سهم شریک ٪</t>
+        </is>
+      </c>
+      <c r="D10" s="194" t="inlineStr">
+        <is>
+          <t>نسبت سهم شرکت ٪</t>
+        </is>
+      </c>
+      <c r="E10" s="194" t="inlineStr">
+        <is>
+          <t>موضوع شراکت</t>
+        </is>
+      </c>
+      <c r="F10" s="194" t="inlineStr">
+        <is>
+          <t>محصول</t>
+        </is>
+      </c>
+      <c r="G10" s="194" t="inlineStr">
+        <is>
+          <t>تلفن</t>
+        </is>
+      </c>
+      <c r="H10" s="194" t="inlineStr">
+        <is>
+          <t>همراه</t>
+        </is>
+      </c>
+      <c r="I10" s="194" t="inlineStr">
+        <is>
+          <t>بانک تسویه</t>
+        </is>
+      </c>
+      <c r="J10" s="194" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="K10" s="194" t="inlineStr">
+        <is>
+          <t>توضیح</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="195" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B11" s="195" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C11" s="195" t="inlineStr">
+        <is>
+          <t>Partner %</t>
+        </is>
+      </c>
+      <c r="D11" s="195" t="inlineStr">
+        <is>
+          <t>Our %</t>
+        </is>
+      </c>
+      <c r="E11" s="195" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F11" s="195" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G11" s="195" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="H11" s="195" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I11" s="195" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="J11" s="195" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K11" s="195" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="196" t="inlineStr">
+        <is>
+          <t>SH01</t>
+        </is>
+      </c>
+      <c r="B12" s="197" t="inlineStr">
+        <is>
+          <t>سعید بابایی</t>
+        </is>
+      </c>
+      <c r="C12" s="198" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="199">
+        <f>IF($C12="","",100-$C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="197" t="inlineStr">
+        <is>
+          <t>کیوی — شراکت فصلی</t>
+        </is>
+      </c>
+      <c r="F12" s="200" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="G12" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3301</t>
+        </is>
+      </c>
+      <c r="H12" s="200" t="inlineStr">
+        <is>
+          <t>0911-112-3344</t>
+        </is>
+      </c>
+      <c r="I12" s="201" t="inlineStr">
+        <is>
+          <t>BN02</t>
+        </is>
+      </c>
+      <c r="J12" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K12" s="200" t="inlineStr">
+        <is>
+          <t>شریک اصلی کیوی؛ خرید و فروش مشترک</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="196" t="inlineStr">
+        <is>
+          <t>SH02</t>
+        </is>
+      </c>
+      <c r="B13" s="197" t="inlineStr">
+        <is>
+          <t>رحمت‌الله اکبری</t>
+        </is>
+      </c>
+      <c r="C13" s="198" t="n">
+        <v>40</v>
+      </c>
+      <c r="D13" s="199">
+        <f>IF($C13="","",100-$C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="197" t="inlineStr">
+        <is>
+          <t>پرتقال تامسون</t>
+        </is>
+      </c>
+      <c r="F13" s="200" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="G13" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3302</t>
+        </is>
+      </c>
+      <c r="H13" s="200" t="inlineStr">
+        <is>
+          <t>0911-223-4455</t>
+        </is>
+      </c>
+      <c r="I13" s="201" t="inlineStr">
+        <is>
+          <t>BN01</t>
+        </is>
+      </c>
+      <c r="J13" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K13" s="200" t="inlineStr">
+        <is>
+          <t>شراکت در خرید تامسون باغ‌های شرق</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="196" t="inlineStr">
+        <is>
+          <t>SH03</t>
+        </is>
+      </c>
+      <c r="B14" s="197" t="inlineStr">
+        <is>
+          <t>مهدی رستمی</t>
+        </is>
+      </c>
+      <c r="C14" s="198" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" s="199">
+        <f>IF($C14="","",100-$C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="197" t="inlineStr">
+        <is>
+          <t>نارنگی پیش‌رس</t>
+        </is>
+      </c>
+      <c r="F14" s="200" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="G14" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3303</t>
+        </is>
+      </c>
+      <c r="H14" s="200" t="inlineStr">
+        <is>
+          <t>0911-334-5566</t>
+        </is>
+      </c>
+      <c r="I14" s="201" t="inlineStr">
+        <is>
+          <t>BN03</t>
+        </is>
+      </c>
+      <c r="J14" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K14" s="200" t="inlineStr">
+        <is>
+          <t>نارنگی؛ تسویه ماهانه</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="196" t="inlineStr">
+        <is>
+          <t>SH04</t>
+        </is>
+      </c>
+      <c r="B15" s="197" t="inlineStr">
+        <is>
+          <t>حسین نیک‌پور</t>
+        </is>
+      </c>
+      <c r="C15" s="198" t="n">
+        <v>50</v>
+      </c>
+      <c r="D15" s="199">
+        <f>IF($C15="","",100-$C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="197" t="inlineStr">
+        <is>
+          <t>کیوی — سردخانه</t>
+        </is>
+      </c>
+      <c r="F15" s="200" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="G15" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3304</t>
+        </is>
+      </c>
+      <c r="H15" s="200" t="inlineStr">
+        <is>
+          <t>0911-445-6677</t>
+        </is>
+      </c>
+      <c r="I15" s="201" t="inlineStr">
+        <is>
+          <t>BN02</t>
+        </is>
+      </c>
+      <c r="J15" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K15" s="200" t="inlineStr">
+        <is>
+          <t>کیوی سردخانه‌ای</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="196" t="inlineStr">
+        <is>
+          <t>SH05</t>
+        </is>
+      </c>
+      <c r="B16" s="197" t="inlineStr">
+        <is>
+          <t>کریم صادقی</t>
+        </is>
+      </c>
+      <c r="C16" s="198" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="199">
+        <f>IF($C16="","",100-$C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="197" t="inlineStr">
+        <is>
+          <t>پرتقال خونی</t>
+        </is>
+      </c>
+      <c r="F16" s="200" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="G16" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3305</t>
+        </is>
+      </c>
+      <c r="H16" s="200" t="inlineStr">
+        <is>
+          <t>0911-556-7788</t>
+        </is>
+      </c>
+      <c r="I16" s="201" t="inlineStr">
+        <is>
+          <t>BN04</t>
+        </is>
+      </c>
+      <c r="J16" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K16" s="200" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="196" t="inlineStr">
+        <is>
+          <t>SH06</t>
+        </is>
+      </c>
+      <c r="B17" s="197" t="inlineStr">
+        <is>
+          <t>عباس موسوی</t>
+        </is>
+      </c>
+      <c r="C17" s="198" t="n">
+        <v>45</v>
+      </c>
+      <c r="D17" s="199">
+        <f>IF($C17="","",100-$C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="197" t="inlineStr">
+        <is>
+          <t>نارنگی — صادراتی</t>
+        </is>
+      </c>
+      <c r="F17" s="200" t="inlineStr">
+        <is>
+          <t>نارنگی</t>
+        </is>
+      </c>
+      <c r="G17" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3306</t>
+        </is>
+      </c>
+      <c r="H17" s="200" t="inlineStr">
+        <is>
+          <t>0911-667-8899</t>
+        </is>
+      </c>
+      <c r="I17" s="201" t="inlineStr">
+        <is>
+          <t>BN01</t>
+        </is>
+      </c>
+      <c r="J17" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K17" s="200" t="inlineStr">
+        <is>
+          <t>بار صادراتی مشترک</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="196" t="inlineStr">
+        <is>
+          <t>SH07</t>
+        </is>
+      </c>
+      <c r="B18" s="197" t="inlineStr">
+        <is>
+          <t>رضا کاظمی</t>
+        </is>
+      </c>
+      <c r="C18" s="198" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="199">
+        <f>IF($C18="","",100-$C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="197" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="F18" s="200" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="G18" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3307</t>
+        </is>
+      </c>
+      <c r="H18" s="200" t="inlineStr">
+        <is>
+          <t>0911-778-9900</t>
+        </is>
+      </c>
+      <c r="I18" s="201" t="inlineStr">
+        <is>
+          <t>BN03</t>
+        </is>
+      </c>
+      <c r="J18" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K18" s="200" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="196" t="inlineStr">
+        <is>
+          <t>SH08</t>
+        </is>
+      </c>
+      <c r="B19" s="197" t="inlineStr">
+        <is>
+          <t>مجید قاسمی</t>
+        </is>
+      </c>
+      <c r="C19" s="198" t="n">
+        <v>40</v>
+      </c>
+      <c r="D19" s="199">
+        <f>IF($C19="","",100-$C19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="197" t="inlineStr">
+        <is>
+          <t>پرتقال والنسیا</t>
+        </is>
+      </c>
+      <c r="F19" s="200" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="G19" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3308</t>
+        </is>
+      </c>
+      <c r="H19" s="200" t="inlineStr">
+        <is>
+          <t>0911-889-0011</t>
+        </is>
+      </c>
+      <c r="I19" s="201" t="inlineStr">
+        <is>
+          <t>BN02</t>
+        </is>
+      </c>
+      <c r="J19" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K19" s="200" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="196" t="inlineStr">
+        <is>
+          <t>SH09</t>
+        </is>
+      </c>
+      <c r="B20" s="197" t="inlineStr">
+        <is>
+          <t>علی شریفی</t>
+        </is>
+      </c>
+      <c r="C20" s="198" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="199">
+        <f>IF($C20="","",100-$C20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="197" t="inlineStr">
+        <is>
+          <t>نارنج</t>
+        </is>
+      </c>
+      <c r="F20" s="200" t="inlineStr">
+        <is>
+          <t>نارنج</t>
+        </is>
+      </c>
+      <c r="G20" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3309</t>
+        </is>
+      </c>
+      <c r="H20" s="200" t="inlineStr">
+        <is>
+          <t>0911-990-1122</t>
+        </is>
+      </c>
+      <c r="I20" s="201" t="inlineStr">
+        <is>
+          <t>BN04</t>
+        </is>
+      </c>
+      <c r="J20" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K20" s="200" t="inlineStr">
+        <is>
+          <t>نارنج؛ شراکت کوچک</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="196" t="inlineStr">
+        <is>
+          <t>SH10</t>
+        </is>
+      </c>
+      <c r="B21" s="197" t="inlineStr">
+        <is>
+          <t>ناصر رحیمی</t>
+        </is>
+      </c>
+      <c r="C21" s="198" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" s="199">
+        <f>IF($C21="","",100-$C21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="197" t="inlineStr">
+        <is>
+          <t>کیوی — درجه یک</t>
+        </is>
+      </c>
+      <c r="F21" s="200" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="G21" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3310</t>
+        </is>
+      </c>
+      <c r="H21" s="200" t="inlineStr">
+        <is>
+          <t>0911-101-2233</t>
+        </is>
+      </c>
+      <c r="I21" s="201" t="inlineStr">
+        <is>
+          <t>BN01</t>
+        </is>
+      </c>
+      <c r="J21" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K21" s="200" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="196" t="inlineStr">
+        <is>
+          <t>SH11</t>
+        </is>
+      </c>
+      <c r="B22" s="197" t="inlineStr">
+        <is>
+          <t>بابک سلطانی</t>
+        </is>
+      </c>
+      <c r="C22" s="198" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" s="199">
+        <f>IF($C22="","",100-$C22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="197" t="inlineStr">
+        <is>
+          <t>پرتقال — میدان بار</t>
+        </is>
+      </c>
+      <c r="F22" s="200" t="inlineStr">
+        <is>
+          <t>پرتقال</t>
+        </is>
+      </c>
+      <c r="G22" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3311</t>
+        </is>
+      </c>
+      <c r="H22" s="200" t="inlineStr">
+        <is>
+          <t>0911-212-3344</t>
+        </is>
+      </c>
+      <c r="I22" s="201" t="inlineStr">
+        <is>
+          <t>BN03</t>
+        </is>
+      </c>
+      <c r="J22" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K22" s="200" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="196" t="inlineStr">
+        <is>
+          <t>SH12</t>
+        </is>
+      </c>
+      <c r="B23" s="197" t="inlineStr">
+        <is>
+          <t>جواد کریمی</t>
+        </is>
+      </c>
+      <c r="C23" s="198" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="199">
+        <f>IF($C23="","",100-$C23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="197" t="inlineStr">
+        <is>
+          <t>کیوی — صادراتی</t>
+        </is>
+      </c>
+      <c r="F23" s="200" t="inlineStr">
+        <is>
+          <t>کیوی</t>
+        </is>
+      </c>
+      <c r="G23" s="200" t="inlineStr">
+        <is>
+          <t>011-4221-3312</t>
+        </is>
+      </c>
+      <c r="H23" s="200" t="inlineStr">
+        <is>
+          <t>0911-323-4455</t>
+        </is>
+      </c>
+      <c r="I23" s="201" t="inlineStr">
+        <is>
+          <t>BN02</t>
+        </is>
+      </c>
+      <c r="J23" s="202" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+      <c r="K23" s="200" t="inlineStr">
+        <is>
+          <t>سهم شریک ۶۰٪ — قرارداد کتبی</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="203" t="inlineStr">
+        <is>
+          <t>SH13</t>
+        </is>
+      </c>
+      <c r="B24" s="204" t="inlineStr"/>
+      <c r="C24" s="205" t="n"/>
+      <c r="D24" s="206">
+        <f>IF($C24="","",100-$C24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="204" t="inlineStr"/>
+      <c r="F24" s="204" t="inlineStr"/>
+      <c r="G24" s="204" t="inlineStr"/>
+      <c r="H24" s="204" t="inlineStr"/>
+      <c r="I24" s="203" t="inlineStr"/>
+      <c r="J24" s="205" t="n"/>
+      <c r="K24" s="204" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="203" t="inlineStr">
+        <is>
+          <t>SH14</t>
+        </is>
+      </c>
+      <c r="B25" s="204" t="inlineStr"/>
+      <c r="C25" s="205" t="n"/>
+      <c r="D25" s="206">
+        <f>IF($C25="","",100-$C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="204" t="inlineStr"/>
+      <c r="F25" s="204" t="inlineStr"/>
+      <c r="G25" s="204" t="inlineStr"/>
+      <c r="H25" s="204" t="inlineStr"/>
+      <c r="I25" s="203" t="inlineStr"/>
+      <c r="J25" s="205" t="n"/>
+      <c r="K25" s="204" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="203" t="inlineStr">
+        <is>
+          <t>SH15</t>
+        </is>
+      </c>
+      <c r="B26" s="204" t="inlineStr"/>
+      <c r="C26" s="205" t="n"/>
+      <c r="D26" s="206">
+        <f>IF($C26="","",100-$C26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="204" t="inlineStr"/>
+      <c r="F26" s="204" t="inlineStr"/>
+      <c r="G26" s="204" t="inlineStr"/>
+      <c r="H26" s="204" t="inlineStr"/>
+      <c r="I26" s="203" t="inlineStr"/>
+      <c r="J26" s="205" t="n"/>
+      <c r="K26" s="204" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="203" t="inlineStr">
+        <is>
+          <t>SH16</t>
+        </is>
+      </c>
+      <c r="B27" s="204" t="inlineStr"/>
+      <c r="C27" s="205" t="n"/>
+      <c r="D27" s="206">
+        <f>IF($C27="","",100-$C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="204" t="inlineStr"/>
+      <c r="F27" s="204" t="inlineStr"/>
+      <c r="G27" s="204" t="inlineStr"/>
+      <c r="H27" s="204" t="inlineStr"/>
+      <c r="I27" s="203" t="inlineStr"/>
+      <c r="J27" s="205" t="n"/>
+      <c r="K27" s="204" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="203" t="inlineStr">
+        <is>
+          <t>SH17</t>
+        </is>
+      </c>
+      <c r="B28" s="204" t="inlineStr"/>
+      <c r="C28" s="205" t="n"/>
+      <c r="D28" s="206">
+        <f>IF($C28="","",100-$C28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="204" t="inlineStr"/>
+      <c r="F28" s="204" t="inlineStr"/>
+      <c r="G28" s="204" t="inlineStr"/>
+      <c r="H28" s="204" t="inlineStr"/>
+      <c r="I28" s="203" t="inlineStr"/>
+      <c r="J28" s="205" t="n"/>
+      <c r="K28" s="204" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="203" t="inlineStr">
+        <is>
+          <t>SH18</t>
+        </is>
+      </c>
+      <c r="B29" s="204" t="inlineStr"/>
+      <c r="C29" s="205" t="n"/>
+      <c r="D29" s="206">
+        <f>IF($C29="","",100-$C29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="204" t="inlineStr"/>
+      <c r="F29" s="204" t="inlineStr"/>
+      <c r="G29" s="204" t="inlineStr"/>
+      <c r="H29" s="204" t="inlineStr"/>
+      <c r="I29" s="203" t="inlineStr"/>
+      <c r="J29" s="205" t="n"/>
+      <c r="K29" s="204" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="203" t="inlineStr">
+        <is>
+          <t>SH19</t>
+        </is>
+      </c>
+      <c r="B30" s="204" t="inlineStr"/>
+      <c r="C30" s="205" t="n"/>
+      <c r="D30" s="206">
+        <f>IF($C30="","",100-$C30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="204" t="inlineStr"/>
+      <c r="F30" s="204" t="inlineStr"/>
+      <c r="G30" s="204" t="inlineStr"/>
+      <c r="H30" s="204" t="inlineStr"/>
+      <c r="I30" s="203" t="inlineStr"/>
+      <c r="J30" s="205" t="n"/>
+      <c r="K30" s="204" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="203" t="inlineStr">
+        <is>
+          <t>SH20</t>
+        </is>
+      </c>
+      <c r="B31" s="204" t="inlineStr"/>
+      <c r="C31" s="205" t="n"/>
+      <c r="D31" s="206">
+        <f>IF($C31="","",100-$C31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="204" t="inlineStr"/>
+      <c r="F31" s="204" t="inlineStr"/>
+      <c r="G31" s="204" t="inlineStr"/>
+      <c r="H31" s="204" t="inlineStr"/>
+      <c r="I31" s="203" t="inlineStr"/>
+      <c r="J31" s="205" t="n"/>
+      <c r="K31" s="204" t="inlineStr"/>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   قاعده: سهم شریک از «وزن» محاسبه می‌شود. در باسکول، عملیات «خرید شراکتی (ورود)» یا «فروش شراکتی (خروج)» را بزنید و کد شریک را در ستون طرف حساب انتخاب کنید؛ سیستم وزن و مبلغ را به دو سهم تقسیم می‌کند و فقط سهم شرکت را سند می‌زند.</t>
+        </is>
+      </c>
+      <c r="B33" s="220" t="n"/>
+      <c r="C33" s="220" t="n"/>
+      <c r="D33" s="220" t="n"/>
+      <c r="E33" s="220" t="n"/>
+      <c r="F33" s="220" t="n"/>
+      <c r="G33" s="220" t="n"/>
+      <c r="H33" s="220" t="n"/>
+      <c r="I33" s="220" t="n"/>
+      <c r="J33" s="220" t="n"/>
+      <c r="K33" s="220" t="n"/>
+    </row>
+    <row r="34" ht="38" customHeight="1">
+      <c r="A34" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   پرداخت به شریک = سهم واریزی ما. هر پرداخت به حساب SHxx در شیت پرداخت (01_Entry) یا تراکنش بانکی (02_Bank) ثبت شود تا مانده بدهی ما به شریک، خودکار محاسبه شود.</t>
+        </is>
+      </c>
+      <c r="B34" s="220" t="n"/>
+      <c r="C34" s="220" t="n"/>
+      <c r="D34" s="220" t="n"/>
+      <c r="E34" s="220" t="n"/>
+      <c r="F34" s="220" t="n"/>
+      <c r="G34" s="220" t="n"/>
+      <c r="H34" s="220" t="n"/>
+      <c r="I34" s="220" t="n"/>
+      <c r="J34" s="220" t="n"/>
+      <c r="K34" s="220" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="F7:G7"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="C12:C31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="نسبت شریک" error="عدد بین ۱ و ۹۹ وارد کنید (درصد سهم شریک)." promptTitle="نسبت سهم شریک" prompt="مثلاً 50 یعنی نصف بار و مبلغ سهم شریک است و نصف دیگر سهم شرکت." type="decimal" operator="between">
+      <formula1>1</formula1>
+      <formula2>99</formula2>
+    </dataValidation>
+    <dataValidation sqref="J12:J31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"فعال,غیرفعال"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I12:I31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>Bnk!$A$10:$A$19</formula1>
+    </dataValidation>
+    <dataValidation sqref="F12:F31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>Prd!$B$10:$B$29</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 مازندشت — سامانه حسابداری سورتینگ&amp;C&amp;8 MAZANDASHT · SHRK&amp;R&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;F&amp;C&amp;8 صفحه &amp;P از &amp;N&amp;R&amp;8 نسخه ۰۴ · ۱۴۰۵</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -22653,7 +26387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFC4623F"/>
@@ -24710,23 +28444,79 @@
           <t>OP20</t>
         </is>
       </c>
-      <c r="B29" s="77" t="n"/>
-      <c r="C29" s="59" t="n"/>
-      <c r="D29" s="59" t="n"/>
-      <c r="E29" s="59" t="n"/>
-      <c r="F29" s="59" t="n"/>
-      <c r="G29" s="59" t="n"/>
-      <c r="H29" s="59" t="n"/>
-      <c r="I29" s="59" t="n"/>
-      <c r="J29" s="59" t="n"/>
-      <c r="K29" s="59" t="n"/>
-      <c r="L29" s="59" t="n"/>
+      <c r="B29" s="77" t="inlineStr">
+        <is>
+          <t>خرید شراکتی (ورود)</t>
+        </is>
+      </c>
+      <c r="C29" s="59" t="inlineStr">
+        <is>
+          <t>ورود</t>
+        </is>
+      </c>
+      <c r="D29" s="59" t="inlineStr">
+        <is>
+          <t>خرید</t>
+        </is>
+      </c>
+      <c r="E29" s="59" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="F29" s="59" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G29" s="59" t="inlineStr">
+        <is>
+          <t>وزن</t>
+        </is>
+      </c>
+      <c r="H29" s="59" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="I29" s="59" t="inlineStr">
+        <is>
+          <t>X004</t>
+        </is>
+      </c>
+      <c r="J29" s="59" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="K29" s="59" t="inlineStr">
+        <is>
+          <t>افزودن</t>
+        </is>
+      </c>
+      <c r="L29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M29" s="59" t="n"/>
       <c r="N29" s="59" t="n"/>
       <c r="O29" s="59" t="n"/>
-      <c r="P29" s="59" t="n"/>
-      <c r="Q29" s="59" t="n"/>
-      <c r="R29" s="78" t="n"/>
+      <c r="P29" s="59" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="Q29" s="59" t="inlineStr">
+        <is>
+          <t>rose</t>
+        </is>
+      </c>
+      <c r="R29" s="78" t="inlineStr">
+        <is>
+          <t>بار شراکتی که وارد انبار می‌شود. طرف حساب = شریک (کد SHxx). مبلغ = وزن خالص × فی؛ در دفتر فقط «سهم شرکت» ثبت می‌شود: بدهکار موجودی مرکبات / بستانکار حساب شریک. پرداخت‌های بعدی به شریک، همان سهم ما را تسویه می‌کند.</t>
+        </is>
+      </c>
       <c r="S29" s="79" t="n"/>
     </row>
     <row r="30" ht="33.75" customHeight="1">
@@ -24735,23 +28525,79 @@
           <t>OP21</t>
         </is>
       </c>
-      <c r="B30" s="77" t="n"/>
-      <c r="C30" s="59" t="n"/>
-      <c r="D30" s="59" t="n"/>
-      <c r="E30" s="59" t="n"/>
-      <c r="F30" s="59" t="n"/>
-      <c r="G30" s="59" t="n"/>
-      <c r="H30" s="59" t="n"/>
-      <c r="I30" s="59" t="n"/>
-      <c r="J30" s="59" t="n"/>
-      <c r="K30" s="59" t="n"/>
-      <c r="L30" s="59" t="n"/>
+      <c r="B30" s="77" t="inlineStr">
+        <is>
+          <t>فروش شراکتی (خروج)</t>
+        </is>
+      </c>
+      <c r="C30" s="59" t="inlineStr">
+        <is>
+          <t>خروج</t>
+        </is>
+      </c>
+      <c r="D30" s="59" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="E30" s="59" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="F30" s="59" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="G30" s="59" t="inlineStr">
+        <is>
+          <t>وزن</t>
+        </is>
+      </c>
+      <c r="H30" s="59" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="I30" s="59" t="inlineStr">
+        <is>
+          <t>X006</t>
+        </is>
+      </c>
+      <c r="J30" s="59" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="K30" s="59" t="inlineStr">
+        <is>
+          <t>هیچ</t>
+        </is>
+      </c>
+      <c r="L30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M30" s="59" t="n"/>
       <c r="N30" s="59" t="n"/>
       <c r="O30" s="59" t="n"/>
-      <c r="P30" s="59" t="n"/>
-      <c r="Q30" s="59" t="n"/>
-      <c r="R30" s="78" t="n"/>
+      <c r="P30" s="59" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="Q30" s="59" t="inlineStr">
+        <is>
+          <t>sky</t>
+        </is>
+      </c>
+      <c r="R30" s="78" t="inlineStr">
+        <is>
+          <t>فروش سهم شرکت از بار شراکتی. طرف حساب = خریدار. در دفتر فقط سهم شرکت ثبت می‌شود: بدهکار خریدار / بستانکار فروش مرکبات. وزن کامل بار از انبار خارج می‌شود.</t>
+        </is>
+      </c>
       <c r="S30" s="79" t="n"/>
     </row>
     <row r="31" ht="33.75" customHeight="1">
@@ -24940,7 +28786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF6B4E9E"/>
@@ -25625,806 +29471,4 @@
   </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFE0A458"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9.7109375" customWidth="1" min="1" max="1"/>
-    <col width="30.7109375" customWidth="1" min="2" max="2"/>
-    <col width="16.7109375" customWidth="1" min="3" max="3"/>
-    <col width="11.7109375" customWidth="1" min="4" max="4"/>
-    <col width="16.7109375" customWidth="1" min="5" max="5"/>
-    <col width="30.7109375" customWidth="1" min="6" max="6"/>
-    <col width="26.7109375" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" s="138" t="inlineStr">
-        <is>
-          <t>مازندشت — سورتینگ و بسته‌بندی مرکبات</t>
-        </is>
-      </c>
-      <c r="C1" s="132" t="inlineStr">
-        <is>
-          <t>MAZANDASHT  ·  CITRUS SORTING &amp; PACKING</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38.25" customHeight="1">
-      <c r="A2" s="133" t="inlineStr">
-        <is>
-          <t>محصولات — خرید و فروش</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45.75" customHeight="1">
-      <c r="A3" s="134" t="inlineStr">
-        <is>
-          <t>برای هر محصول، دسته (نوع مرکبات)، واحد و سبد پیش‌فرض تعریف می‌شود</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
-        <is>
-          <t>راهنما</t>
-        </is>
-      </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>ورود دستی</t>
-        </is>
-      </c>
-      <c r="C4" s="36" t="inlineStr">
-        <is>
-          <t>خودکار</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="inlineStr">
-        <is>
-          <t>ورود</t>
-        </is>
-      </c>
-      <c r="E4" s="38" t="inlineStr">
-        <is>
-          <t>خروج</t>
-        </is>
-      </c>
-      <c r="F4" s="50" t="inlineStr">
-        <is>
-          <t>هشدار</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>محصولات</t>
-        </is>
-      </c>
-      <c r="B5" s="108" t="n"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>پرتقال</t>
-        </is>
-      </c>
-      <c r="D5" s="108" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>نارنگی</t>
-        </is>
-      </c>
-      <c r="F5" s="108" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>لیمو</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="52">
-        <f>COUNTIF($B$10:$B$29,"?*")</f>
-        <v/>
-      </c>
-      <c r="B6" s="109" t="n"/>
-      <c r="C6" s="85">
-        <f>COUNTIF($C$10:$C$29,"پرتقال")</f>
-        <v/>
-      </c>
-      <c r="D6" s="109" t="n"/>
-      <c r="E6" s="53">
-        <f>COUNTIF($C$10:$C$29,"نارنگی")</f>
-        <v/>
-      </c>
-      <c r="F6" s="109" t="n"/>
-      <c r="G6" s="86">
-        <f>COUNTIF($C$10:$C$29,"لیمو")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="6.75" customHeight="1"/>
-    <row r="8" ht="33.75" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
-        <is>
-          <t>کد</t>
-        </is>
-      </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>نام محصول</t>
-        </is>
-      </c>
-      <c r="C8" s="42" t="inlineStr">
-        <is>
-          <t>دسته / نوع مرکبات</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>واحد</t>
-        </is>
-      </c>
-      <c r="E8" s="42" t="inlineStr">
-        <is>
-          <t>سبد پیش‌فرض</t>
-        </is>
-      </c>
-      <c r="F8" s="42" t="inlineStr">
-        <is>
-          <t>توضیح</t>
-        </is>
-      </c>
-      <c r="G8" s="42" t="inlineStr">
-        <is>
-          <t>برچسب کشویی</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D9" s="43" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>Default Basket</t>
-        </is>
-      </c>
-      <c r="F9" s="43" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="G9" s="43" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="23.25" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>PB01</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>پرتقال تامسون</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>پرتقال</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E10" s="58" t="inlineStr">
-        <is>
-          <t>BK03</t>
-        </is>
-      </c>
-      <c r="F10" s="60" t="inlineStr">
-        <is>
-          <t>خرید از باغ / میدان بار</t>
-        </is>
-      </c>
-      <c r="G10" s="84">
-        <f>IF($B10="","",$B10&amp;" – "&amp;$C10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="23.25" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>PB02</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="inlineStr">
-        <is>
-          <t>پرتقال خونی</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="inlineStr">
-        <is>
-          <t>پرتقال</t>
-        </is>
-      </c>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E11" s="58" t="inlineStr">
-        <is>
-          <t>BK03</t>
-        </is>
-      </c>
-      <c r="F11" s="60" t="n"/>
-      <c r="G11" s="84">
-        <f>IF($B11="","",$B11&amp;" – "&amp;$C11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="23.25" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>PB03</t>
-        </is>
-      </c>
-      <c r="B12" s="45" t="inlineStr">
-        <is>
-          <t>پرتقال کاراکارا</t>
-        </is>
-      </c>
-      <c r="C12" s="47" t="inlineStr">
-        <is>
-          <t>پرتقال</t>
-        </is>
-      </c>
-      <c r="D12" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E12" s="58" t="inlineStr">
-        <is>
-          <t>BK03</t>
-        </is>
-      </c>
-      <c r="F12" s="60" t="n"/>
-      <c r="G12" s="84">
-        <f>IF($B12="","",$B12&amp;" – "&amp;$C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="23.25" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>PB04</t>
-        </is>
-      </c>
-      <c r="B13" s="45" t="inlineStr">
-        <is>
-          <t>پرتقال بیروتی</t>
-        </is>
-      </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>پرتقال</t>
-        </is>
-      </c>
-      <c r="D13" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E13" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F13" s="60" t="n"/>
-      <c r="G13" s="84">
-        <f>IF($B13="","",$B13&amp;" – "&amp;$C13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="23.25" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>PB05</t>
-        </is>
-      </c>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>پرتقال یافا</t>
-        </is>
-      </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>پرتقال</t>
-        </is>
-      </c>
-      <c r="D14" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E14" s="58" t="inlineStr">
-        <is>
-          <t>BK03</t>
-        </is>
-      </c>
-      <c r="F14" s="60" t="n"/>
-      <c r="G14" s="84">
-        <f>IF($B14="","",$B14&amp;" – "&amp;$C14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="23.25" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>PB06</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="inlineStr">
-        <is>
-          <t>نارنگی پیچ</t>
-        </is>
-      </c>
-      <c r="C15" s="47" t="inlineStr">
-        <is>
-          <t>نارنگی</t>
-        </is>
-      </c>
-      <c r="D15" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E15" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F15" s="60" t="n"/>
-      <c r="G15" s="84">
-        <f>IF($B15="","",$B15&amp;" – "&amp;$C15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="23.25" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>PB07</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>نارنگی ژاپنی</t>
-        </is>
-      </c>
-      <c r="C16" s="47" t="inlineStr">
-        <is>
-          <t>نارنگی</t>
-        </is>
-      </c>
-      <c r="D16" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E16" s="58" t="inlineStr">
-        <is>
-          <t>BK07</t>
-        </is>
-      </c>
-      <c r="F16" s="60" t="n"/>
-      <c r="G16" s="84">
-        <f>IF($B16="","",$B16&amp;" – "&amp;$C16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="23.25" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>PB08</t>
-        </is>
-      </c>
-      <c r="B17" s="45" t="inlineStr">
-        <is>
-          <t>نارنگی اونشو</t>
-        </is>
-      </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>نارنگی</t>
-        </is>
-      </c>
-      <c r="D17" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E17" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F17" s="60" t="n"/>
-      <c r="G17" s="84">
-        <f>IF($B17="","",$B17&amp;" – "&amp;$C17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="23.25" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>PB09</t>
-        </is>
-      </c>
-      <c r="B18" s="45" t="inlineStr">
-        <is>
-          <t>نارنگی یافا</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>نارنگی</t>
-        </is>
-      </c>
-      <c r="D18" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E18" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F18" s="60" t="n"/>
-      <c r="G18" s="84">
-        <f>IF($B18="","",$B18&amp;" – "&amp;$C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="23.25" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>PB10</t>
-        </is>
-      </c>
-      <c r="B19" s="45" t="inlineStr">
-        <is>
-          <t>لیمو شیرین</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="inlineStr">
-        <is>
-          <t>لیمو</t>
-        </is>
-      </c>
-      <c r="D19" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E19" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F19" s="60" t="n"/>
-      <c r="G19" s="84">
-        <f>IF($B19="","",$B19&amp;" – "&amp;$C19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="23.25" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>PB11</t>
-        </is>
-      </c>
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>لیمو ترش</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>لیمو</t>
-        </is>
-      </c>
-      <c r="D20" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E20" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F20" s="60" t="n"/>
-      <c r="G20" s="84">
-        <f>IF($B20="","",$B20&amp;" – "&amp;$C20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="23.25" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>PB12</t>
-        </is>
-      </c>
-      <c r="B21" s="45" t="inlineStr">
-        <is>
-          <t>کامکوات</t>
-        </is>
-      </c>
-      <c r="C21" s="47" t="inlineStr">
-        <is>
-          <t>سایر</t>
-        </is>
-      </c>
-      <c r="D21" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E21" s="58" t="inlineStr">
-        <is>
-          <t>BK04</t>
-        </is>
-      </c>
-      <c r="F21" s="60" t="n"/>
-      <c r="G21" s="84">
-        <f>IF($B21="","",$B21&amp;" – "&amp;$C21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>PB13</t>
-        </is>
-      </c>
-      <c r="B22" s="45" t="inlineStr">
-        <is>
-          <t>گریپ‌فرویت</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>گریپ‌فرویت</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E22" s="58" t="inlineStr">
-        <is>
-          <t>BK03</t>
-        </is>
-      </c>
-      <c r="F22" s="60" t="n"/>
-      <c r="G22" s="84">
-        <f>IF($B22="","",$B22&amp;" – "&amp;$C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="23.25" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>PB14</t>
-        </is>
-      </c>
-      <c r="B23" s="45" t="inlineStr">
-        <is>
-          <t>خرمالو</t>
-        </is>
-      </c>
-      <c r="C23" s="47" t="inlineStr">
-        <is>
-          <t>سایر</t>
-        </is>
-      </c>
-      <c r="D23" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E23" s="58" t="inlineStr">
-        <is>
-          <t>BK01</t>
-        </is>
-      </c>
-      <c r="F23" s="60" t="n"/>
-      <c r="G23" s="84">
-        <f>IF($B23="","",$B23&amp;" – "&amp;$C23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="23.25" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>PB15</t>
-        </is>
-      </c>
-      <c r="B24" s="45" t="inlineStr">
-        <is>
-          <t>نارنج</t>
-        </is>
-      </c>
-      <c r="C24" s="47" t="inlineStr">
-        <is>
-          <t>سایر</t>
-        </is>
-      </c>
-      <c r="D24" s="47" t="inlineStr">
-        <is>
-          <t>کیلوگرم</t>
-        </is>
-      </c>
-      <c r="E24" s="58" t="inlineStr">
-        <is>
-          <t>BK03</t>
-        </is>
-      </c>
-      <c r="F24" s="60" t="n"/>
-      <c r="G24" s="84">
-        <f>IF($B24="","",$B24&amp;" – "&amp;$C24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="23.25" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
-        <is>
-          <t>PB16</t>
-        </is>
-      </c>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="47" t="n"/>
-      <c r="D25" s="47" t="n"/>
-      <c r="E25" s="58" t="n"/>
-      <c r="F25" s="60" t="n"/>
-      <c r="G25" s="84">
-        <f>IF($B25="","",$B25&amp;" – "&amp;$C25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="23.25" customHeight="1">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>PB17</t>
-        </is>
-      </c>
-      <c r="B26" s="45" t="n"/>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="58" t="n"/>
-      <c r="F26" s="60" t="n"/>
-      <c r="G26" s="84">
-        <f>IF($B26="","",$B26&amp;" – "&amp;$C26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="23.25" customHeight="1">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>PB18</t>
-        </is>
-      </c>
-      <c r="B27" s="45" t="n"/>
-      <c r="C27" s="47" t="n"/>
-      <c r="D27" s="47" t="n"/>
-      <c r="E27" s="58" t="n"/>
-      <c r="F27" s="60" t="n"/>
-      <c r="G27" s="84">
-        <f>IF($B27="","",$B27&amp;" – "&amp;$C27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="23.25" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>PB19</t>
-        </is>
-      </c>
-      <c r="B28" s="45" t="n"/>
-      <c r="C28" s="47" t="n"/>
-      <c r="D28" s="47" t="n"/>
-      <c r="E28" s="58" t="n"/>
-      <c r="F28" s="60" t="n"/>
-      <c r="G28" s="84">
-        <f>IF($B28="","",$B28&amp;" – "&amp;$C28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="23.25" customHeight="1">
-      <c r="A29" s="44" t="inlineStr">
-        <is>
-          <t>PB20</t>
-        </is>
-      </c>
-      <c r="B29" s="45" t="n"/>
-      <c r="C29" s="47" t="n"/>
-      <c r="D29" s="47" t="n"/>
-      <c r="E29" s="58" t="n"/>
-      <c r="F29" s="60" t="n"/>
-      <c r="G29" s="84">
-        <f>IF($B29="","",$B29&amp;" – "&amp;$C29)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A8:G30"/>
-  <mergeCells count="10">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:B6"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="C10:C30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>ListCategories</formula1>
-    </dataValidation>
-    <dataValidation sqref="D10:D30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>ListUnits</formula1>
-    </dataValidation>
-    <dataValidation sqref="E10:E30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>ListBaskets</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.28" right="0.28" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;Lمازندشت&amp;RMAZANDASHT · CITRUS</oddHeader>
-    <oddFooter>&amp;Lمازندشت — سورتینگ و بسته‌بندی مرکبات&amp;Cصفحه &amp;P از &amp;N&amp;RMAZANDASHT · 1405</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -22,12 +22,12 @@
     <sheet name="Help" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="AcctCodes">Acc!$A$10:$A$280</definedName>
-    <definedName name="AcctTbl">Acc!$A$10:$J$280</definedName>
+    <definedName name="AcctCodes">Acc!$A$10:$A$281</definedName>
+    <definedName name="AcctTbl">Acc!$A$10:$J$281</definedName>
     <definedName name="BankTbl">Bnk!$A$10:$G$19</definedName>
     <definedName name="BasketTbl">Bsk!$B$10:$F$21</definedName>
     <definedName name="GroupTbl">Grp!$A$10:$F$52</definedName>
-    <definedName name="ListAllCodes">OFFSET(Acc!$A$10,0,0,MAX(COUNTIF(Acc!$D$10:$D$280,"?*"),1),1)</definedName>
+    <definedName name="ListAllCodes">OFFSET(Acc!$A$10,0,0,MAX(COUNTIF(Acc!$D$10:$D$281,"?*"),1),1)</definedName>
     <definedName name="ListBanks">OFFSET(Bnk!$B$10,0,0,MAX(COUNTIF(Bnk!$B$10:$B$19,"?*"),1),1)</definedName>
     <definedName name="ListBasketOps">OFFSET(Op!$B$24,0,0,MAX(COUNTIF(Op!$B$24:$B$33,"?*"),1),1)</definedName>
     <definedName name="ListBaskets">OFFSET(Bsk!$B$10,0,0,MAX(COUNTIF(Bsk!$B$10:$B$21,"?*"),1),1)</definedName>
@@ -2423,12 +2423,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="105" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="78" fillId="20" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
@@ -2443,6 +2437,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4452,51 +4452,51 @@
     </row>
     <row r="51"/>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="216" t="inlineStr">
+      <c r="A52" s="224" t="inlineStr">
         <is>
           <t xml:space="preserve">     فایل‌های همراه — با یک کلیک باز می‌شوند (مسیر نسبی، همه در همین پوشه)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="217" t="inlineStr">
+      <c r="A53" s="225" t="inlineStr">
         <is>
           <t>دفتر ثبت  01_Entry</t>
         </is>
       </c>
-      <c r="C53" s="217" t="inlineStr">
+      <c r="C53" s="225" t="inlineStr">
         <is>
           <t>بانک  02_Bank</t>
         </is>
       </c>
-      <c r="E53" s="217" t="inlineStr">
+      <c r="E53" s="225" t="inlineStr">
         <is>
           <t>گزارش‌ها  03_Report</t>
         </is>
       </c>
-      <c r="G53" s="217" t="inlineStr">
+      <c r="G53" s="225" t="inlineStr">
         <is>
           <t>فاکتورها  04_Inv</t>
         </is>
       </c>
-      <c r="I53" s="217" t="inlineStr">
+      <c r="I53" s="225" t="inlineStr">
         <is>
           <t>تراز  05_Bal</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="217" t="inlineStr">
+      <c r="A54" s="225" t="inlineStr">
         <is>
           <t>خریداران  06_Buyers</t>
         </is>
       </c>
-      <c r="C54" s="217" t="inlineStr">
+      <c r="C54" s="225" t="inlineStr">
         <is>
           <t>نمونه  07_Demo</t>
         </is>
       </c>
-      <c r="E54" s="217" t="inlineStr">
+      <c r="E54" s="225" t="inlineStr">
         <is>
           <t>داشبورد  08_Dash</t>
         </is>
@@ -10142,15 +10142,15 @@
           <t>۰۹   شراکت — خرید و فروش مشترک</t>
         </is>
       </c>
-      <c r="B125" s="222" t="n"/>
-      <c r="C125" s="222" t="n"/>
-      <c r="D125" s="222" t="n"/>
-      <c r="E125" s="222" t="n"/>
-      <c r="F125" s="222" t="n"/>
-      <c r="G125" s="222" t="n"/>
-      <c r="H125" s="222" t="n"/>
-      <c r="I125" s="222" t="n"/>
-      <c r="J125" s="223" t="n"/>
+      <c r="B125" s="220" t="n"/>
+      <c r="C125" s="220" t="n"/>
+      <c r="D125" s="220" t="n"/>
+      <c r="E125" s="220" t="n"/>
+      <c r="F125" s="220" t="n"/>
+      <c r="G125" s="220" t="n"/>
+      <c r="H125" s="220" t="n"/>
+      <c r="I125" s="220" t="n"/>
+      <c r="J125" s="221" t="n"/>
     </row>
     <row r="126" ht="46" customHeight="1">
       <c r="A126" s="212" t="inlineStr">
@@ -10158,15 +10158,15 @@
           <t>شیت Shrk فهرست شرکاست: کد SHxx، نام، «نسبت سهم شریک» و «نسبت سهم شرکت» (خودکار ۱۰۰ منهای آن). همین کدها به شیت Acc هم اضافه شده‌اند (گروه «شرکا»)، پس در باسکول، شیت پرداخت، تراکنش بانکی، دفاتر و ترازنامه مثل هر طرف حساب دیگری انتخاب می‌شوند.</t>
         </is>
       </c>
-      <c r="B126" s="224" t="n"/>
-      <c r="C126" s="224" t="n"/>
-      <c r="D126" s="224" t="n"/>
-      <c r="E126" s="224" t="n"/>
-      <c r="F126" s="224" t="n"/>
-      <c r="G126" s="224" t="n"/>
-      <c r="H126" s="224" t="n"/>
-      <c r="I126" s="224" t="n"/>
-      <c r="J126" s="225" t="n"/>
+      <c r="B126" s="222" t="n"/>
+      <c r="C126" s="222" t="n"/>
+      <c r="D126" s="222" t="n"/>
+      <c r="E126" s="222" t="n"/>
+      <c r="F126" s="222" t="n"/>
+      <c r="G126" s="222" t="n"/>
+      <c r="H126" s="222" t="n"/>
+      <c r="I126" s="222" t="n"/>
+      <c r="J126" s="223" t="n"/>
     </row>
     <row r="127" ht="46" customHeight="1">
       <c r="A127" s="213" t="inlineStr">
@@ -10174,15 +10174,15 @@
           <t xml:space="preserve">     •  در باسکول دو عملیات تازه اضافه شده: «خرید شراکتی (ورود)» و «فروش شراکتی (خروج)». کافی است عملیات را انتخاب و کد شریک را در ستون «کد حساب / مقصد وجه» بزنید.</t>
         </is>
       </c>
-      <c r="B127" s="224" t="n"/>
-      <c r="C127" s="224" t="n"/>
-      <c r="D127" s="224" t="n"/>
-      <c r="E127" s="224" t="n"/>
-      <c r="F127" s="224" t="n"/>
-      <c r="G127" s="224" t="n"/>
-      <c r="H127" s="224" t="n"/>
-      <c r="I127" s="224" t="n"/>
-      <c r="J127" s="225" t="n"/>
+      <c r="B127" s="222" t="n"/>
+      <c r="C127" s="222" t="n"/>
+      <c r="D127" s="222" t="n"/>
+      <c r="E127" s="222" t="n"/>
+      <c r="F127" s="222" t="n"/>
+      <c r="G127" s="222" t="n"/>
+      <c r="H127" s="222" t="n"/>
+      <c r="I127" s="222" t="n"/>
+      <c r="J127" s="223" t="n"/>
     </row>
     <row r="128" ht="46" customHeight="1">
       <c r="A128" s="213" t="inlineStr">
@@ -10190,15 +10190,15 @@
           <t xml:space="preserve">     •  محاسبه به وزن است: شیت Scale شش ستون تازه دارد — نسبت شرکت، سهم شرکت (ریال)، سهم شریک (ریال)، سهم شرکت (kg)، سهم شریک (kg) و کنترل. مبلغ هر ردیف = وزن خالص × فی.</t>
         </is>
       </c>
-      <c r="B128" s="224" t="n"/>
-      <c r="C128" s="224" t="n"/>
-      <c r="D128" s="224" t="n"/>
-      <c r="E128" s="224" t="n"/>
-      <c r="F128" s="224" t="n"/>
-      <c r="G128" s="224" t="n"/>
-      <c r="H128" s="224" t="n"/>
-      <c r="I128" s="224" t="n"/>
-      <c r="J128" s="225" t="n"/>
+      <c r="B128" s="222" t="n"/>
+      <c r="C128" s="222" t="n"/>
+      <c r="D128" s="222" t="n"/>
+      <c r="E128" s="222" t="n"/>
+      <c r="F128" s="222" t="n"/>
+      <c r="G128" s="222" t="n"/>
+      <c r="H128" s="222" t="n"/>
+      <c r="I128" s="222" t="n"/>
+      <c r="J128" s="223" t="n"/>
     </row>
     <row r="129" ht="46" customHeight="1">
       <c r="A129" s="213" t="inlineStr">
@@ -10206,15 +10206,15 @@
           <t xml:space="preserve">     •  در دفتر روزنامه فقط «سهم شرکت» سند می‌خورد (خرید: بدهکار موجودی / بستانکار شریک — فروش: بدهکار خریدار / بستانکار فروش). سهم شریک در گزارش شیت Shrk فایل 01_Entry دیده می‌شود.</t>
         </is>
       </c>
-      <c r="B129" s="224" t="n"/>
-      <c r="C129" s="224" t="n"/>
-      <c r="D129" s="224" t="n"/>
-      <c r="E129" s="224" t="n"/>
-      <c r="F129" s="224" t="n"/>
-      <c r="G129" s="224" t="n"/>
-      <c r="H129" s="224" t="n"/>
-      <c r="I129" s="224" t="n"/>
-      <c r="J129" s="225" t="n"/>
+      <c r="B129" s="222" t="n"/>
+      <c r="C129" s="222" t="n"/>
+      <c r="D129" s="222" t="n"/>
+      <c r="E129" s="222" t="n"/>
+      <c r="F129" s="222" t="n"/>
+      <c r="G129" s="222" t="n"/>
+      <c r="H129" s="222" t="n"/>
+      <c r="I129" s="222" t="n"/>
+      <c r="J129" s="223" t="n"/>
     </row>
     <row r="130" ht="46" customHeight="1">
       <c r="A130" s="213" t="inlineStr">
@@ -10222,15 +10222,15 @@
           <t xml:space="preserve">     •  پرداخت به شریک = سهم واریزی ما: در شیت پرداخت نوع «پرداخت»، کد SHxx و روش پرداخت را بزنید. این پرداخت‌ها در جدول شرکا از بدهی ما کم می‌شود و ستون «مانده» بدهی باقی‌مانده را نشان می‌دهد.</t>
         </is>
       </c>
-      <c r="B130" s="224" t="n"/>
-      <c r="C130" s="224" t="n"/>
-      <c r="D130" s="224" t="n"/>
-      <c r="E130" s="224" t="n"/>
-      <c r="F130" s="224" t="n"/>
-      <c r="G130" s="224" t="n"/>
-      <c r="H130" s="224" t="n"/>
-      <c r="I130" s="224" t="n"/>
-      <c r="J130" s="225" t="n"/>
+      <c r="B130" s="222" t="n"/>
+      <c r="C130" s="222" t="n"/>
+      <c r="D130" s="222" t="n"/>
+      <c r="E130" s="222" t="n"/>
+      <c r="F130" s="222" t="n"/>
+      <c r="G130" s="222" t="n"/>
+      <c r="H130" s="222" t="n"/>
+      <c r="I130" s="222" t="n"/>
+      <c r="J130" s="223" t="n"/>
     </row>
     <row r="131" ht="46" customHeight="1">
       <c r="A131" s="213" t="inlineStr">
@@ -10238,15 +10238,15 @@
           <t xml:space="preserve">     •  برای تغییر نسبت یک شریک، فقط ستون «نسبت سهم شریک ٪» را در همین شیت عوض کنید؛ فایل‌های دیگر با باز شدن، Sync خود را از نو می‌خوانند (نسخه جدید پوشه، همان کدها).</t>
         </is>
       </c>
-      <c r="B131" s="224" t="n"/>
-      <c r="C131" s="224" t="n"/>
-      <c r="D131" s="224" t="n"/>
-      <c r="E131" s="224" t="n"/>
-      <c r="F131" s="224" t="n"/>
-      <c r="G131" s="224" t="n"/>
-      <c r="H131" s="224" t="n"/>
-      <c r="I131" s="224" t="n"/>
-      <c r="J131" s="225" t="n"/>
+      <c r="B131" s="222" t="n"/>
+      <c r="C131" s="222" t="n"/>
+      <c r="D131" s="222" t="n"/>
+      <c r="E131" s="222" t="n"/>
+      <c r="F131" s="222" t="n"/>
+      <c r="G131" s="222" t="n"/>
+      <c r="H131" s="222" t="n"/>
+      <c r="I131" s="222" t="n"/>
+      <c r="J131" s="223" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="1" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -12913,7 +12913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P280"/>
+  <dimension ref="A1:P281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -23485,6 +23485,65 @@
       <c r="K280">
         <f>IF($A280="","",IF(LEFT($A280,2)="SH","شرکا",""))</f>
         <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="164" t="inlineStr">
+        <is>
+          <t>X022</t>
+        </is>
+      </c>
+      <c r="B281" s="164" t="inlineStr">
+        <is>
+          <t>سایر حساب</t>
+        </is>
+      </c>
+      <c r="C281" s="164" t="inlineStr">
+        <is>
+          <t>هزینه</t>
+        </is>
+      </c>
+      <c r="D281" s="164" t="inlineStr">
+        <is>
+          <t>کارمزد و هزینه‌های بانکی</t>
+        </is>
+      </c>
+      <c r="E281" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F281" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G281" s="164" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>حساب هزینه</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="K281">
+        <f>IF($A281="","",IF(LEFT($A281,2)="X0","سایر حساب",""))</f>
+        <v/>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>همه کارمزدها و هزینه‌های بانکی اینجا جمع می‌شود.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23697,7 +23756,7 @@
     </row>
     <row r="8"/>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="218" t="inlineStr">
+      <c r="A9" s="216" t="inlineStr">
         <is>
           <t>فهرست شرکا   کدها را تغییر ندهید؛ نام و نسبت را آزادانه به‌روز کنید</t>
         </is>
@@ -24621,38 +24680,38 @@
     </row>
     <row r="32"/>
     <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="219" t="inlineStr">
+      <c r="A33" s="217" t="inlineStr">
         <is>
           <t xml:space="preserve">   قاعده: سهم شریک از «وزن» محاسبه می‌شود. در باسکول، عملیات «خرید شراکتی (ورود)» یا «فروش شراکتی (خروج)» را بزنید و کد شریک را در ستون طرف حساب انتخاب کنید؛ سیستم وزن و مبلغ را به دو سهم تقسیم می‌کند و فقط سهم شرکت را سند می‌زند.</t>
         </is>
       </c>
-      <c r="B33" s="220" t="n"/>
-      <c r="C33" s="220" t="n"/>
-      <c r="D33" s="220" t="n"/>
-      <c r="E33" s="220" t="n"/>
-      <c r="F33" s="220" t="n"/>
-      <c r="G33" s="220" t="n"/>
-      <c r="H33" s="220" t="n"/>
-      <c r="I33" s="220" t="n"/>
-      <c r="J33" s="220" t="n"/>
-      <c r="K33" s="220" t="n"/>
+      <c r="B33" s="218" t="n"/>
+      <c r="C33" s="218" t="n"/>
+      <c r="D33" s="218" t="n"/>
+      <c r="E33" s="218" t="n"/>
+      <c r="F33" s="218" t="n"/>
+      <c r="G33" s="218" t="n"/>
+      <c r="H33" s="218" t="n"/>
+      <c r="I33" s="218" t="n"/>
+      <c r="J33" s="218" t="n"/>
+      <c r="K33" s="218" t="n"/>
     </row>
     <row r="34" ht="38" customHeight="1">
-      <c r="A34" s="221" t="inlineStr">
+      <c r="A34" s="219" t="inlineStr">
         <is>
           <t xml:space="preserve">   پرداخت به شریک = سهم واریزی ما. هر پرداخت به حساب SHxx در شیت پرداخت (01_Entry) یا تراکنش بانکی (02_Bank) ثبت شود تا مانده بدهی ما به شریک، خودکار محاسبه شود.</t>
         </is>
       </c>
-      <c r="B34" s="220" t="n"/>
-      <c r="C34" s="220" t="n"/>
-      <c r="D34" s="220" t="n"/>
-      <c r="E34" s="220" t="n"/>
-      <c r="F34" s="220" t="n"/>
-      <c r="G34" s="220" t="n"/>
-      <c r="H34" s="220" t="n"/>
-      <c r="I34" s="220" t="n"/>
-      <c r="J34" s="220" t="n"/>
-      <c r="K34" s="220" t="n"/>
+      <c r="B34" s="218" t="n"/>
+      <c r="C34" s="218" t="n"/>
+      <c r="D34" s="218" t="n"/>
+      <c r="E34" s="218" t="n"/>
+      <c r="F34" s="218" t="n"/>
+      <c r="G34" s="218" t="n"/>
+      <c r="H34" s="218" t="n"/>
+      <c r="I34" s="218" t="n"/>
+      <c r="J34" s="218" t="n"/>
+      <c r="K34" s="218" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -6143,7 +6143,7 @@
       </c>
       <c r="U8" s="150" t="inlineStr">
         <is>
-          <t>بانک عامل (کد و نام)</t>
+          <t>بانک شرکت (کد و نام)</t>
         </is>
       </c>
     </row>

--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -27,7 +27,7 @@
     <definedName name="BankTbl">Bnk!$A$10:$G$19</definedName>
     <definedName name="BasketTbl">Bsk!$B$10:$F$21</definedName>
     <definedName name="GroupTbl">Grp!$A$10:$F$52</definedName>
-    <definedName name="ListAllCodes">OFFSET(Acc!$A$10,0,0,MAX(COUNTIF(Acc!$D$10:$D$281,"?*"),1),1)</definedName>
+    <definedName name="ListAllCodes">OFFSET(Sync!$B$10,0,0,MAX(COUNTIF(Sync!$C$10:$C$281,"?*"),1),1)</definedName>
     <definedName name="ListBanks">OFFSET(Bnk!$B$10,0,0,MAX(COUNTIF(Bnk!$B$10:$B$19,"?*"),1),1)</definedName>
     <definedName name="ListBasketOps">OFFSET(Op!$B$24,0,0,MAX(COUNTIF(Op!$B$24:$B$33,"?*"),1),1)</definedName>
     <definedName name="ListBaskets">OFFSET(Bsk!$B$10,0,0,MAX(COUNTIF(Bsk!$B$10:$B$21,"?*"),1),1)</definedName>

--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -3797,7 +3797,7 @@
     <row r="3" ht="20.25" customHeight="1">
       <c r="A3" s="107" t="inlineStr">
         <is>
-          <t>فایل مادر (INFO) — مرکز تعریف حساب‌ها، عملیات، سبدها، بانک‌ها و پارامترها  ·  نسخه ۰۱  ·  Excel 2013</t>
+          <t>فایل مادر (فایل مادر 00_Master) — مرکز تعریف حساب‌ها، عملیات، سبدها، بانک‌ها و پارامترها  ·  نسخه ۰۱  ·  Excel 2013</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
     <row r="10" ht="21.75" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>INFO  ·  فایل مادر — همین فایل</t>
+          <t>فایل مادر 00_Master  ·  فایل مادر — همین فایل</t>
         </is>
       </c>
       <c r="B10" s="109" t="n"/>
@@ -4069,7 +4069,7 @@
     <row r="24" ht="26.25" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>فایل مادر 00_Master</t>
         </is>
       </c>
       <c r="B24" s="111" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="27" ht="20.25" customHeight="1">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>۰۱ ثبت ← INFO</t>
+          <t>۰۱ ثبت ← فایل مادر 00_Master</t>
         </is>
       </c>
       <c r="B27" s="112" t="n"/>
@@ -4134,14 +4134,14 @@
     <row r="28" ht="20.25" customHeight="1">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>۰۲ گزارش ← ۰۱ ثبت + INFO</t>
+          <t>۰۲ گزارش ← ۰۱ ثبت + فایل مادر 00_Master</t>
         </is>
       </c>
       <c r="B28" s="112" t="n"/>
       <c r="C28" s="113" t="n"/>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>ریز باسکول، سبد و پرداخت‌ها؛ نام و گروه از INFO</t>
+          <t>ریز باسکول، سبد و پرداخت‌ها؛ نام و گروه از فایل مادر 00_Master</t>
         </is>
       </c>
       <c r="E28" s="112" t="n"/>
@@ -4154,7 +4154,7 @@
     <row r="29" ht="20.25" customHeight="1">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>۰۳ فاکتور ← ۰۱ ثبت + INFO</t>
+          <t>۰۳ فاکتور ← ۰۱ ثبت + فایل مادر 00_Master</t>
         </is>
       </c>
       <c r="B29" s="112" t="n"/>
@@ -4194,7 +4194,7 @@
     <row r="31" ht="20.25" customHeight="1">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>۰۵ بانک ← INFO + ۰۱ ثبت</t>
+          <t>۰۵ بانک ← فایل مادر 00_Master + ۰۱ ثبت</t>
         </is>
       </c>
       <c r="B31" s="112" t="n"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>بعد از هر تغییر در INFO، فایل‌های دیگر را باز کنید و Data ← Edit Links ← Update Values بزنید.</t>
+          <t>بعد از هر تغییر در فایل مادر 00_Master، فایل‌های دیگر را باز کنید و Data ← Edit Links ← Update Values بزنید.</t>
         </is>
       </c>
       <c r="C39" s="112" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>اگر فرمولی «#NAME?» داد، یعنی فایل INFO بسته یا جابه‌جا شده است؛ ابتدا لینک را Update کنید.</t>
+          <t>اگر فرمولی «#NAME?» داد، یعنی فایل فایل مادر 00_Master بسته یا جابه‌جا شده است؛ ابتدا لینک را Update کنید.</t>
         </is>
       </c>
       <c r="C42" s="112" t="n"/>
@@ -4578,18 +4578,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
     <hyperlink ref="A44" location="Help!A20" display="راهنمای کامل سامانه — روی این نوار کلیک کنید"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId17"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
@@ -4602,7 +4602,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -8929,7 +8929,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="106" t="inlineStr">
         <is>
-          <t>راهنمای کامل فایل مادر (INFO)</t>
+          <t>راهنمای کامل فایل مادر (فایل مادر 00_Master)</t>
         </is>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="91" t="inlineStr">
         <is>
-          <t>این شیت قفل است و فقط برای مطالعه است. همه فایل‌های دیگر از همین فایل خوانده می‌شوند؛ بنابراین ترتیب کار همیشه این است: اول INFO، بعد ثبت، بعد گزارش/فاکتور/ترازنامه. هر بخش را با یک مثال واقعی از عملیات سورتینگ توضیح داده‌ایم.</t>
+          <t>این شیت قفل است و فقط برای مطالعه است. همه فایل‌های دیگر از همین فایل خوانده می‌شوند؛ بنابراین ترتیب کار همیشه این است: اول فایل مادر 00_Master، بعد ثبت، بعد گزارش/فاکتور/ترازنامه. هر بخش را با یک مثال واقعی از عملیات سورتینگ توضیح داده‌ایم.</t>
         </is>
       </c>
       <c r="B5" s="112" t="n"/>
@@ -9209,7 +9209,7 @@
     <row r="29" ht="32.25" customHeight="1">
       <c r="B29" s="102" t="inlineStr">
         <is>
-          <t>قانون یک‌خطی: INFO تعریف می‌کند، «ثبت» می‌نویسد، بقیه می‌خوانند و گزارش می‌دهند.</t>
+          <t>قانون یک‌خطی: فایل مادر 00_Master تعریف می‌کند، «ثبت» می‌نویسد، بقیه می‌خوانند و گزارش می‌دهند.</t>
         </is>
       </c>
       <c r="C29" s="112" t="n"/>
@@ -9252,7 +9252,7 @@
     <row r="33" ht="81" customHeight="1">
       <c r="B33" s="101" t="inlineStr">
         <is>
-          <t>جریان داده یک‌طرفه است: INFO → ثبت → گزارش/فاکتور/ترازنامه. فایل بانک هم از INFO بانک‌ها و از ثبت پرداخت‌ها را می‌خواند تا مغایرت بانکی را نشان دهد. هیچ‌گاه داده را در دو جا وارد نکنید؛ اگر بار در باسکول ثبت شد، همان‌جا می‌ماند و گزارش‌ها از همان می‌خوانند. فایل 07 نمونه هیچ ارتباطی با فایل‌های اصلی ندارد و برای آموزش است؛ داده‌هایش را جدی نگیرید.</t>
+          <t>جریان داده یک‌طرفه است: فایل مادر 00_Master → ثبت → گزارش/فاکتور/ترازنامه. فایل بانک هم از فایل مادر 00_Master بانک‌ها و از ثبت پرداخت‌ها را می‌خواند تا مغایرت بانکی را نشان دهد. هیچ‌گاه داده را در دو جا وارد نکنید؛ اگر بار در باسکول ثبت شد، همان‌جا می‌ماند و گزارش‌ها از همان می‌خوانند. فایل 07 نمونه هیچ ارتباطی با فایل‌های اصلی ندارد و برای آموزش است؛ داده‌هایش را جدی نگیرید.</t>
         </is>
       </c>
     </row>
@@ -9744,14 +9744,14 @@
     <row r="84" ht="81" customHeight="1">
       <c r="B84" s="101" t="inlineStr">
         <is>
-          <t>فایل‌های دیگر به INFO لینک خارجی دارند. وقتی INFO را تغییر می‌دهید و ذخیره می‌کنید، فایل‌های دیگر ممکن است تا زمانی که باز و Update نشوند، مقدار قدیمی را نشان دهند. در Excel 2013: فایل را باز کنید، اگر پیام «This workbook contains links…» آمد Update را بزنید؛ یا از مسیر Data → Edit Links → Update Values استفاده کنید. برای اطمینان، یک بار Ctrl+Alt+F9 بزنید تا همه فرمول‌ها از نو محاسبه شوند.</t>
+          <t>فایل‌های دیگر به فایل مادر 00_Master لینک خارجی دارند. وقتی فایل مادر 00_Master را تغییر می‌دهید و ذخیره می‌کنید، فایل‌های دیگر ممکن است تا زمانی که باز و Update نشوند، مقدار قدیمی را نشان دهند. در Excel 2013: فایل را باز کنید، اگر پیام «This workbook contains links…» آمد Update را بزنید؛ یا از مسیر Data → Edit Links → Update Values استفاده کنید. برای اطمینان، یک بار Ctrl+Alt+F9 بزنید تا همه فرمول‌ها از نو محاسبه شوند.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="81" customHeight="1">
       <c r="B85" s="101" t="inlineStr">
         <is>
-          <t>اگر فایل‌ها را جابه‌جا کردید، Edit Links → Change Source را بزنید و 00_Master.xlsx جدید را انتخاب کنید. اگر نام INFO را عوض کردید، همین کار لازم است. هرگز فایل INFO را با نام دیگری ذخیره نکنید مگر اینکه همه لینک‌ها را عوض کنید. در نسخه ۰۱ مسیرها نسبی‌اند؛ یعنی اگر کل پوشه را جابه‌جا کنید، لینک‌ها سالم می‌مانند به شرطی که همه فایل‌ها با هم جابه‌جا شوند.</t>
+          <t>اگر فایل‌ها را جابه‌جا کردید، Edit Links → Change Source را بزنید و 00_Master.xlsx جدید را انتخاب کنید. اگر نام فایل مادر 00_Master را عوض کردید، همین کار لازم است. هرگز فایل فایل مادر 00_Master را با نام دیگری ذخیره نکنید مگر اینکه همه لینک‌ها را عوض کنید. در نسخه ۰۱ مسیرها نسبی‌اند؛ یعنی اگر کل پوشه را جابه‌جا کنید، لینک‌ها سالم می‌مانند به شرطی که همه فایل‌ها با هم جابه‌جا شوند.</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
     <row r="91" ht="66" customHeight="1">
       <c r="B91" s="101" t="inlineStr">
         <is>
-          <t>ترازنامه باید همیشه تراز باشد: جمع بدهکاران = جمع بستانکاران. اگر نبود، اول مانده‌های افتتاحیه INFO را چک کنید، بعد ردیف‌های بدون طرف حساب در ثبت، و در آخر عملیات‌هایی که حساب معینشان خالی است. شیت حسابرسی همین کنترل‌ها را ردیف‌به‌ردیف نشان می‌دهد.</t>
+          <t>ترازنامه باید همیشه تراز باشد: جمع بدهکاران = جمع بستانکاران. اگر نبود، اول مانده‌های افتتاحیه فایل مادر 00_Master را چک کنید، بعد ردیف‌های بدون طرف حساب در ثبت، و در آخر عملیات‌هایی که حساب معینشان خالی است. شیت حسابرسی همین کنترل‌ها را ردیف‌به‌ردیف نشان می‌دهد.</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
     <row r="95" ht="81" customHeight="1">
       <c r="B95" s="101" t="inlineStr">
         <is>
-          <t>#NAME? یعنی نام محدوده یا فایل پیدا نشد: معمولاً INFO بسته است یا اسم شیت عوض شده. فایل را باز و لینک را Update کنید. #REF! یعنی محدوده حذف شده یا ردیف/ستون جابه‌جا شده. #VALUE! یعنی در سلول عددی، متن گذاشته‌اید (مثلاً فی خرید را با کاما یا خط تیره وارد کرده‌اید). #N/A یعنی VLOOKUP کد را پیدا نکرده؛ کد را با شیت Accounts مقایسه کنید.</t>
+          <t>#NAME? یعنی نام محدوده یا فایل پیدا نشد: معمولاً فایل مادر 00_Master بسته است یا اسم شیت عوض شده. فایل را باز و لینک را Update کنید. #REF! یعنی محدوده حذف شده یا ردیف/ستون جابه‌جا شده. #VALUE! یعنی در سلول عددی، متن گذاشته‌اید (مثلاً فی خرید را با کاما یا خط تیره وارد کرده‌اید). #N/A یعنی VLOOKUP کد را پیدا نکرده؛ کد را با شیت Accounts مقایسه کنید.</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
     <row r="100" ht="66" customHeight="1">
       <c r="B100" s="101" t="inlineStr">
         <is>
-          <t>هر هفته یک نسخه از کل پوشه با تاریخ در نام بگیرید: Mazandasht_1405-07-10. فایل INFO را جداگانه هم نگه دارید، چون مرجع تعریف‌هاست. قبل از هر تغییر بزرگ (افزودن گروه، تغییر پارامتر، ارتقای نسخه) یک نسخه فوری بگیرید. فایل‌ها را روی OneDrive یا فضای ابری نگه دارید تا اگر سیستم خراب شد، قابل بازیابی باشند.</t>
+          <t>هر هفته یک نسخه از کل پوشه با تاریخ در نام بگیرید: Mazandasht_1405-07-10. فایل فایل مادر 00_Master را جداگانه هم نگه دارید، چون مرجع تعریف‌هاست. قبل از هر تغییر بزرگ (افزودن گروه، تغییر پارامتر، ارتقای نسخه) یک نسخه فوری بگیرید. فایل‌ها را روی OneDrive یا فضای ابری نگه دارید تا اگر سیستم خراب شد، قابل بازیابی باشند.</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10029,7 @@
     <row r="114" ht="20.25" customHeight="1">
       <c r="B114" s="160" t="inlineStr">
         <is>
-          <t>•  بعد از هر تغییر INFO: Data → Edit Links → Update Values.</t>
+          <t>•  بعد از هر تغییر فایل مادر 00_Master: Data → Edit Links → Update Values.</t>
         </is>
       </c>
     </row>

--- a/Mazandasht_v04/00_Master.xlsx
+++ b/Mazandasht_v04/00_Master.xlsx
@@ -62,7 +62,7 @@
     <definedName name="ShrkTbl">Shrk!$A$12:$D$31</definedName>
     <definedName name="ListShrk">OFFSET(Shrk!$A$12,0,0,MAX(COUNTIF(Shrk!$B$12:$B$31,"?*"),1),1)</definedName>
     <definedName name="ListShrkNames">OFFSET(Shrk!$B$12,0,0,MAX(COUNTIF(Shrk!$B$12:$B$31,"?*"),1),1)</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Home'!$A$1:$J$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Co'!$A$1:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Par'!$A$8:$E$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Par'!$7:$9</definedName>
@@ -965,7 +965,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="80">
+  <borders count="84">
     <border>
       <left/>
       <right/>
@@ -1860,11 +1860,55 @@
         <color rgb="00D8D2C2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D8D2C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8D2C2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D8D2C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8D2C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8D2C2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -2441,8 +2485,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="106" fillId="34" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3769,10 +3815,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.7109375" customWidth="1" min="1" max="10"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -4464,46 +4519,64 @@
           <t>دفتر ثبت  01_Entry</t>
         </is>
       </c>
-      <c r="C53" s="225" t="inlineStr">
+      <c r="B53" s="226" t="n"/>
+      <c r="C53" s="227" t="n"/>
+      <c r="D53" s="225" t="inlineStr">
         <is>
           <t>بانک  02_Bank</t>
         </is>
       </c>
-      <c r="E53" s="225" t="inlineStr">
+      <c r="E53" s="226" t="n"/>
+      <c r="F53" s="227" t="n"/>
+      <c r="G53" s="225" t="inlineStr">
         <is>
           <t>گزارش‌ها  03_Report</t>
         </is>
       </c>
-      <c r="G53" s="225" t="inlineStr">
-        <is>
-          <t>فاکتورها  04_Inv</t>
-        </is>
-      </c>
-      <c r="I53" s="225" t="inlineStr">
-        <is>
-          <t>تراز  05_Bal</t>
-        </is>
-      </c>
+      <c r="H53" s="226" t="n"/>
+      <c r="I53" s="227" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="225" t="inlineStr">
         <is>
+          <t>فاکتورها  04_Inv</t>
+        </is>
+      </c>
+      <c r="B54" s="226" t="n"/>
+      <c r="C54" s="227" t="n"/>
+      <c r="D54" s="225" t="inlineStr">
+        <is>
+          <t>تراز  05_Bal</t>
+        </is>
+      </c>
+      <c r="E54" s="226" t="n"/>
+      <c r="F54" s="227" t="n"/>
+      <c r="G54" s="225" t="inlineStr">
+        <is>
           <t>خریداران  06_Buyers</t>
         </is>
       </c>
-      <c r="C54" s="225" t="inlineStr">
+      <c r="H54" s="226" t="n"/>
+      <c r="I54" s="227" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="225" t="inlineStr">
         <is>
           <t>نمونه  07_Demo</t>
         </is>
       </c>
-      <c r="E54" s="225" t="inlineStr">
+      <c r="B55" s="226" t="n"/>
+      <c r="C55" s="227" t="n"/>
+      <c r="D55" s="225" t="inlineStr">
         <is>
           <t>داشبورد  08_Dash</t>
         </is>
       </c>
+      <c r="E55" s="226" t="n"/>
+      <c r="F55" s="227" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="74">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="D28:J28"/>
     <mergeCell ref="G12:H12"/>
@@ -4515,6 +4588,7 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G53:I53"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="B23:J23"/>
@@ -4524,9 +4598,11 @@
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="A52:J52"/>
+    <mergeCell ref="D53:F53"/>
     <mergeCell ref="D29:J29"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="B38:J38"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="B34:J34"/>
@@ -4539,13 +4615,16 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D55:F55"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="D31:J31"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G54:I54"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="G15:H15"/>
@@ -4560,6 +4639,7 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="B35:J35"/>
+    <mergeCell ref="D54:F54"/>
     <mergeCell ref="D27:J27"/>
     <mergeCell ref="D32:J32"/>
     <mergeCell ref="A1:F1"/>
@@ -4570,6 +4650,7 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="B39:J39"/>
+    <mergeCell ref="A54:C54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId1"/>
@@ -4583,13 +4664,13 @@
     <hyperlink ref="A44" location="Help!A20" display="راهنمای کامل سامانه — روی این نوار کلیک کنید"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId17"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.3" footer="0.3"/>
